--- a/Vigil_Content_v2.0.xlsx
+++ b/Vigil_Content_v2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicsmacbook/pCloud Drive/Personal/Vigil/Vigil v2/vigil-build/Vigil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FC6D94-0B9C-2047-A922-909F590018EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FE3BB9-1C94-D847-9424-9CD0D97FFEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12020" yWindow="660" windowWidth="17320" windowHeight="18460" activeTab="1" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="179">
   <si>
     <t>Hover Links</t>
   </si>
@@ -2580,42 +2580,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Our Lady of Fatima.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Title given to the Virgin Mary following reported apparitions to three shepherd children — Lúcia dos Santos, Francisco Marto and Jacinta Marto — at Fátima, Portugal, between May and October 1917. The Church remembers her today; the memorial falls on this date because 13 May 1917 was the date of the first apparition, and the message carried there was, at its heart, a call to witness and to prayer in a world shaped by conflict.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Author · Acts of the Apostles (1st century AD). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Traditionally identified as Luke, a physician and companion of St Paul, and as the author of both the synonymous Gospel and the Acts of the Apostles. He is featured today because Acts 1 gives the disciples — and the reader — their commission: to be witnesses to the risen Christ from Jerusalem to the ends of the earth.</t>
-    </r>
-  </si>
-  <si>
     <t>We are in the fifth week of Eastertide, on the Saturday before the Sixth Sunday of Easter.
 This week, we have moved through love, friendship, choosing, intercession and witness. Saturday in the liturgical week has its own quality — a pause before the Sunday, a moment to let what has been given settle before the arc begins again.</t>
   </si>
@@ -2630,23 +2594,6 @@
     <t>10 May 2026
 6th Sunday of Easter
 Eastertide · Week Six</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PEACE [pees]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>The English word barely carries what the original means.
-In the Greek of the New Testament, eirēnē (εἰρήνη) translates the Hebrew shalom (שָׁלוֹם) — and shalom is not the absence of conflict. It is a positive condition: wholeness, right relation, the settled flourishing of a life held in proper order before God and neighbour. To greet someone with shalom was not to wish them a quiet life. It was to wish them everything that makes life fully itself.
-When Jesus says "my peace I give to you," he is not offering tranquillity. He is offering participation in the deep order that holds all things — the peace that belongs to someone who knows, even in the darkest hours, that the outcome is not finally in doubt.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2749,6 +2696,921 @@
         <family val="1"/>
       </rPr>
       <t>Traditionally identified as one of the Twelve Apostles and as the author of the fourth Gospel, three letters and the book of Revelation. He is featured today because John 14 places this gift of peace in the Farewell Discourse — Christ's final private words to his disciples before his death — where it arrives not as reassurance, but as something deliberately left behind.</t>
+    </r>
+  </si>
+  <si>
+    <t>CL-0511</t>
+  </si>
+  <si>
+    <t>11 May 2026
+Monday
+Eastertide · Week Six</t>
+  </si>
+  <si>
+    <t>CL-0512</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">12 May 2026
+Tuesday
+Eastertide · Week Six
+Optional Memorals: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Sts Nereus and Achilleus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Martyrs
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Pancras</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, Martyr</t>
+    </r>
+  </si>
+  <si>
+    <t>CL-0513</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">13 May 2026
+Tuesday
+Eastertide · Week Six
+Optional Memorals: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Our Lady of Fatima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Author · Acts of the Apostles (1st century AD). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Traditionally identified as Luke, a physician and companion of St Paul, and as the author of both the synonymous Gospel and the Acts of the Apostles. He is featured today because Acts 1 gives the disciples — and the reader — their commission: to be witnesses to the risen Christ from Jerusalem to the ends of the earth.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in the sixth week of Eastertide, five weeks on from the resurrection and one week from Pentecost.
+The season is moving toward its close — and as it does, Vigil turns to a word that belongs to this threshold moment: what it means to be held when the one who held you is about to leave.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"Comfort, O comfort my people,
+says your God.
+Speak tenderly to Jerusalem,
+and cry to her
+that she has served her term,
+that her penalty is paid,
+that she has received from the Lord's hand
+double for all her sins."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Isaiah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 40:1–2 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You are the God who speaks tenderly — not across the distance, but into it.
+Where grief, fear or weariness has made us feel that you have gone far off, draw near.
+Where we have kept sorrow to ourselves because we were not sure it was permitted, teach us to receive what you are already offering.
+Come close to the places in us that have forgotten how to breathe.
+Let your comfort be not a word spoken at us, but a presence that stays.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Isaiah (8th–6th century BC). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>A prophet of ancient Israel. He wrote at a time when Israel had been conquered by Babylon and its people taken into exile — far from home, far from the Temple, and with the sense that God, who had spoken to and through Israel, had fallen silent because of their disobedience. Isaiah 40 opens with God's first word back into that silence.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Today, when someone offers you kindness — a patient word, an unexpected gesture, a moment of genuine attention — let yourself receive it fully rather than deflecting or minimising it. 
+Do not say it was nothing. Sit with it for a moment and let it be what it is: God speaking tenderly, through an ordinary person, into an ordinary day.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Comfort arrives through hands before it arrives as theology</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">There is a kind of grief that does not want to be argued with. It has heard all the right things said kindly, and it has not moved.
+What it needs is not more words. It needs someone to come in and sit down.
+That is what God commands in Isaiah — not explanation, not theology, but closeness. Speak to the heart. Come in near. The word he uses, nacham, is the word for someone who cannot breathe, being given breath back by another's presence.
+The Spirit Jesus promises is the one who does exactly this — not a message sent from safety, but a presence that comes into the heaviness and stays.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where has God felt far off to you and why? And is it possible that the distance is not his, but yours?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>We are in the sixth week of Eastertide, moving through the final days before Pentecost.
+Today the Church may remember</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Saints Nereus and Achilleus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Pancras</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — three early Christians who were put to death for their faith. Their lives ask a question that Eastertide has been building toward: what is it that holds when everything else is taken away?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Rejoice in the Lord always; again I will say, Rejoice. Let your gentleness be known to everyone. The Lord is near. Do not worry about anything, but in everything by prayer and supplication with thanksgiving let your requests be made known to God. And the peace of God, which surpasses all understanding, will guard your hearts and your minds in Christ Jesus."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Philippians 4:4–7 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Paul writes this from prison. That is not background detail — it is the whole point. He is not describing how he feels. He is describing what he has chosen, and from where.
+Notice what follows immediately after the command to rejoice: do not worry about anything. Paul places them side by side because he knows they cannot both occupy the same ground. Worry insists that the outcome is uncertain and that you are responsible for it. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Chairō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> insists that the ground beneath you is held by someone else, regardless of what is happening above it.
+That is not cheerfulness. It is a decision — made before the circumstances change, because it does not depend on them changing.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where has worry made joy feel not just distant but dishonest? And what would it mean to place that difficulty before God with thanksgiving and to trust that the ground holds?</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You are the ground that holds when everything else feels uncertain.
+Teach us to rejoice not as those who have no difficulties, but as those who know where they stand.
+Where worry has crowded out joy, loosen its grip.
+Where the difficulty is real and the rejoicing feels impossible, meet us there — and let your peace, which we cannot manufacture for ourselves, guard what we cannot protect alone.
+Let what Paul found in a prison cell become real in us today.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Today, when you notice worry beginning to take hold — a problem turned over, a fear rehearsed — stop and name it before God plainly. 
+Then, before you return to it, find one thing in your immediate life to give thanks for. Not to cancel the worry out, but to place both things before God at the same time. 
+That is Paul's move: not pretending the difficulty away, but refusing to let it have the last word.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rejoicing is not the absence of worry. It is the decision not to let worry pray alone.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in the sixth week of Eastertide, three days from Pentecost.
+The season is almost complete — and as it closes, Vigil turns to the word that the whole arc of these fifty days has been quietly preparing the reader to receive.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalmist</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> does not ask to understand truth, or to be given truth as a possession. The request is simpler and stranger than that: lead me in it. As though truth were a path already laid out ahead — not something the Psalmist constructs by thinking hard enough, but something that requires a guide.
+That is a different relationship to truth than most of us default to. We tend to treat truth as a destination we arrive at through our own effort — research, argument, certainty accumulated over time. The Psalm imagines something less controlling and more trustworthy: truth as the territory God moves through, and the invitation to follow.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>What if the truths you have been trying hardest to work out are less in need of further effort, and more in need of a guide? The Psalmist does not ask to arrive — only to be moving in the right direction, with the right one leading.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You are the God whose truth holds and whose pathways are laid to guide us.
+Where we have strained after certainty, teach us to be led instead.
+Where we have clutched at answers, open our hands.
+Where we have mistaken our conclusions for your truth, correct us gently.
+Make us to know your ways, and teach us your paths — and let that be enough.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">At some point today, choose one thing you believe to be true — about God, about yourself, about someone you find difficult — and hold it lightly rather than tightly.
+Not to doubt it, but to ask: is this truth? 
+Does it hold because it is real, or because I have needed it to be?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Truth that can bear the weight of that question will still be standing at the end of the day.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Our Lady of Fatima.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Title given to the Virgin Mary following reported apparitions to three shepherd children — Lúcia dos Santos, Francisco Marto and Jacinta Marto — at Fátima, Portugal, between May and October 1917. The Church remembers her today; the memorial falls on this date because 13 May 1917 was the date of the first apparition, and the message carried there was, at its heart, a call to witness and to prayer in a world shaped by conflict.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Author · Psalm 25 (c. 10th century BC). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally attributed to King David, this is a psalm of petition written in an acrostic form — each verse beginning with a successive letter of the Hebrew alphabet — addressed to God in a time of personal distress and uncertainty. It is featured today because Psalm 25 gives the day's word its deepest register: not truth as argument or possession, but truth as a path into which the Psalmist asks to be led by God.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Make me to know your ways, O Lord;
+teach me your paths.
+Lead me in your truth, and teach me,
+for you are the God of my salvation;
+for you I wait all day long."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 25:4–5 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TRUTH [trooth]
+The word has been worn smooth by overuse. We reach for it in arguments, to win them. We invoke it to settle things.
+But in the Hebrew of the Old Testament, the word for truth is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>emet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (אֱמֶת) — and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>emet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> does not primarily mean factual accuracy. It comes from the root aman, meaning to be firm, to hold, to bear weight without giving way. Emet is what does not collapse under you. It is the quality of something you can lean on — not an argument to be won, but a ground to be stood on.
+The Greek word for truth, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>alētheia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ἀλήθεια), reaches for something slightly different but equally surprising: it means, literally, what is not hidden — what has been brought into the open and can be seen as it actually is.
+Put the two together and you have something worth sitting with. Truth, in scripture, is not something you possess or defeat someone else with. It is something you are led into — a territory more spacious than you expected, and more stable than anything you could have constructed for yourself.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">REJOICE [ri-joiss]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+In ordinary Greek, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>chairō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (χαίρω) carried the full warmth of the word: celebration, festivity, the mood that belongs to a wedding or a homecoming or good news just arrived. It is the word you use when something has gone well.
+Which is why </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> use of it is so disorienting. In his letter to the Philippians, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>chairō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> appears more often than in any other New Testament text — and </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> writes it from prison, to people facing persecution, with the instruction that it applies always. Not when things improve. Not when the fear lifts. Always.
+He says it once, and then — as if he knows the reader will assume he has overstated — he says it again.
+This is not a call to feel cheerful. It is a call to locate your joy somewhere that circumstances cannot reach: in the fact of God, the nearness of Christ, the ground that holds whether the news is good or not. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is not asking for something he has never tried. He is asking for it from inside a cell, which is the clearest possible evidence that he believes it can be done.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sts Nereus and Achilleus (1st–2nd century AD).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Early Christian martyrs, traditionally honoured as soldiers in the imperial Roman army who converted to Christianity and refused further military service. The Church remembers them today; their deaths give the day's word its sharpest edge — joy held not as mood but as conviction at the cost of everything.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">St Pancras (c. 289–304 AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">A young Christian martyr, put to death in Rome at approximately fourteen years of age during the persecution under Diocletian. The Church remembers him today; his youth and the sureness of his faith give the day's word a particular force — </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>chairō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> chosen before a life had fully begun.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">St Paul (1st century AD). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Apostle, missionary and author of letters central to the New Testament. He is featured today because his letter to the Philippians — written from prison — contains the New Testament's most concentrated and insistent use of chairō: rejoice always, and then (in case anyone missed it) rejoice again.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">COMFORT [kum-fert]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The word has grown soft in ordinary use. We reach for it when someone is sad and we want to say something kind. But comfort, in its full biblical register, is not softness at all.
+The Hebrew word at the heart of </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Isaiah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 40 is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>nacham</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (נָחַם) — to breathe again, to be brought back to breath. It is the word for someone crushed under a weight so heavy they can no longer draw air, and then relieved of it. 
+When the Jewish scholars who translated the Old Testament into Greek rendered this word, they chose </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>parakaleō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (παρακαλέω): to call someone to your side, to come in close, to strengthen from within. It is the root of the word </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>paraklētos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — the name Jesus gives the Holy Spirit that he will send after he is gone.
+Comfort, then, is not a gentle word spoken from across the room. It is the movement of God into the place where someone cannot breathe.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PEACE [pees]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">The English word barely carries what the original means.
+In the Greek of the New Testament, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>eirēnē</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (εἰρήνη) translates the Hebrew </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>shalom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (שָׁלוֹם) — and shalom is not the absence of conflict. It is a positive condition: wholeness, right relation, the settled flourishing of a life held in proper order before God and neighbour. To greet someone with shalom was not to wish them a quiet life. It was to wish them everything that makes life fully itself.
+When Jesus says "my peace I give to you," he is not offering tranquillity. He is offering participation in the deep order that holds all things — the peace that belongs to someone who knows, even in the darkest hours, that the outcome is not finally in doubt.</t>
     </r>
   </si>
 </sst>
@@ -3004,7 +3866,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3112,6 +3974,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3650,7 +4515,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
@@ -3917,7 +4782,7 @@
         <v>130</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3928,7 +4793,7 @@
         <v>133</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D10" s="25" t="s">
         <v>134</v>
@@ -3949,34 +4814,165 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="405" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="D11" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="25" t="s">
+      <c r="F11" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="G11" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="H11" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="I11" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="H11" s="24" t="s">
+    </row>
+    <row r="12" spans="1:9" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="I11" s="28" t="s">
+      <c r="B12" s="37" t="s">
         <v>151</v>
       </c>
+      <c r="C12" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="I14" s="28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="28"/>
+    </row>
+    <row r="16" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="28"/>
+    </row>
+    <row r="17" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="28"/>
+    </row>
+    <row r="18" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="22"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Vigil_Content_v2.0.xlsx
+++ b/Vigil_Content_v2.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicsmacbook/pCloud Drive/Personal/Vigil/Vigil v2/vigil-build/Vigil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FE3BB9-1C94-D847-9424-9CD0D97FFEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61972F28-3AE9-B346-90A2-1703A6A2CFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12020" yWindow="660" windowWidth="17320" windowHeight="18460" activeTab="1" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29340" windowHeight="18460" activeTab="1" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
   </bookViews>
   <sheets>
     <sheet name="April" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="233">
   <si>
     <t>Hover Links</t>
   </si>
@@ -2758,24 +2758,6 @@
   </si>
   <si>
     <t>CL-0513</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">13 May 2026
-Tuesday
-Eastertide · Week Six
-Optional Memorals: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Our Lady of Fatima</t>
-    </r>
   </si>
   <si>
     <r>
@@ -3613,12 +3595,1544 @@
 When Jesus says "my peace I give to you," he is not offering tranquillity. He is offering participation in the deep order that holds all things — the peace that belongs to someone who knows, even in the darkest hours, that the outcome is not finally in doubt.</t>
     </r>
   </si>
+  <si>
+    <t>CL-0514</t>
+  </si>
+  <si>
+    <t>CL-0515</t>
+  </si>
+  <si>
+    <t>CL-0516</t>
+  </si>
+  <si>
+    <t>14 May 2026
+Thursday
+Eastertide · Week Six
+Solemnity · The Ascension of the Lord</t>
+  </si>
+  <si>
+    <t>We are in Eastertide, and today the Church keeps the Solemnity of the Ascension — the fortieth day of the great fifty, when the risen Christ is taken up in glory and the disciples are left standing, looking upward, between what has been and what is coming.
+This is not an ending. It is the hinge on which everything turns.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>ASCEND [uh-SEND]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To ascend is not to disappear. It is to enter more fully into the place from which all things are governed.
+The Greek word used in Acts is analēmpsis (ἀνάλημψις) — a taking up, a receiving into — and what is received is not a ghost or a spirit, but a body: the same body that was broken and raised, now carried into the presence of God. 
+In the Psalms, ascent language belongs to worship — the pilgrim going up to Jerusalem, moving toward the place where heaven and earth meet. 
+The Ascension of Christ does not abolish that language. It fulfils it: the one who goes up is not leaving the world behind, but drawing it after him into God.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"God put this power to work in Christ when he raised him from the dead and seated him at his right hand in the heavenly places, far above all rule and authority and power and dominion, and above every name that is named, not only in this age but also in the age to come."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Ephesians 1:20–21 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Paul (1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Apostle, missionary and author of letters central to the New Testament. He is featured today because the Letter to the Ephesians gives the Ascension its most precise theological framing: not absence, but enthronement — Christ raised and seated above every power that claims authority over the world.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">There is a temptation, on the Ascension, to read it as loss — the one who was near becoming remote, the visible becoming invisible. The disciples standing on the hillside feel it. They are left looking at the sky.
+But </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> language in Ephesians does not describe distance. It describes authority: Christ seated at God's right hand, far above every power that competes for the governance of the world. The Ascension is not Christ retreating from history. It is Christ enthroned over it.
+That distinction matters for the ordinary life of faith. The one you pray to is not absent and sympathetic. He is present and sovereign — which is a different kind of comfort, and a more demanding one.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where have you been treating Christ as someone who has gone away and left you to manage, rather than as the one in whose hands everything already rests? If Christ is not absent but enthroned — governing, not withdrawn — what would you do differently today with that knowledge fully in view?</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You ascended not to leave us, but to reign over every power, every fear, every thing that seems to be in charge of our lives.
+Where we have behaved as though the world were unguided, remind us that you holds it in your arms.
+Where we have mistaken your hiddenness for absence, open our eyes.
+Let the same power that raised you from the dead be at work in us. Make us less afraid of what is coming, because we know where you are seated.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Choose one responsibility or anxiety you have been treating as the load you alone must carry. Not to put it down — it may be real and serious — but to carry it differently.
+Before you return to it today, look up — physically, deliberately — and name it before God. Say: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>I am not above this. But you are.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Then return to it — not as the person responsible for the outcome, but as someone working under a governance that holds even this.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>That is what it means to live after the Ascension.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">15 May 2026
+Friday
+Eastertide ·  Week Six
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Isidore the Farmer</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in the sixth week of Eastertide, the day after the Ascension — the season in its final stretch with Pentecost just one week away.
+Today the Church may remember </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Isidore the Farmer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, a labourer whose ordinary life became, across its length, an act of prayer.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">TEND [tend]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To tend is not to control. It is to give consistent, unglamorous attention to something that cannot grow by force.
+The Hebrew </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>shamar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (שָׁמַר) — to keep, to watch over, to guard — runs through the creation narratives and the psalms as the word for what is entrusted to human care.
+In Genesis, the human creature is placed in the garden not to possess it but to till and to keep it: to bring faithful attention to bear on something whose life is given, not made. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Isidore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> spent his working life doing precisely that, in a single field, over many years. He did not change the world. He tended it.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Isidore the Farmer (c. 1070–1130 AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Spanish agricultural labourer, canonised in 1622, patron saint of farmers and of Madrid. The Church remembers him today; his life gives the day's word its most concrete instance — faithfulness not as achievement but as daily, unglamorous tending of what has been given.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Author · Psalm 121 (c. 10th–6th century BC). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">One of the Songs of Ascent — psalms sung by pilgrims travelling up to Jerusalem for the great feasts. It is featured today because Psalm 121 gives the word </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>shamar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> its fullest devotional range: the God who tends his people with an attention that never fails.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"The Lord is your keeper;
+the Lord is your shade at your right hand.
+The sun shall not strike you by day,
+nor the moon by night.
+The Lord will keep you from all evil;
+he will keep your life.
+The Lord will keep
+your going out and your coming in
+from this time on and for evermore."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 121:5–8 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The same word — </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>shamar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, to tend or keep — belongs both to the human creature in the garden and to God watching over the pilgrim on the road. 
+That is not coincidence. It is the shape of the whole relationship: we are called to tend what we have been given because we ourselves are tended by one whose attention does not waver.
+Most of what we tend never makes news. A friendship kept alive by small regular acts of faithfulness. A habit of prayer returned to on the days when it costs something. A piece of work done carefully when no one is watching.
+St Isidore's life was not dramatic. But the tradition has remembered it for nine centuries, which is its own kind of testimony about what faithfulness looks like when you stay with it.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Some things in your life are tended; others are merely handled. The difference is not the size of the thing or the time you give it, but whether you are truly present to it. What is asking for your presence — not your efficiency — today?</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You are the keeper who does not sleep, present at our going out and our coming in.
+Teach us to tend what you have given us — not to impress, not to achieve, but because faithful attention is the shape love takes over time.
+Where we have neglected the small things in hope of larger ones, call us back.
+Where we have become weary of the unremarkable, let us find you there.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">At some point today, do one ordinary thing — make a drink, walk a familiar route, return a message you have been putting off — and do it slowly, as an act of deliberate attention rather than efficient completion.
+Before you begin, name it before God: this is what I am tending. I offer you my attention to it.
+The word </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>shamar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> does not mean doing more. It means being present to what you are already doing, as though it were worth your full care.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Tending is not a task to complete. It is a posture to practise.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">16 May 2026
+Saturday
+Eastertide · Week Six
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Simon Stock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in the sixth week of Eastertide, on the Saturday before Pentecost — the last full day of the great fifty, one threshold away from the coming of the Spirit.
+The Church may remember today </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Simon Stock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, who lived most of his life in waiting, and whose patience became a kind of prophecy.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>WAIT [wayt]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To wait is not to be passive. It is to hold yourself in readiness for something you cannot produce.
+The Hebrew </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>qavah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (קָוָה) — to wait, but also to hope, to stretch toward — carries a quality of active tension rather than passive endurance. The root image is of a cord drawn taut: something under pressure, straining in one direction, held firm by the expectation of what is coming. 
+In the Psalms, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>qavah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is the posture of the soul before God on the edge of dawn, through the darkest hours, believing that morning is coming before the sky shows any sign of it.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You ask us to wait — not as those who have been forgotten, but as those who know what is coming.
+Where our restlessness has mistaken activity for faithfulness, help us to be still.
+Where we have grown impatient with your timing, teach us the posture of those who watch for the morning.
+Hold us in readiness for what only you can give.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">At some point today, when you feel the pull to check, to plan, to move on to the next thing — pause instead. Physically stop. Let thirty seconds become a minute.
+In that pause, name before God one thing you have been trying to force into resolution. Do not pray for a solution. Simply hold it open, as a question rather than a problem, and say: I am waiting for you in this.
+The Psalmist who watched for the morning did not make the sun rise. He simply remained awake and oriented until it did.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>That is the whole practice: to remain awake, and to stay facing the right direction.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Simon Stock (c. 1165–1265 AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">English friar and prior general of the Carmelites, an order of religious life rooted in a tradition of solitary prayer and watchful waiting. The Church remembers him today; his life of contemplative perseverance gives the day's word its particular depth.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Author · Psalm 130 (c. 10th–6th century BC). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>One of the seven Penitential Psalms and one of the Songs of Ascent — a psalm of waiting from within distress. It is featured today because Psalm 130 gives qavah its most concentrated expression: not passive endurance, but active, tensed hope held through the dark.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"I wait for the Lord, my soul waits,
+and in his word I hope;
+my soul waits for the Lord
+more than those who watch for the morning,
+more than those who watch for the morning."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 130:5–6 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalmist</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> repeats the image — more than those who watch for the morning, more than those who watch for the morning — because saying it once is not enough. This is not a quick glance toward the horizon. It is a long watching, a posture held through the night.
+The disciples, in the days between the Ascension and the coming of the Spirit at Pentecost, are told to wait — not to go back to their old lives, not to manufacture what they need, but to remain and receive what is promised. 
+That waiting is not wasted time. It is the necessary form of a trust that cannot be forced.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Waiting feels unproductive because we measure time by what we make of it. But qavah — the stretched, taut waiting of the Psalmist — is not empty. It is oriented. Where are you being asked to stop producing and start receiving, and what would it cost you to trust that the waiting itself is the right response?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">13 May 2026
+Wednesday
+Eastertide · Week Six
+Optional Memorals: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Our Lady of Fatima</t>
+    </r>
+  </si>
+  <si>
+    <t>CL-0517</t>
+  </si>
+  <si>
+    <t>CL-0518</t>
+  </si>
+  <si>
+    <t>CL-0519</t>
+  </si>
+  <si>
+    <t>17 May 2026
+7th Sunday of Easter
+Eastertide · Week Seven</t>
+  </si>
+  <si>
+    <t>We are in Eastertide, on the Seventh Sunday of Easter — one week from Pentecost, the last Sunday of the great fifty days.
+Today, Vigil turns to a word that belongs to this threshold: a word that sounds like it refers to something distant and overwhelming, but turns out to describe something much closer to home.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"O Lord, our Sovereign, how majestic is your name in all the earth!
+When I look at your heavens, the work of your fingers,
+the moon and the stars that you have established;
+what are human beings that you are mindful of them,
+mortals that you care for them?
+Yet you have made them a little lower than God,
+and crowned them with glory and honour."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 8:1, 3–5 (NRSV)</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You made us to carry something of your weight in the world — and we have mostly forgotten this.
+Where we have made ourselves smaller than you made us, remind us.
+Where we have treated our own lives as unimportant, or the lives of others as disposable, correct us.
+Restore in us the dignity of people who bear your image — not as pride, but as responsibility.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Identify the one voice — a memory, a comparison, a habit of self-description — that most consistently persuades you that your life does not weigh very much.
+Every time you hear it today, answer it with the plain fact: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"I was made in the image of someone whose name is majestic in all the earth."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 
+That is not arrogance. It is accuracy.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Glory was not something you had to earn. It was given. The practice is learning to stop arguing with the gift.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Author · Psalm 8 (c. 10th century BC).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Traditionally attributed to King David, this is a psalm of praise addressed to God as Creator. It is featured today because it contains one of scripture's most surprising claims: that </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kabod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — the word for God's own weight and glory — belongs also to human beings, given by God before any achievement or merit.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>GLORY [GLAW-ree]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+In Hebrew, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kabod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (כָּבוֹד) comes from a root meaning weight — heaviness, substance, the quality of something that cannot be ignored or passed through. The </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kabod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> of God is not brightness as decoration. It is the felt reality of a presence too substantial for the world around it to simply absorb.
+When the writers of the Old Testament use </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kabod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> of human beings — and they do — something unexpected happens. A person of </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kabod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is not famous or impressive. They are real in a way that commands attention. The honour given to a parent, the weight a judge carries, the dignity of a life faithfully lived: these are </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kabod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> too. 
+The word does not belong only to the heavens. It belongs wherever something is genuinely what it is.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalmist</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> starts where most of us start: with the sky, and the sudden sense of smallness. The moon and the stars that you established. Beside all that, what are we?
+The expected answer is: not much. The actual answer is stranger than that.
+You have crowned them with glory and honour. The same word — </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kabod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — that belongs to the presence of God is given here to human beings. Not because they have earned it, but because this is what it means to be human: to carry something of that weight in the world.
+Most of us do not feel glorious. We feel tired, partial, smaller than we hoped. And yet the Psalmist will not let that feeling be the last word.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>When did you last feel the full weight of your own life — not your achievements or your failures, but simply the fact of being someone God made and has not stopped being mindful of? And what has been quietly convincing you, since then, that it was a mistake rather than the truest thing about you?</t>
+    </r>
+  </si>
+  <si>
+    <t>18 May 2026
+Monday
+Eastertide · Week Seven</t>
+  </si>
+  <si>
+    <t>We are in the seventh and final week of Eastertide, two days from Pentecost.
+The great fifty days are almost over. This week Vigil turns to a word that belongs to the threshold: what it means to come through something without being undone by it.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">OVERCOME [oh-ver-KUM]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Greek word is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>nikaō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (νικάω) — to conquer, to prevail, to pass through something and emerge on the other side still yourself. In the ancient world it belonged to the language of battle and contest: Nike, the goddess of victory, gave the word its most familiar face.
+But in the New Testament, nikaō migrates somewhere quieter. It describes not the person who was protected from difficulty, but the person who went through it and was not finally destroyed by it. The one who nikaō does not avoid the fight. They come out the other side.
+There is a compound form — </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hypernikaō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — that intensifies this further. Not merely to overcome, but to overcome beyond overcoming: to come through so completely that even the struggle has been made to serve something.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"Who will separate us from the love of Christ? Will hardship, or distress, or persecution, or famine, or nakedness, or peril, or sword? No, in all these things we are more than conquerors through him who loved us."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Romans</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 8:35, 37 (NRSV)</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You know what we are carrying — the hardship that is real, the fear that has made itself at home, the thing we have let write our conclusions for too long.
+We are not asking you to remove it. We are asking you to be more present in it than it is.
+Let the love that neither hardship nor peril can separate us from be more solid, today, than the weight of what presses against us.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">There is something in your life — you know what it is — that has been acting as though it has the final word. And there is almost certainly someone in your life carrying the same weight: the person who has gone quiet, the friend whose difficulty you have been meaning to acknowledge, the one for whom the hardship or distress or loss is very present today.
+Contact them. Not to fix anything. Not with a solution or a verse or an encouragement. Simply to say: I have been thinking of you, and I am not going anywhere.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>That is what it looks like to be, for one person, the evidence that love cannot be separated from them by what they are going through. Hypernikaō, enacted in an ordinary day.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Paul (1st century AD).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Apostle and author of letters central to the New Testament. He wrote the Letter to the Romans to a community facing a real danger of torture or execution for their faith, so when he lists hardships, he is not speaking in abstractions. He is featured today because Romans 8 gives the day's word its most searching expression: not that suffering is avoided, but that it cannot separate those who are loved by God from that love.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The word overcome doesn't appear in that passage. What appears instead is "more than conquerors" — and in the Greek, that is a single word: hypernikaō. The word we began with, pressed to its furthest point.
+In writing the Letter to the Romans, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> does not say the hardships listed go away. He names them plainly — hardship, distress, famine, peril, sword — because he is writing to people living under Roman rule, many of them from the poorest classes in society or even slaves, and many facing real danger for their faith. 
+So he is not offering comfort to people who might one day suffer. He is writing to people already in it, and saying: even so, none of this separates you from the love of God.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul's point is not that suffering must be extreme to count. It is that nothing — of any size, any kind — falls outside the reach of this love. What have you been carrying without bringing it to God, not because it felt too heavy, but because you were not sure it was worth his attention?</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Eastertide, on the eve of Pentecost — the last day of the great fifty, the threshold before the Spirit comes.
+Tomorrow the season ends and a new one begins. Today is a day for standing still before what is about to arrive.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">HOLY [HOH-lee]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Hebrew root is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>qadosh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (קָדוֹשׁ) — set apart, cut off from the ordinary, other than what surrounds it. In the Hebrew scriptures, the word first belongs to God alone: the sound of the one thing in existence that is wholly what it is, uncorrupted and unlike anything else.
+But </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>qadosh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> does not stay with God. It moves. The altar is holy because it is where God is approached. The day is holy because it is set aside for God. And in the New Testament, the people of God are holy — not because they have achieved moral perfection, but because they have been set apart: drawn into relation with the one who is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>qadosh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> in himself, and beginning, slowly, to be changed by that proximity.
+The Greek word for holy, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hagios</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ἅγιος), carries the same weight. The Holy Spirit is not only a spirit that is morally good. It is the Spirit who is other — who brings the presence of the utterly different into the ordinary life of the world. 
+And tomorrow, on Pentecost, that Spirit arrives.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"I saw the Lord sitting on a throne, high and lofty; and the hem of his robe filled the temple. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Seraphs</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> were in attendance above him; each had six wings: with two they covered their faces, and with two they covered their feet, and with two they flew. 
+And one called to another and said: 'Holy, holy, holy is the Lord of hosts; the whole earth is full of his glory.'"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Isaiah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 6:1b–3 (NRSV)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Isaiah (8th–7th century BC).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">A prophet of ancient Israel, writing at a time of political turmoil and moral crisis among God's people. He is featured today because the vision recorded at the opening of his prophetic calling — in which he sees God enthroned and the whole earth declared full of divine glory — gives the day's word its deepest register: holiness not as moral tidiness but as the overwhelming reality of God's presence breaking into ordinary life.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Seraphs.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Heavenly figures described in the vision of the prophet Isaiah as attendants around the throne of God. The Hebrew word saraph means burning one. They are depicted with six wings — two covering their faces before the divine presence, two covering their feet in reverence, and two for flight. They appear in this passage and nowhere else in the Hebrew scriptures.</t>
+    </r>
+  </si>
+  <si>
+    <t>19 May 2026
+Tuesday
+Eastertide · Week Seven
+Eve of Pentecost</t>
+  </si>
+  <si>
+    <t>Lord,
+You are holy — utterly unlike anything else, and yet present in the ordinary rooms and ordinary days of ordinary people.
+Tomorrow your Spirit arrives. Today we bring you what we are: distracted, incomplete, not as ready as we would like to be.
+We are not asking to be overwhelmed. We are asking to be open.
+Come, Holy Spirit, into the ordinary ground of this life. Find whatever room there is, and fill it.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Before the day is over, do one thing to make yourself genuinely available to what is coming — not by becoming more impressive or more prepared, but by removing something that has been filling the space.
+Identify one thing that has been occupying the room: a distraction returned to too often, a resentment kept close, a busyness that has crowded out quiet. Set it down deliberately before God today — not permanently, not with great drama, but as a single act of making space.
+The Holy Spirit does not wait for perfect conditions. But </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Isaiah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> was in the temple. The disciples were gathered and waiting. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Availability is not the same as worthiness. It is simply the decision to be present to what is already here.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Isaiah went to the temple to pray. He was not looking for what happened. And yet the utterly different — the one the seraphs cannot look at directly — filled the room he was standing in.
+That is what </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>qadosh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> does. It does not wait for the right conditions or the right person. It breaks through into ordinary life because ordinary life is already full of it, whether the people inside it know it or not.
+Tomorrow, on Pentecost, the Holy Spirit came upon the followers of Jesus — not in a grand public place but in a room, among ordinary people who did not fully know what they were waiting for.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>You are reading this in your own ordinary place, on the day before. Isaiah was not prepared. The disciples had been told to wait but did not know for what. Neither preparedness nor understanding was the condition. What would it mean, today, to simply make yourself present — and willing to be surprised?</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3674,6 +5188,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF3D4A5C"/>
+      <name val="Georgia"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -3987,8 +5515,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF3D4A5C"/>
       <color rgb="FFFFFDF5"/>
-      <color rgb="FF3D4A5C"/>
       <color rgb="FFF2EBE0"/>
       <color rgb="FF8C8680"/>
       <color rgb="FFFFFFFF"/>
@@ -4515,7 +6043,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
@@ -4782,7 +6310,7 @@
         <v>130</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4825,7 +6353,7 @@
         <v>143</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>145</v>
@@ -4851,25 +6379,25 @@
         <v>151</v>
       </c>
       <c r="C12" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E12" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="E12" s="26" t="s">
+      <c r="F12" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="G12" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="F12" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="G12" s="27" t="s">
+      <c r="H12" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="I12" s="28" t="s">
         <v>159</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4880,25 +6408,25 @@
         <v>153</v>
       </c>
       <c r="C13" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="F13" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="I13" s="28" t="s">
         <v>175</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4906,75 +6434,217 @@
         <v>154</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="C14" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="F14" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="F14" s="24" t="s">
+      <c r="G14" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="H14" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="I14" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="I14" s="28" t="s">
-        <v>172</v>
-      </c>
     </row>
-    <row r="15" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="22"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="28"/>
+    <row r="15" spans="1:9" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="I15" s="28" t="s">
+        <v>185</v>
+      </c>
     </row>
-    <row r="16" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="28"/>
+    <row r="16" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="I16" s="28" t="s">
+        <v>192</v>
+      </c>
     </row>
-    <row r="17" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="28"/>
+    <row r="17" spans="1:9" ht="374" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>202</v>
+      </c>
     </row>
-    <row r="18" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="22"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="28"/>
+    <row r="18" spans="1:9" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="I19" s="28" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="22"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="28"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="30" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/Vigil_Content_v2.0.xlsx
+++ b/Vigil_Content_v2.0.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicsmacbook/pCloud Drive/Personal/Vigil/Vigil v2/vigil-build/Vigil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61972F28-3AE9-B346-90A2-1703A6A2CFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6055D966-6C87-9143-96B1-BD63771C0194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29340" windowHeight="18460" activeTab="1" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
+    <workbookView xWindow="12000" yWindow="660" windowWidth="17400" windowHeight="18460" activeTab="1" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
   </bookViews>
   <sheets>
     <sheet name="April" sheetId="3" r:id="rId1"/>
     <sheet name="May" sheetId="2" r:id="rId2"/>
+    <sheet name="June" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">April!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">June!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">May!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="336">
   <si>
     <t>Hover Links</t>
   </si>
@@ -3173,72 +3175,6 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve"> 25:4–5 — NRSV</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TRUTH [trooth]
-The word has been worn smooth by overuse. We reach for it in arguments, to win them. We invoke it to settle things.
-But in the Hebrew of the Old Testament, the word for truth is </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>emet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (אֱמֶת) — and </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>emet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> does not primarily mean factual accuracy. It comes from the root aman, meaning to be firm, to hold, to bear weight without giving way. Emet is what does not collapse under you. It is the quality of something you can lean on — not an argument to be won, but a ground to be stood on.
-The Greek word for truth, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>alētheia</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (ἀλήθεια), reaches for something slightly different but equally surprising: it means, literally, what is not hidden — what has been brought into the open and can be seen as it actually is.
-Put the two together and you have something worth sitting with. Truth, in scripture, is not something you possess or defeat someone else with. It is something you are led into — a territory more spacious than you expected, and more stable than anything you could have constructed for yourself.</t>
     </r>
   </si>
   <si>
@@ -4186,43 +4122,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">St Simon Stock (c. 1165–1265 AD). 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">English friar and prior general of the Carmelites, an order of religious life rooted in a tradition of solitary prayer and watchful waiting. The Church remembers him today; his life of contemplative perseverance gives the day's word its particular depth.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Author · Psalm 130 (c. 10th–6th century BC). 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>One of the seven Penitential Psalms and one of the Songs of Ascent — a psalm of waiting from within distress. It is featured today because Psalm 130 gives qavah its most concentrated expression: not passive endurance, but active, tensed hope held through the dark.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <i/>
         <sz val="12"/>
@@ -4435,40 +4334,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Author · Psalm 8 (c. 10th century BC).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Traditionally attributed to King David, this is a psalm of praise addressed to God as Creator. It is featured today because it contains one of scripture's most surprising claims: that </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>kabod</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> — the word for God's own weight and glory — belongs also to human beings, given by God before any achievement or merit.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="12"/>
@@ -4647,10 +4512,6 @@
     <t>18 May 2026
 Monday
 Eastertide · Week Seven</t>
-  </si>
-  <si>
-    <t>We are in the seventh and final week of Eastertide, two days from Pentecost.
-The great fifty days are almost over. This week Vigil turns to a word that belongs to the threshold: what it means to come through something without being undone by it.</t>
   </si>
   <si>
     <r>
@@ -4833,112 +4694,6 @@
     </r>
   </si>
   <si>
-    <t>We are in Eastertide, on the eve of Pentecost — the last day of the great fifty, the threshold before the Spirit comes.
-Tomorrow the season ends and a new one begins. Today is a day for standing still before what is about to arrive.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">HOLY [HOH-lee]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-The Hebrew root is </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>qadosh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (קָדוֹשׁ) — set apart, cut off from the ordinary, other than what surrounds it. In the Hebrew scriptures, the word first belongs to God alone: the sound of the one thing in existence that is wholly what it is, uncorrupted and unlike anything else.
-But </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>qadosh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> does not stay with God. It moves. The altar is holy because it is where God is approached. The day is holy because it is set aside for God. And in the New Testament, the people of God are holy — not because they have achieved moral perfection, but because they have been set apart: drawn into relation with the one who is </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>qadosh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> in himself, and beginning, slowly, to be changed by that proximity.
-The Greek word for holy, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>hagios</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (ἅγιος), carries the same weight. The Holy Spirit is not only a spirit that is morally good. It is the Spirit who is other — who brings the presence of the utterly different into the ordinary life of the world. 
-And tomorrow, on Pentecost, that Spirit arrives.</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <i/>
@@ -5038,12 +4793,6 @@
       </rPr>
       <t>Heavenly figures described in the vision of the prophet Isaiah as attendants around the throne of God. The Hebrew word saraph means burning one. They are depicted with six wings — two covering their faces before the divine presence, two covering their feet in reverence, and two for flight. They appear in this passage and nowhere else in the Hebrew scriptures.</t>
     </r>
-  </si>
-  <si>
-    <t>19 May 2026
-Tuesday
-Eastertide · Week Seven
-Eve of Pentecost</t>
   </si>
   <si>
     <t>Lord,
@@ -5092,7 +4841,282 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Isaiah went to the temple to pray. He was not looking for what happened. And yet the utterly different — the one the seraphs cannot look at directly — filled the room he was standing in.
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>TRUTH [trooth]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The word has been worn smooth by overuse. We reach for it in arguments, to win them. We invoke it to settle things.
+But in the Hebrew of the Old Testament, the word for truth is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>emet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (אֱמֶת) — and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>emet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> does not primarily mean factual accuracy. It comes from the root aman, meaning to be firm, to hold, to bear weight without giving way. Emet is what does not collapse under you. It is the quality of something you can lean on — not an argument to be won, but a ground to be stood on.
+The Greek word for truth, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>alētheia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ἀλήθεια), reaches for something slightly different but equally surprising: it means, literally, what is not hidden — what has been brought into the open and can be seen as it actually is.
+Put the two together and you have something worth sitting with. Truth, in scripture, is not something you possess or defeat someone else with. It is something you are led into — a territory more spacious than you expected, and more stable than anything you could have constructed for yourself.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Psalmist · Psalm 8 (c. 10th century BC).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Traditionally attributed to King David, this is a psalm of praise addressed to God as Creator. It is featured today because it contains one of scripture's most surprising claims: that </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kabod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — the word for God's own weight and glory — belongs also to human beings, given by God before any achievement or merit.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Simon Stock (c. 1165–1265 AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">English friar and prior general of the Carmelites, an order of religious life rooted in a tradition of solitary prayer and watchful waiting. The Church remembers him today; his life of contemplative perseverance gives the day's word its particular depth.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Psalmist · Psalm 130 (c. 10th–6th century BC).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Psalms were composed by many hands across the centuries and the identity of most authors is unknown.  Psalm 130 is one of the Penitential Psalms and the Songs of Ascent. It is featured today because it gives qavah its most concentrated expression: not passive endurance, but active, tensed hope held through the dark.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in the seventh and final week of Eastertide, with less than a week until Pentecost.
+The great fifty days are almost over. This week Vigil turns to a word that belongs to the threshold: what it means to come through something without being undone by it.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">HOLY [HOH-lee]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Hebrew root is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>qadosh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (קָדוֹשׁ) and means that which is set apart, cut off from the ordinary, other than what surrounds it.  In the Hebrew scriptures, the word first belongs to God alone: the sound of the one thing in existence that is wholly what it is, uncorrupted and unlike anything else.
+But </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>qadosh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> does not stay with God. It moves. The altar is holy because it is where God is approached. The day is holy because it is set aside for God. And in the New Testament, the people of God are holy — not because they have achieved moral perfection, but because they have been set apart: drawn into relation with the one who is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>qadosh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> in himself, and beginning, slowly, to be changed by that proximity.
+The Greek word for holy, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hagios</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ἅγιος), carries the same weight. The Holy Spirit is not only a spirit that is morally good. It is the Spirit who is other — who brings the presence of the utterly different into the ordinary life of the world. 
+And tomorrow, on Pentecost, that Spirit arrives.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Isaiah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> went to the temple to pray. He was not looking for what happened. And yet the utterly different — the one the seraphs cannot look at directly — filled the room he was standing in.
 That is what </t>
     </r>
     <r>
@@ -5125,6 +5149,1688 @@
         <family val="1"/>
       </rPr>
       <t>You are reading this in your own ordinary place, on the day before. Isaiah was not prepared. The disciples had been told to wait but did not know for what. Neither preparedness nor understanding was the condition. What would it mean, today, to simply make yourself present — and willing to be surprised?</t>
+    </r>
+  </si>
+  <si>
+    <t>CL-0520</t>
+  </si>
+  <si>
+    <t>19 May 2026
+Tuesday
+Eastertide · Week Seven</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">20 May 2026
+Wednesday
+Eastertide · Week Seven
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Bernadine of Siena</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, priest</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"Therefore God also highly exalted him and gave him the name that is above every name, so that at the name of Jesus every knee should bend, in heaven and on earth and under the earth, and every tongue should confess that Jesus Christ is Lord, to the glory of God the Father."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Philippians 2:9–11 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAME [naym]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+In the ancient Greco-Roman world, a name was not simply a label. 
+Onoma (ὄνομα) — the Greek word </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> uses in his letter to the Philippians — carried the person's identity, authority and honour within it. To act in someone's name was to act with their full weight behind you. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> knew this, and he also knew something older behind it. In the Hebrew scriptures, shem (שֵׁם) — the word for name — carried the same concentrated sense. This is why the divine name is treated so carefully throughout scripture — not as a magic word, but as the concentrated reality of who God is. 
+When </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> writes of a name above every name, he is drawing on both registers at once: the Greek world his Philippian readers inhabited, and the Jewish inheritance that shaped everything he knew about God.
+The name above every name, in that light, is not a label promoted above others. It is the one name that carries the full weight of who Christ is — and what that weight can bear.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Most of us have inherited the name of Jesus as a given — something received so early and repeated so often that for many, it passes through the mouth without always passing through the mind.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> letter to the Philippians pushes back against that. The name he is writing about is not a formula. It carries the full weight of who Christ is — the presence, the authority and the capacity to act. A name, in the world Paul inhabited, was not a label attached from outside. It was the thing itself.
+A thousand years after </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Bernardine of Siena</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> spent thirty years travelling the length of Italy on foot, drawing crowds of thousands in town squares, and directing everything — every sermon, every journey — toward a single point: the name of Jesus as the centre of Christian life. Not a system. Not a theology to be mastered. A name to be returned to.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Where in your life has the name of Jesus become background noise? When did you last say it slowly, meaning it? And what do you find, or fail to find, when you bring it into the room with whatever you are carrying today?</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You gave to Christ the name that is above every name — and you gave it as a gift, not a title.
+Where we have said your name without thinking, teach us to say it again.
+Where your name has become familiar in the wrong way — worn smooth by habit, emptied by repetition — restore its weight.
+Let what we say with our mouths become what we carry in our lives.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">At some point today, say the name of Jesus — not in a prayer, not in a formula, but deliberately, as an act of attention. Say it once and hold it for a moment, as though you were handing something solid rather than sounding a noise.
+Bernardine believed that a name held up in silence could do more than an hour of eloquent speech. He may have been right.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The name is not a password. It is a presence.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Bernardine of Siena (1380–1444 AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Italian priest and member of the Franciscans — a Christian religious order committed to poverty, preaching and travelling ministry.  His entire ministry was built on the theology of the Holy Name of Jesus, which he promoted through the IHS monogram — the first three letters of Jesus' name in Greek — becoming the most celebrated itinerant preacher of fifteenth-century Italy.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">St Paul (1st century AD). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Apostle, missionary and author of letters central to the New Testament. He is featured today because the Christ-hymn in Philippians 2 gives the day's word its fullest register: the name above every name is not a title awarded to Jesus but the concentrated substance of who he is, given by God in response to a life of complete self-emptying.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in the seventh and final week of Eastertide, four days from Pentecost. 
+The great fifty days are almost complete, and as they close, many Christian traditions remember </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Bernardine of Siena</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — a Franciscan friar whose life was given, from beginning to end, to a single word: the name of Jesus.</t>
+    </r>
+  </si>
+  <si>
+    <t>CL-0521</t>
+  </si>
+  <si>
+    <t>CL-0522</t>
+  </si>
+  <si>
+    <t>CL-0523</t>
+  </si>
+  <si>
+    <t>CL-0524</t>
+  </si>
+  <si>
+    <t>CL-0525</t>
+  </si>
+  <si>
+    <t>CL-0526</t>
+  </si>
+  <si>
+    <t>CL-0527</t>
+  </si>
+  <si>
+    <t>CL-0528</t>
+  </si>
+  <si>
+    <t>CL-0529</t>
+  </si>
+  <si>
+    <t>CL-0530</t>
+  </si>
+  <si>
+    <t>CL-0531</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">21 May 2026
+Thursday
+Eastertide · Week Seven
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Christopher Magallanes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, priest, and companions, martyrs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">22 May 2026
+Friday
+Eastertide · Week Seven
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Rita of Cassia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, religious</t>
+    </r>
+  </si>
+  <si>
+    <t>23 May 2026
+Saturday
+Eastertide · Week Seven</t>
+  </si>
+  <si>
+    <t>28 May 2026
+Thursday
+Ordinary Time · Week One</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">27 May 2026
+Wednesday
+Ordinary Time · Week One
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Augustine of Canterbury</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, bishop</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">29 May 2026
+Friday
+Ordinary Time · Week One
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Paul VI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, pope</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">25 May 2026
+Monday
+Ordinary Time · Week One
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Blessed Virgin Mary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, Mother of the Church</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">30 May 2026
+Saturday
+Ordinary Time · Week One
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Blesssed Virgin Mary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> on Saturday</t>
+    </r>
+  </si>
+  <si>
+    <t>31 May 2026
+Sunday
+Ordinary Time · Week Two
+Solemnity: The Most Holy Trinity</t>
+  </si>
+  <si>
+    <t>24 May 2026
+Sunday
+Eastertide · Week Seven
+Solemnity: Pentecost</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">26 May 2026
+Tuesday
+Ordinary Time · Week One
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Philip Neri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, priest</t>
+    </r>
+  </si>
+  <si>
+    <t>CH-0601</t>
+  </si>
+  <si>
+    <t>CH-0602</t>
+  </si>
+  <si>
+    <t>CH-0603</t>
+  </si>
+  <si>
+    <t>CH-0604</t>
+  </si>
+  <si>
+    <t>CH-0605</t>
+  </si>
+  <si>
+    <t>CH-0606</t>
+  </si>
+  <si>
+    <t>CH-0607</t>
+  </si>
+  <si>
+    <t>CH-0608</t>
+  </si>
+  <si>
+    <t>CH-0609</t>
+  </si>
+  <si>
+    <t>CH-0610</t>
+  </si>
+  <si>
+    <t>CH-0611</t>
+  </si>
+  <si>
+    <t>CH-0612</t>
+  </si>
+  <si>
+    <t>CH-0613</t>
+  </si>
+  <si>
+    <t>CH-0614</t>
+  </si>
+  <si>
+    <t>CH-0615</t>
+  </si>
+  <si>
+    <t>CH-0616</t>
+  </si>
+  <si>
+    <t>CH-0617</t>
+  </si>
+  <si>
+    <t>CH-0618</t>
+  </si>
+  <si>
+    <t>CH-0619</t>
+  </si>
+  <si>
+    <t>CH-0620</t>
+  </si>
+  <si>
+    <t>CH-0621</t>
+  </si>
+  <si>
+    <t>CH-0622</t>
+  </si>
+  <si>
+    <t>CH-0623</t>
+  </si>
+  <si>
+    <t>CH-0624</t>
+  </si>
+  <si>
+    <t>CH-0625</t>
+  </si>
+  <si>
+    <t>CH-0626</t>
+  </si>
+  <si>
+    <t>CH-0627</t>
+  </si>
+  <si>
+    <t>CH-0628</t>
+  </si>
+  <si>
+    <t>CH-0629</t>
+  </si>
+  <si>
+    <t>CH-0630</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">02 June 2026
+Tuesday
+Ordinary Time · Week Two
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Marcellinus and St Peter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, martyrs</t>
+    </r>
+  </si>
+  <si>
+    <t>04 June 2026
+Thursday
+Ordinary Time · Week Two</t>
+  </si>
+  <si>
+    <t>07 June 2026
+Sunday
+Ordinary Time · Week Three
+Solemnity: The Most Sacred Heart of Jesus</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">03 June 2026
+Wednesday
+Ordinary Time · Week Two
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Charles Lwanga and companions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, martyrs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">05 June 2026
+Friday
+Ordinary Time · Week Two
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Boniface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, bishop and martyr</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">06 June 2026
+Saturday
+Ordinary Time · Week Two
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Norbert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, bishop
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Blessed Virgin Mary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> on Saturday</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">01 June 2026
+Monday
+Ordinary Time · Week Two
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Justin Martyr</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Eastertide, on the eve of Pentecost — the last few days of the great fifty, the threshold before the Spirit comes.
+Very soon, the season ends and a new one begins. Today is a day for standing still before what is about to arrive.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Forgiveness is easy to praise and difficult to practise, because practising it requires acknowledging that something real was done — that the wound was not imaginary and the wrong not minor. The temptation is to short-circuit this by moving quickly to the language of forgiveness without passing through the fact of injury.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> instruction in Colossians does not bypass the wound. It acknowledges a complaint — a real grievance between real people — and then asks something costly: to respond to it in the way God has responded to you.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Christopher Magallanes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> was arrested on false charges, given no trial and executed. His last recorded words were not a claim to justice, but an absolution: "I am innocent and die innocent. I absolve with all my heart those who seek my death and ask God that my blood bring peace to a divided Mexico." He did not pretend the wrong was not real. He released the claim anyway.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where have you been holding a complaint that has not yet become forgiveness — and what do you imagine it would cost you to let it go?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Christopher Magallanes (1869–1927).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mexican diocesan priest. The Church remembers him today with his twenty-four companions — priests and laymen killed during the Cristero War, a period of violent anti-Catholic persecution in Mexico. He was arrested while travelling to celebrate Mass on a farm, given no trial and executed. His last words were an act of forgiveness and a prayer for peace.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+St Paul (1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Apostle, missionary and author of letters central to the New Testament. He is featured today because his letter to the Colossians gives the day's word its most searching instruction: to forgive one another as the Lord has forgiven us — not as a counsel of naïve optimism, but as a response to a grace already received.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in the seventh and final week of Eastertide, three days before Pentecost.
+Today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Christopher Magallanes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and twenty-four companions, priests and laypeople who were killed in Mexico in the 1920s and who went to their deaths with forgiveness on their lips.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">FORGIVE [fer-GIV]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To forgive is not to pretend that the wrong did not happen. 
+It is to release the claim it has on you and to release your claim against the person who inflicted it.
+The Greek aphiēmi (ἀφίημι) means to send away, to let go, to release. In the New Testament it is used both for the forgiveness of sins and for the release of debts.
+The two meanings are not coincidental: the debt language speaks to a God who is owed something and chooses to cancel it; the sin language speaks to a God whose standard has been violated and who chooses not to prosecute — in both cases, the initiative of forgiveness is entirely God's.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You have forgiven more in us than we know how to name — without waiting for us to deserve it.
+Where we are carrying wounds we have not yet named to you, give us the honesty to speak them.
+Where we have been wronged, help us to let the forgiveness you have shown us become the forgiveness we offer in turn
+Give us the courage to release what we have been carrying, and the grace to carry it no longer.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">At some point today, write down — briefly, honestly — one grievance you have been holding: what was done, and by whom. Let the writing be as plain as possible, without drama.
+Then set the pen down, and say once: I forgive this. Not because the wrong was small, but because you are no longer willing to carry it. If the feeling does not follow immediately, that is normal. The act precedes the feeling.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The forgiveness that changes us usually begins before we feel ready to give it.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in the seventh and final week of Eastertide, two days from Pentecost.
+Today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Rita of Cascia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — a fifteenth-century nun whose long life became, in ways she could not have planned, an answer to a single question: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>what does it mean to follow?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>FOLLOW [FOL-oh]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To follow is to move in someone else's direction, at their pace, toward a destination they have chosen rather than you.
+The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>akolouthein</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ἀκολουθεῖν) is used throughout the New Testament almost exclusively for discipleship. It is not the word for walking behind someone in a crowd. It is the word for a deliberate reorientation of a life — giving up the right to set your own course and moving instead in the direction of another.
+What makes the word unusual is what it does not require. It does not require understanding the destination. It does not require feeling ready. In almost every instance where Jesus uses it in the Gospels, the person called to follow has no map, no guarantee and no particular preparation. They are simply asked whether they will go.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"Bear with one another and, if anyone has a complaint against another, forgive each other; just as the Lord has forgiven you, so you also must forgive."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Colossians 3:13 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You call us to follow you — not in the abstract, but from the actual circumstances of our lives.
+Where we have been dragging our feet, give us the grace to move.
+When we are afraid of where you are leading us, meet us with your presence.
+Teach us to trust that you know the road, even when we cannot see it.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Rita of Cascia (1381–1457). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Italian Augustinian nun. She is associated with impossible causes and with a life shaped, at every stage, by unchosen suffering which she came to embrace as a form of following Christ into his Passion. She bore a wound on her forehead — understood as a partial stigmata from Christ's Crown of Thorns — for the last fifteen years of her life.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+St Peter (1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally identified as one of the Twelve Apostles, a leading witness to the resurrection and as the author of two letters in the New Testament. He is featured today because the First Letter of Peter addresses communities facing persecution and suffering, and gives the day's word its clearest theological grounding: the call to follow Christ is not a call away from difficulty but into it, in His steps.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Identify one person in your life in whom you can see something of Christ — a patience, a steadiness, a quality of faith you recognise as real. 
+Reach out to them today in some form: a message, a call, a question. Let their direction become, for a moment, your direction.
+And if you find the openness to go further, you might ask them how they have learned to follow — what it has cost them, and what it has given them.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>We often learn to follow Christ by first learning to follow those in whom his life is visible.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Following, as the New Testament means it, is not the same as agreeing with someone's ideas. It requires a genuine reorientation — turning toward God, and moving in that direction even when the path is not the one you would have chosen.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Rita of Cascia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> wanted to give her life to God in one way. God led her through another: marriage, widowhood, years of refusal before she finally entered the convent. At each stage she had to choose, again, whether to follow God within the life she actually had — not the life she had planned.
+Rita's life was not what she expected. But at each stage, God was present in it — and accessible to her precisely because she stopped fighting the shape of it and began following within it.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where in your own life have you been waiting for better conditions before you follow — before you pray, before you trust, before you give God the part of your life you have been holding back? What would it mean to follow from exactly where you are now?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"For to this you have been called, because Christ also suffered for you, leaving you an example, so that you should follow in his steps."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+1 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Peter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2:21 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <t>We are at the end of the great fifty days. Eastertide closes today — one day before Pentecost, when the Church waits for what Christ promised before he left.
+The waiting is almost over.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Being open is harder than it sounds, because most of us are only selectively open — ready to receive the things we were already hoping for, and guarded against the rest.
+The disciples waiting before Pentecost had no clear picture of what was coming. They had been told to wait, and that something would arrive — but the shape of it was unknown. What the Spirit required of them before it came was not understanding, not preparation, and not worthiness. It required only that they stay in the room.
+There are parts of your life where you have been expecting God to act — and where, over time, the expectation may have hardened into a particular shape: the specific outcome, the particular answer, the change that would look exactly the way you imagined. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where might that expectation itself be the obstruction — and what would it mean, today, to release the shape of what you are waiting for, and simply remain open?</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You promised to send what your people needed, and you kept that promise.
+Where we have been waiting with clenched hands, open them.
+Where we have decided the shape of what you will give, help us to let that go.
+Where fear has made us guarded, make us available.
+We do not know what you are about to do. We are asking only to be open when you do it.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Before the day ends, choose one area of your life where you have been waiting for God to act — and where, honestly, you have already decided what the answer should look like.
+Hold that expectation for a moment. Then, deliberately, loosen your grip on it. Not in resignation, but in trust: the one who is coming knows better than you do what you need.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Openness is not passivity. It is the active decision to stop obstructing what God wants to give.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Paul (1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Apostle, missionary and author of letters central to the New Testament. He is featured today because the final verses of the Acts of the Apostles show him in Rome — under arrest, under guard — proclaiming the Kingdom of God with complete freedom and without hindrance. It is from his situation that the day's word takes its deepest meaning.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>OPEN [OH-pen]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To be open is not simply to be unlocked. It is to be without obstruction — available, undefended, ready to receive what comes.
+The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>akōlytōs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ἀκωλύτως) means unhindered, unimpeded, free from obstacle. In the final lines of the Acts of the Apostles, it is the word used to describe how </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> proclaimed the Kingdom of God in Rome for two years — not freely in the sense of being unguarded, but freely in the sense of being unblocked, the message moving without restraint from a man under house arrest.
+There is something striking in that. The obstruction was still there — the chains, the soldier, the appeal to Caesar — and yet the word that closes the whole account of the early Church is this one: unhindered. What was open was not the door, but the proclamation that went through it.
+On the last day before Pentecost, the question the word puts to the reader is not whether the way ahead is clear. It is whether you are open to what God is about to do.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"He lived there for two full years at his own expense and welcomed all who came to him, proclaiming the kingdom of God and teaching about the Lord Jesus Christ with all boldness and without hindrance."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Acts 28:30–31 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <t>Eastertide ends today. 
+The great fifty days — which began at Easter and have carried the Church through resurrection, ascension and expectation — reach their completion in the feast of Pentecost.
+This is the day the Spirit came.</t>
+  </si>
+  <si>
+    <t>Lord,
+You did not leave your people to manage alone. You promised the Spirit, and you sent the Spirit, and the Spirit has not been withdrawn.
+Where we have been trying to live the Christian life on our own resources, remind us what you gave us.
+Where we have grown tired, breathe.
+Where we have grown cold, kindle.
+Where we have grown silent, speak through us in ways we could not have found ourselves.
+Come, Holy Spirit.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">What arrived at Pentecost did not arrive quietly. It arrived as wind and fire — disruptive, unmistakable, impossible to ignore. The disciples in that room had been waiting, praying and keeping still. They had done everything that could be done from the human side.
+And then something happened that they could not have produced by their own waiting.
+That is the character of the Spirit throughout scripture: it is not generated, it is received. It comes from outside the system. It does not reward effort in the way that effort normally expects to be rewarded. It comes when and how it will — which is not an argument against preparation, but an argument against the assumption that preparation is what causes the arrival.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where in your life have you been trying to generate what can only be received — working to produce a quality of faith, peace or love that is, in the end, a gift? 
+And what would it mean to stop producing and simply become the kind of person through whom the Spirit can move?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>SPIRIT [SPIR-it]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+In the original languages of scripture, the word for spirit carries more than one meaning at once — and that is not an accident.
+The Hebrew </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>ruach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (רוּחַ) means wind, breath and spirit. The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>pneuma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (πνεῦμα) carries the same range. In both cases, what the word holds together is the movement of an invisible force that is known not by being seen but by what it does: the breath that animates a body, the wind that bends the trees, the spirit that moves through and beyond what is merely physical.
+This is why, when the Spirit arrives at Pentecost, it arrives as wind and fire — not as metaphors added afterward to explain something, but as the thing itself in its most recognisable forms. The word was never only spiritual in the modern, ethereal sense. It was always also breath. Always also force.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"When the day of Pentecost had come, they were all together in one place. 
+And suddenly from heaven there came a sound like the rush of a violent wind, and it filled the entire house where they were sitting. 
+Divided tongues, as of fire, appeared among them, and a tongue rested on each of them. 
+All of them were filled with the Holy Spirit and began to speak in other languages, as the Spirit gave them ability."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Acts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2:1–4 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Choose one thing today that you have been trying to do in your own strength — a conversation you have been dreading, a habit you have been fighting, a relationship you have been managing — and before you face it, pause and ask the Spirit to go with you into it.
+Not a long prayer. A single breath, and the simplest of requests:
+Come, Holy Spirit.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Veni, Sancte Spiritus.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Spirit does not need elaborate invitation. It needs only the door to be open.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are at the start of Ordinary Time — the first Monday after Pentecost, and the first weekday of a new season.
+Ordinary Time is not a diminishment. It is the season in which what was given at Easter and Pentecost is carried into the whole ordinary length of a life. 
+The Church begins it today by remembering Mary — present at the Annunciation, present at the cross, and present in the Upper Room when the Spirit came. She is the one figure who stands at every threshold of the story, and the Church calls her its mother.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">MOTHERHOOD [MU-thər-hud]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The word comes from the Old English modor — one who carries, tends and forms — and it has always meant more than biological origin. A mother is the one in whose care something comes to be itself.
+The Church's claim that Mary is its mother rests on a specific observation: she was there. At the Annunciation, she received the Word before anyone else. And in the days between the Ascension and Pentecost, she was in the Upper Room with the apostles, praying with them as they waited for the Spirit who would bring the Church to life.
+Acts places her there in a single, quiet phrase — Mary the mother of Jesus — among the disciples, at prayer, before everything began. She is not leading. She is not speaking. She is present, and she is praying. 
+The Church has understood that as a form of motherhood: not the motherhood of authority, but of faithful, sustaining presence at the moment of birth.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"All these were constantly devoting themselves to prayer, together with certain women, including Mary the mother of Jesus, as well as his brothers."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Acts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 1:14 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mary carried Christ — literally, bodily — and then spent the rest of her life releasing him: to his ministry, to the disciples, to the cross, to the Church.
+Motherhood, in her case, was inseparable from the willingness to let go of what she had carried.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>What are you holding onto that belongs, now, in someone else's hands? Identify it. Then find one concrete act today that begins the transfer.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The description in Acts is almost aggressively ordinary. 
+Mary, identified only by her relationship to Jesus, is doing what everyone else is doing. But she had already lived through the Annunciation, the cross, and everything in-between, and she knew something about carrying that the others were only beginning to learn.
+That is what Luke's account of her shows, from beginning to end: a life shaped by receiving something not asked for, carrying it at cost, and releasing it when the time came. 
+At the Annunciation she received. At the cross she held on. In the Upper Room she let the Church be born from what she had carried.
+Motherhood, in this sense, is not possession. It is the willingness to carry something fully and then to release it into the world rather than keep it for yourself.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>What have you been carrying — a person, a responsibility, a vision for someone else's life — that may now be asking to be released rather than held?</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You gave your Church a mother who knew how to carry and how to release.
+Where we have confused holding on with faithfulness, show us the difference.
+Where we have carried something that was never ours to keep — a person, a hope, a vision for someone else's life — give us the courage to open our hands.
+Let what we have carried with love be released with love, as she did.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Author · Acts of the Apostles (1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF0E0D0"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally identified as Luke, a physician and companion of St Paul, and as the author of both the synonymous Gospel and the Acts of the Apostles. He is featured today because the opening of Acts 2 is his account of the Spirit's arrival at Pentecost — the event that closes Eastertide and opens the life of the Church.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Author · Acts of the Apostles (1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally identified as Luke, a physician and companion of St Paul, and as the author of both the synonymous Gospel and the Acts of the Apostles. He is featured today because it is in Acts 1 that Mary appears for the last time in the New Testament, as the Church waits for the Spirit that will bring it to life.</t>
     </r>
   </si>
 </sst>
@@ -5132,7 +6838,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5203,8 +6909,42 @@
       <name val="Georgia"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFF0E0D0"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FFF0E0D0"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFF0E0D0"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFF0E0D0"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFF0E0D0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5244,6 +6984,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFDF5"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC04040"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC04040"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -5394,7 +7146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -5507,6 +7259,27 @@
     <xf numFmtId="15" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5515,6 +7288,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF0E0D0"/>
+      <color rgb="FFC04040"/>
       <color rgb="FF3D4A5C"/>
       <color rgb="FFFFFDF5"/>
       <color rgb="FFF2EBE0"/>
@@ -6043,7 +7818,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
@@ -6353,7 +8128,7 @@
         <v>143</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>145</v>
@@ -6382,7 +8157,7 @@
         <v>156</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>157</v>
@@ -6411,7 +8186,7 @@
         <v>162</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>163</v>
@@ -6426,7 +8201,7 @@
         <v>166</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6434,13 +8209,13 @@
         <v>154</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>167</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>172</v>
@@ -6460,180 +8235,757 @@
     </row>
     <row r="15" spans="1:9" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B15" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="D15" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="F15" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="I15" s="28" t="s">
         <v>184</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="G15" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B16" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="D16" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="I16" s="28" t="s">
         <v>191</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="374" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B17" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="D17" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="E17" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="G17" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="E17" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="F17" s="24" t="s">
+      <c r="H17" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="G17" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>202</v>
+      <c r="B18" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>226</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="24" t="s">
+    <row r="19" spans="1:9" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="E18" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="F18" s="24" t="s">
+      <c r="E19" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="G18" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="I18" s="28" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="37" t="s">
+      <c r="F19" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="G19" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="H19" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="I19" s="28" t="s">
         <v>219</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>224</v>
-      </c>
-      <c r="G19" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="I19" s="28" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B20" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="D20" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="C20" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>226</v>
-      </c>
       <c r="E20" s="24" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G20" s="27" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H20" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="I20" s="28" t="s">
-        <v>228</v>
+      <c r="B21" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>239</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
+    <row r="22" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="I22" s="28" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>320</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="44" customFormat="1" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>322</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="G25" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="I25" s="43" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>333</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="28"/>
+    </row>
+    <row r="28" spans="1:9" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="B28" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="28"/>
+    </row>
+    <row r="29" spans="1:9" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="28"/>
+    </row>
+    <row r="30" spans="1:9" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="28"/>
+    </row>
+    <row r="31" spans="1:9" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="28"/>
+    </row>
+    <row r="32" spans="1:9" ht="86" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="28"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="30" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C755C3-D0F0-E142-815A-4D8AA9E2C63B}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="10"/>
+    <col min="2" max="2" width="40.83203125" style="2" customWidth="1"/>
+    <col min="3" max="9" width="50.83203125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="3" customFormat="1" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="4" customFormat="1" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>299</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="14"/>
+    </row>
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="14"/>
+    </row>
+    <row r="4" spans="1:9" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+    </row>
+    <row r="5" spans="1:9" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="14"/>
+    </row>
+    <row r="6" spans="1:9" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:9" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="28"/>
+    </row>
+    <row r="8" spans="1:9" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="28"/>
+    </row>
+    <row r="9" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="23"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="28"/>
+    </row>
+    <row r="10" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="28"/>
+    </row>
+    <row r="11" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="28"/>
+    </row>
+    <row r="12" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="B12" s="37"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="28"/>
+    </row>
+    <row r="13" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="B13" s="37"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="28"/>
+    </row>
+    <row r="14" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B14" s="37"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="28"/>
+    </row>
+    <row r="15" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="B15" s="37"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="28"/>
+    </row>
+    <row r="16" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B16" s="37"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="28"/>
+    </row>
+    <row r="17" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="B17" s="37"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="28"/>
+    </row>
+    <row r="18" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B18" s="23"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="28"/>
+    </row>
+    <row r="19" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="B19" s="37"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="28"/>
+    </row>
+    <row r="20" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" s="37"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="28"/>
+    </row>
+    <row r="21" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>282</v>
+      </c>
       <c r="B21" s="37"/>
       <c r="C21" s="24"/>
       <c r="D21" s="24"/>
@@ -6643,6 +8995,137 @@
       <c r="H21" s="24"/>
       <c r="I21" s="28"/>
     </row>
+    <row r="22" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="B22" s="37"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="28"/>
+    </row>
+    <row r="23" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="B23" s="37"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="28"/>
+    </row>
+    <row r="24" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="B24" s="37"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="28"/>
+    </row>
+    <row r="25" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="B25" s="23"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="28"/>
+    </row>
+    <row r="26" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="B26" s="37"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="28"/>
+    </row>
+    <row r="27" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="B27" s="37"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="28"/>
+    </row>
+    <row r="28" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="B28" s="37"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="28"/>
+    </row>
+    <row r="29" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="B29" s="37"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="28"/>
+    </row>
+    <row r="30" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="B30" s="37"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="28"/>
+    </row>
+    <row r="31" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="B31" s="37"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="28"/>
+    </row>
+    <row r="32" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Vigil_Content_v2.0.xlsx
+++ b/Vigil_Content_v2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicsmacbook/pCloud Drive/Personal/Vigil/Vigil v2/vigil-build/Vigil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6055D966-6C87-9143-96B1-BD63771C0194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419CC4D7-A394-B042-A420-B60E1FA498FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12000" yWindow="660" windowWidth="17400" windowHeight="18460" activeTab="1" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="26880" windowHeight="18460" activeTab="1" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
   </bookViews>
   <sheets>
     <sheet name="April" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">June!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">May!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="347">
   <si>
     <t>Hover Links</t>
   </si>
@@ -5607,33 +5607,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">25 May 2026
-Monday
-Ordinary Time · Week One
-Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>The Blessed Virgin Mary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, Mother of the Church</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">30 May 2026
 Saturday
 Ordinary Time · Week One
@@ -5819,12 +5792,6 @@
     <t>04 June 2026
 Thursday
 Ordinary Time · Week Two</t>
-  </si>
-  <si>
-    <t>07 June 2026
-Sunday
-Ordinary Time · Week Three
-Solemnity: The Most Sacred Heart of Jesus</t>
   </si>
   <si>
     <r>
@@ -6820,6 +6787,358 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>CHEERFUL [CHEER-ful]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Greek word is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hilaros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ἱλαρός) — and it is the root of the English word "hilarity." That connection is worth pausing on.
+Hilaros does not mean politely pleasant. It means radiantly, freely glad — the gladness of someone who has nothing left to protect. 
+When </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> uses it, as we shall see in today's scripture, he uses it to describe a quality of giving: not the giving of someone discharging an obligation, but of someone who gives because they are genuinely free to.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Philip Neri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> spent decades in Rome doing exactly that — drawing people to God through prayer, music and long hours of conversation, with a quality of hilaritas that his contemporaries found disarming and, in the best sense, inexplicable. He did not perform joy. He had discovered the freedom that produces it.
+Cheerfulness, in this sense, is not a mood. It is the outward sign of an inward liberty.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">The point is this: the one who sows sparingly will also reap sparingly, and the one who sows bountifully will also reap bountifully. 
+Each of you must give as you have made up your mind, not reluctantly or under compulsion, for God loves a cheerful giver.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+2 Corinthians 9:6–7 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You love a cheerful giver — not because you need our gifts, but because the freedom to give freely is itself a form of knowing you.
+Where we have given under compulsion — from duty, guilt or the fear of what others will think — forgive us.
+Where we have become calculating with our time, our kindness, our attention: loosen the grip.
+Make us free enough to be generous — not by removing what it costs, but by drawing us close enough to you that the cost no longer has the last word.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are at the start of Ordinary Time, on the Tuesday after Pentecost.
+Today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Philip Neri,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> a sixteenth-century priest who made holiness so attractive that people came looking for it.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Philip Neri (1515–1595 AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Italian priest and founder of the Congregation of the Oratory in Rome. The Church remembers him today; his life gave the word </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hilaritas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> its most sustained theological expression — a holiness so free and so glad that people came from across the city to be near it.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+St Paul (1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apostle, missionary and author of letters central to the New Testament. He is featured today because his second letter to the Corinthians gives the day's word its precise scriptural ground: the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hilaros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>-giver is not someone who has mastered generosity, but someone who has been freed from the compulsion not to give.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Most of us know the difference between giving that is free and giving that is not. The free kind — the meal made with genuine pleasure, the time offered without calculating what it costs — feels different to the person receiving it. They can tell. And so can you.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Philip Neri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> drew people to God not by argument but by the quality of his attention. What they described, centuries later, was something close to delight: the sense that he was genuinely glad they were there.
+There is probably one person in your life it is easy to be generous toward — and one for whom the giving has quietly become a calculation. The difference rarely lies in what they deserve. It usually lies in something in you.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>What has made generosity toward that second person feel like expenditure rather than freedom — and what would change if you brought that tightness to God before you returned to the relationship?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Philip Neri's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>cheefulness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> had a very specific shape: he was never somewhere else. Not managing the conversation, not calculating what the other person was costing him, not half-present while protecting his time. His attention was the form his freedom took.
+Choose one person you will encounter today — in person, by message, or by phone. Decide now to give them your full attention when that moment comes.
+When it arrives, stop composing your reply while they are still speaking or typing. Be entirely there.
+Notice what happens in you as you do it. If it feels like freedom — easy, unguarded, genuinely glad — that is cheefulness. 
+If it feels like effort or cost, that is not a failure. That is the place to pray from: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Lord, this is where my grip is still tight. Please loosen it. Help me to become your cheerful servant.</t>
+    </r>
+  </si>
+  <si>
+    <t>Red Major</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>07 June 2026
+Sunday
+Ordinary Time · Week Three
+Solemnity: Corpus Christi</t>
+  </si>
+  <si>
+    <t>Palette</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">25 May 2026
+Monday
+Ordinary Time · Week One
+Memorial: The Blessed Virgin Mary, Mother of the Church
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St. Bede the Venerable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, priest and Doctor of the Church</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Author · Acts of the Apostles (1st century AD). 
 </t>
     </r>
@@ -6831,6 +7150,27 @@
         <family val="1"/>
       </rPr>
       <t>Traditionally identified as Luke, a physician and companion of St Paul, and as the author of both the synonymous Gospel and the Acts of the Apostles. He is featured today because it is in Acts 1 that Mary appears for the last time in the New Testament, as the Church waits for the Spirit that will bring it to life.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Bede the Venerable [c. 673–735]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>An Anglo-Saxon monk, scholar and historian. The Church remembers him as one of the first and greatest interpreters of scripture in the Latin West — a man who spent almost his entire life within a few miles of the Benedictine monastery in Northumbria (northern England) where he was placed as a child.</t>
     </r>
   </si>
 </sst>
@@ -6999,7 +7339,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -7142,11 +7482,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -7279,6 +7658,24 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7596,220 +7993,230 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
-    <col min="2" max="2" width="40.83203125" style="2" customWidth="1"/>
-    <col min="3" max="9" width="50.83203125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="40.83203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" style="2" customWidth="1"/>
+    <col min="4" max="10" width="50.83203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="45" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="4" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="4" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="J2" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="J3" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
     </row>
-    <row r="5" spans="1:9" ht="290" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="290" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="D5" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="E5" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="F5" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="G5" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="H5" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="I5" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="J5" s="28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="273" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="273" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="49"/>
+      <c r="C6" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="J6" s="15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="D7" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="E7" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="F7" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="G7" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="H7" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="I7" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="I7" s="35" t="s">
+      <c r="J7" s="35" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="31" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="30" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -7818,863 +8225,928 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
-    <col min="2" max="2" width="40.83203125" style="2" customWidth="1"/>
-    <col min="3" max="9" width="50.83203125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="40.83203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" style="2" customWidth="1"/>
+    <col min="4" max="10" width="50.83203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="45" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="4" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="4" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="J2" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="J3" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="5" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="J4" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="J5" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="374" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="374" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="47"/>
+      <c r="C6" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="D6" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="E6" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F6" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="G6" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="H6" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="I6" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="J6" s="28" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="47"/>
+      <c r="C7" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="D7" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="E7" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="F7" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="G7" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="H7" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="I7" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="J7" s="28" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="374" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="374" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="47"/>
+      <c r="C8" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="D8" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="E8" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="F8" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="G8" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="H8" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="I8" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="J8" s="28" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="47"/>
+      <c r="C9" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="D9" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="E9" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="F9" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="G9" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="H9" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="I9" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="I9" s="28" t="s">
+      <c r="J9" s="28" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="47"/>
+      <c r="C10" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="D10" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="E10" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="F10" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="G10" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="H10" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="I10" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="J10" s="28" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="47"/>
+      <c r="C11" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="D11" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="E11" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="F11" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="G11" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="H11" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="I11" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I11" s="28" t="s">
+      <c r="J11" s="28" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="47"/>
+      <c r="C12" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="D12" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="E12" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="F12" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="G12" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="H12" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="I12" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="J12" s="28" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="47"/>
+      <c r="C13" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="D13" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="E13" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="F13" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="G13" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="H13" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="I13" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="I13" s="28" t="s">
+      <c r="J13" s="28" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="47"/>
+      <c r="C14" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="D14" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="E14" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="F14" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="G14" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="H14" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="I14" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="J14" s="28" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="47"/>
+      <c r="C15" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="D15" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="E15" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="F15" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="G15" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="H15" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="H15" s="24" t="s">
+      <c r="I15" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="J15" s="28" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="47"/>
+      <c r="C16" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="D16" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="F16" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="G16" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="H16" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="I16" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="J16" s="28" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="374" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="374" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="47"/>
+      <c r="C17" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="D17" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="E17" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="F17" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="G17" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="H17" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="I17" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="I17" s="28" t="s">
+      <c r="J17" s="28" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="47"/>
+      <c r="C18" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="D18" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="E18" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="F18" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="G18" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="H18" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="I18" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="I18" s="28" t="s">
+      <c r="J18" s="28" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="47"/>
+      <c r="C19" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="D19" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="E19" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="F19" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="G19" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="H19" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="H19" s="24" t="s">
+      <c r="I19" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="I19" s="28" t="s">
+      <c r="J19" s="28" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="47"/>
+      <c r="C20" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="C20" s="24" t="s">
-        <v>300</v>
-      </c>
       <c r="D20" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="E20" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="F20" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="G20" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="H20" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="H20" s="24" t="s">
+      <c r="I20" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="J20" s="28" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="47"/>
+      <c r="C21" s="37" t="s">
         <v>233</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="D21" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="E21" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="F21" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="G21" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="G21" s="27" t="s">
+      <c r="H21" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="I21" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="I21" s="28" t="s">
+      <c r="J21" s="28" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="47"/>
+      <c r="C22" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="D22" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="H22" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="I22" s="24" t="s">
         <v>304</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="I22" s="28" t="s">
-        <v>302</v>
+      <c r="J22" s="28" t="s">
+        <v>300</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="47"/>
+      <c r="C23" s="37" t="s">
         <v>253</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>307</v>
-      </c>
       <c r="D23" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="H23" s="27" t="s">
         <v>308</v>
       </c>
-      <c r="E23" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="G23" s="27" t="s">
+      <c r="I23" s="24" t="s">
         <v>310</v>
       </c>
-      <c r="H23" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="I23" s="28" t="s">
-        <v>311</v>
+      <c r="J23" s="28" t="s">
+        <v>309</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="47"/>
+      <c r="C24" s="37" t="s">
         <v>254</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="D24" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="H24" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="D24" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="F24" s="24" t="s">
+      <c r="I24" s="24" t="s">
         <v>316</v>
       </c>
-      <c r="G24" s="27" t="s">
+      <c r="J24" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="H24" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="I24" s="28" t="s">
-        <v>319</v>
-      </c>
     </row>
-    <row r="25" spans="1:9" s="44" customFormat="1" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="44" customFormat="1" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="B25" s="40" t="s">
-        <v>261</v>
-      </c>
-      <c r="C25" s="38" t="s">
+      <c r="B25" s="48" t="s">
+        <v>340</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>260</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="G25" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="H25" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="I25" s="38" t="s">
         <v>325</v>
       </c>
-      <c r="E25" s="41" t="s">
-        <v>326</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>324</v>
-      </c>
-      <c r="G25" s="42" t="s">
-        <v>323</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>327</v>
-      </c>
-      <c r="I25" s="43" t="s">
-        <v>334</v>
+      <c r="J25" s="43" t="s">
+        <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="B26" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="C26" s="24" t="s">
+      <c r="B26" s="47" t="s">
+        <v>341</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>345</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="F26" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="G26" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>331</v>
+      </c>
+      <c r="I26" s="24" t="s">
         <v>329</v>
       </c>
-      <c r="E26" s="26" t="s">
-        <v>330</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>332</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>333</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="I26" s="28" t="s">
-        <v>335</v>
+      <c r="J26" s="28" t="s">
+        <v>346</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="B27" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="28"/>
+      <c r="B27" s="47" t="s">
+        <v>341</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>338</v>
+      </c>
+      <c r="H27" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>337</v>
+      </c>
     </row>
-    <row r="28" spans="1:9" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="47" t="s">
+        <v>341</v>
+      </c>
+      <c r="C28" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="C28" s="24"/>
       <c r="D28" s="24"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="28"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="28"/>
     </row>
-    <row r="29" spans="1:9" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="47" t="s">
+        <v>342</v>
+      </c>
+      <c r="C29" s="37" t="s">
         <v>255</v>
       </c>
-      <c r="C29" s="24"/>
       <c r="D29" s="24"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="28"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="28"/>
     </row>
-    <row r="30" spans="1:9" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="47" t="s">
+        <v>342</v>
+      </c>
+      <c r="C30" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="C30" s="24"/>
       <c r="D30" s="24"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="28"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="28"/>
     </row>
-    <row r="31" spans="1:9" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="B31" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="C31" s="24"/>
+      <c r="B31" s="47" t="s">
+        <v>342</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>258</v>
+      </c>
       <c r="D31" s="24"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="28"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="28"/>
     </row>
-    <row r="32" spans="1:9" ht="86" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="86" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A32" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="B32" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="C32" s="24"/>
+      <c r="B32" s="47" t="s">
+        <v>341</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>259</v>
+      </c>
       <c r="D32" s="24"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="28"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="28"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="30" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="27" fitToHeight="8" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -8683,452 +9155,546 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
-    <col min="2" max="2" width="40.83203125" style="2" customWidth="1"/>
-    <col min="3" max="9" width="50.83203125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="40.83203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" style="2" customWidth="1"/>
+    <col min="4" max="10" width="50.83203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="45" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="4" customFormat="1" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="4" customFormat="1" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>299</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="14"/>
+      <c r="B3" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="14"/>
     </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+    <row r="4" spans="1:10" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B4" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="14"/>
+    </row>
+    <row r="5" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="14"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="14"/>
     </row>
-    <row r="4" spans="1:9" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="B4" s="6" t="s">
+    <row r="6" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="28"/>
+    </row>
+    <row r="7" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="14"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="28"/>
     </row>
-    <row r="5" spans="1:9" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="14"/>
+    <row r="8" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="28"/>
     </row>
-    <row r="6" spans="1:9" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="28"/>
+    <row r="9" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" s="23"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="28"/>
     </row>
-    <row r="7" spans="1:9" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="28"/>
+    <row r="10" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="28"/>
     </row>
-    <row r="8" spans="1:9" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="28"/>
+    <row r="11" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="28"/>
     </row>
-    <row r="9" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="28"/>
+    <row r="12" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="C12" s="37"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="28"/>
     </row>
-    <row r="10" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="28"/>
+    <row r="13" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C13" s="37"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="28"/>
     </row>
-    <row r="11" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="28"/>
+    <row r="14" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" s="37"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="28"/>
     </row>
-    <row r="12" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="28"/>
+    <row r="15" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C15" s="37"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="28"/>
     </row>
-    <row r="13" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="28"/>
+    <row r="16" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="28"/>
     </row>
-    <row r="14" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="28"/>
-    </row>
-    <row r="15" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="28"/>
-    </row>
-    <row r="16" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+    <row r="17" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="28"/>
-    </row>
-    <row r="17" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="24"/>
+      <c r="B17" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C17" s="37"/>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="28"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="28"/>
     </row>
-    <row r="18" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="24"/>
+        <v>278</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C18" s="23"/>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="28"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="28"/>
     </row>
-    <row r="19" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="24"/>
+        <v>279</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C19" s="37"/>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="28"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="28"/>
     </row>
-    <row r="20" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="24"/>
+        <v>280</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C20" s="37"/>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="28"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="28"/>
     </row>
-    <row r="21" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="28"/>
+    </row>
+    <row r="22" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="28"/>
+      <c r="B22" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C22" s="37"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="28"/>
     </row>
-    <row r="22" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+    <row r="23" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="28"/>
+      <c r="B23" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="C23" s="37"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="28"/>
     </row>
-    <row r="23" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+    <row r="24" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="28"/>
+      <c r="B24" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C24" s="37"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="28"/>
     </row>
-    <row r="24" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+    <row r="25" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="28"/>
+      <c r="B25" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="28"/>
     </row>
-    <row r="25" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+    <row r="26" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="28"/>
+      <c r="B26" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C26" s="37"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="28"/>
     </row>
-    <row r="26" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+    <row r="27" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="B26" s="37"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="28"/>
+      <c r="B27" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="C27" s="37"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="28"/>
     </row>
-    <row r="27" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+    <row r="28" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="B27" s="37"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="28"/>
+      <c r="B28" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C28" s="37"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="28"/>
     </row>
-    <row r="28" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+    <row r="29" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="28"/>
+      <c r="B29" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="C29" s="37"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="28"/>
     </row>
-    <row r="29" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+    <row r="30" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="28"/>
+      <c r="B30" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="C30" s="37"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="28"/>
     </row>
-    <row r="30" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+    <row r="31" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="B30" s="37"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="28"/>
+      <c r="B31" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="C31" s="37"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="28"/>
     </row>
-    <row r="31" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="28"/>
-    </row>
-    <row r="32" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="30" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="27" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Vigil_Content_v2.0.xlsx
+++ b/Vigil_Content_v2.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicsmacbook/pCloud Drive/Personal/Vigil/Vigil v2/vigil-build/Vigil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419CC4D7-A394-B042-A420-B60E1FA498FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69367205-1F7E-D74C-9187-6B957D8A102D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="26880" windowHeight="18460" activeTab="1" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
   </bookViews>
   <sheets>
     <sheet name="April" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="427">
   <si>
     <t>Hover Links</t>
   </si>
@@ -5547,11 +5547,6 @@
 Eastertide · Week Seven</t>
   </si>
   <si>
-    <t>28 May 2026
-Thursday
-Ordinary Time · Week One</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">27 May 2026
 Wednesday
@@ -5606,33 +5601,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">30 May 2026
-Saturday
-Ordinary Time · Week One
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>The Blesssed Virgin Mary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> on Saturday</t>
-    </r>
-  </si>
-  <si>
     <t>31 May 2026
 Sunday
 Ordinary Time · Week Two
@@ -5760,157 +5728,6 @@
   </si>
   <si>
     <t>CH-0630</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">02 June 2026
-Tuesday
-Ordinary Time · Week Two
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Marcellinus and St Peter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, martyrs</t>
-    </r>
-  </si>
-  <si>
-    <t>04 June 2026
-Thursday
-Ordinary Time · Week Two</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">03 June 2026
-Wednesday
-Ordinary Time · Week Two
-Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Charles Lwanga and companions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, martyrs</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">05 June 2026
-Friday
-Ordinary Time · Week Two
-Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Boniface</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, bishop and martyr</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">06 June 2026
-Saturday
-Ordinary Time · Week Two
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Norbert</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">, bishop
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>The Blessed Virgin Mary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> on Saturday</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">01 June 2026
-Monday
-Ordinary Time · Week Two
-Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Justin Martyr</t>
-    </r>
   </si>
   <si>
     <t>We are in Eastertide, on the eve of Pentecost — the last few days of the great fifty, the threshold before the Spirit comes.
@@ -6491,169 +6308,6 @@
 In Christ's name, Amen.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">What arrived at Pentecost did not arrive quietly. It arrived as wind and fire — disruptive, unmistakable, impossible to ignore. The disciples in that room had been waiting, praying and keeping still. They had done everything that could be done from the human side.
-And then something happened that they could not have produced by their own waiting.
-That is the character of the Spirit throughout scripture: it is not generated, it is received. It comes from outside the system. It does not reward effort in the way that effort normally expects to be rewarded. It comes when and how it will — which is not an argument against preparation, but an argument against the assumption that preparation is what causes the arrival.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Where in your life have you been trying to generate what can only be received — working to produce a quality of faith, peace or love that is, in the end, a gift? 
-And what would it mean to stop producing and simply become the kind of person through whom the Spirit can move?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>SPIRIT [SPIR-it]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-In the original languages of scripture, the word for spirit carries more than one meaning at once — and that is not an accident.
-The Hebrew </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>ruach</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (רוּחַ) means wind, breath and spirit. The Greek </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>pneuma</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (πνεῦμα) carries the same range. In both cases, what the word holds together is the movement of an invisible force that is known not by being seen but by what it does: the breath that animates a body, the wind that bends the trees, the spirit that moves through and beyond what is merely physical.
-This is why, when the Spirit arrives at Pentecost, it arrives as wind and fire — not as metaphors added afterward to explain something, but as the thing itself in its most recognisable forms. The word was never only spiritual in the modern, ethereal sense. It was always also breath. Always also force.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>"When the day of Pentecost had come, they were all together in one place. 
-And suddenly from heaven there came a sound like the rush of a violent wind, and it filled the entire house where they were sitting. 
-Divided tongues, as of fire, appeared among them, and a tongue rested on each of them. 
-All of them were filled with the Holy Spirit and began to speak in other languages, as the Spirit gave them ability."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Acts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 2:1–4 — NRSV</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Choose one thing today that you have been trying to do in your own strength — a conversation you have been dreading, a habit you have been fighting, a relationship you have been managing — and before you face it, pause and ask the Spirit to go with you into it.
-Not a long prayer. A single breath, and the simplest of requests:
-Come, Holy Spirit.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Veni, Sancte Spiritus.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>The Spirit does not need elaborate invitation. It needs only the door to be open.</t>
-    </r>
-  </si>
-  <si>
     <t>We are at the start of Ordinary Time — the first Monday after Pentecost, and the first weekday of a new season.
 Ordinary Time is not a diminishment. It is the season in which what was given at Easter and Pentecost is carried into the whole ordinary length of a life. 
 The Church begins it today by remembering Mary — present at the Annunciation, present at the cross, and present in the Upper Room when the Spirit came. She is the one figure who stands at every threshold of the story, and the Church calls her its mother.</t>
@@ -6772,21 +6426,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Author · Acts of the Apostles (1st century AD). 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFF0E0D0"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Traditionally identified as Luke, a physician and companion of St Paul, and as the author of both the synonymous Gospel and the Acts of the Apostles. He is featured today because the opening of Acts 2 is his account of the Spirit's arrival at Pentecost — the event that closes Eastertide and opens the life of the Church.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="12"/>
@@ -7101,12 +6740,6 @@
     <t>Green</t>
   </si>
   <si>
-    <t>07 June 2026
-Sunday
-Ordinary Time · Week Three
-Solemnity: Corpus Christi</t>
-  </si>
-  <si>
     <t>Palette</t>
   </si>
   <si>
@@ -7173,12 +6806,3321 @@
       <t>An Anglo-Saxon monk, scholar and historian. The Church remembers him as one of the first and greatest interpreters of scripture in the Latin West — a man who spent almost his entire life within a few miles of the Benedictine monastery in Northumbria (northern England) where he was placed as a child.</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are at the start of Ordinary Time — the season in which the life of the resurrection is carried into the whole ordinary length of a life.
+Today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Augustine of Canterbury</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, who was sent from Rome to the British Isles, the Western edge of the known Christian world in 597, and arrived not knowing what he would find there.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">SENT [sent]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To be sent is not the same as choosing to go. It implies a prior act — someone else's decision, someone else's purpose — and a direction you did not set for yourself.
+The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>apostellō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ἀποστέλλω) means to send out, to dispatch, to commission. It is the verb from which "apostle" is made — and that etymology matters. An apostle is not simply a messenger, someone carrying news on behalf of another. A messenger delivers what they have been given and departs. An apostle is sent with authority: to represent, to act, to embody the one who sent them in the place they are sent to.
+The distinction is not subtle. When the risen Christ tells his disciples "as the Father has sent me, so I send you," he is not commissioning a courier service. He is extending his own mission — making them participants in it, not merely carriers of it.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>How beautiful upon the mountains are the feet of the messenger who announces peace, who brings good news, who announces salvation, who says to Zion, 'Your God reigns.'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Isaiah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 52:7 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You send your messengers before you know the road they will travel.
+Where we have been waiting for certainty before we consent to go, give us the courage of those who went first.
+Where we have kept what we were given to carry, teach us to move.
+Let the beauty of your sending be visible not just in our gifts but in our going — the ordinary faithfulness of feet that do not turn back.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Augustine carried the Gospel to people who had no framework to receive it — no shared language, no common reference point, nothing to make the message feel familiar. What he had was the message itself, and the authority of the one who sent him.
+Today, before you enter a conversation or situation where the other person seems unreachable — impatient, indifferent, closed — pause beforehand and say simply: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"Lord, I am going in your name. Send me into this."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Then go. Not performing anything. Not managing the outcome. Simply present, on ground you did not choose, carrying a commission that is not yours to put down.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The apostle does not wait for a welcome. They go because they have been sent.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Augustine of Canterbury (d. 604 AD).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Benedictine monk sent by Pope Gregory the Great to evangelise the Anglo-Saxons in 597. He landed in Kent, was received by King Æthelberht, and became the first Archbishop of Canterbury. His mission gives the day's word its most concrete instance — a person sent to an unknown place with a commission that was not his own.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Isaiah (8th–7th century BC).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">A prophet of ancient Israel, writing during a time of military defeat and national crisis. Today's scripture comes from Isaiah 52, a later section of the book associated with the Babylonian exile, addressing a people who have been waiting a long time for rescue and have almost stopped believing it will come.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">St Gregory the Great (c. 540–604 AD).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Bishop of Rome and one of the most influential figures in the early medieval Church. He is featured today because it was he who conceived and commissioned the mission to the Anglo-Saxons, chose Augustine to lead it.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The feet in </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Isaiah's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> image are beautiful not because they arrived quickly. They are beautiful because they carried something desperately needed — and because, behind them, was a very long road.
+An apostle is not self-commissioned. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Augustine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> did not go to Kent because he had decided the Anglo-Saxons needed him. He went because the Pope, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Gregory the Great</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, sent him — and when the journey became frightening enough that he turned back halfway, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Gregory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> wrote: go. And he went.
+That is what being sent means. When the going becomes difficult, you are not renegotiating with yourself. You are accountable to the one who sent you. And that accountability is a kind of freedom: you are not responsible for the outcome. You are responsible for the going.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where have you been broadly willing — open to the idea of being sent — but specifically resistant to the person, the place or the task in front of you? And what would it take to stop resisting and simply go?</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Ordinary Time — the season that follows Pentecost, when the Church carries what it has received back into the full ordinary length of a life.
+There is no great feast today. The liturgical colour is green: the colour of growth, of steady life, of things becoming what they were made to be without drama or announcement.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Psalmist · Psalm 27 (c. 10th–6th century BC).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalm 27 is traditionally attributed to King David, though the Psalms were composed across many generations. It is a psalm of trust and longing written in the face of real threat and it is featured today because it gives the day's word its clearest devotional form: not seeking as anxious searching, but seeking as the deliberate orientation of a life toward the one thing that matters most.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You are the one thing worth seeking — and you tell us to seek.
+Where our attention has scattered across a dozen urgent things, gather it.
+Where we have been looking in the wrong directions,
+not out of wickedness but out of confusion, turn us gently toward you.
+Let us seek your face today, not as an obligation
+but as the thing we most want to find.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Choose one moment today when you notice yourself scattered — pulled between competing demands, unable to settle, unsure what to do first — and use that moment deliberately.
+Stop. Say the </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalmist's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> phrase to yourself: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">One thing I asked. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Let it pause the scatter.
+Then return to what you were doing — but carrying a slightly different question: is what I'm giving my attention to now the one thing, or am I avoiding it?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Every time you return to that question, you are practising the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalmist's</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> kind of seeking: not frantically, not perfectly — just deliberately, in the direction of God.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>SEEK [seek]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To seek is not the same as to search randomly. It is to move toward something you believe or know exists, even before you have found it.
+The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>zēteō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ζητέω) appears throughout the New Testament as an active, present-tense command — not a one-time action but a continuous orientation. 
+appears in the New Testament as an active, present tense command.  It is something to continue to do, it is not a one-off. A life of faith, as Jesus describes it, is not an occasional reach toward God, but a sustained orientation towards Him.
+The seeking is not desperate; it is deliberate. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalmist</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is not asking for safety, success or resolution of any particular difficulty. What he is seeking is to live in the house of the Lord. The seeking has been narrowed to its simplest possible form.
+Most of us seek many things — and not all of them badly. But there is a difference between the seeking that scatters you across a hundred anxious goals, and the seeking that draws everything back toward a single centre. The </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalmist</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> has found that centre, and the rest of the psalm holds together differently because of it.
+Think of the thing you checked first this morning before you were properly awake — the inbox, the news, the problem you went to sleep still turning over. That is not necessarily the wrong thing to care about. But it is probably not the one thing.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>What would it mean to name, before God today, the one thing you are actually looking for — beneath everything you are chasing?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">One thing I asked of the Lord,
+that will I seek after:
+to live in the house of the Lord
+all the days of my life,
+to behold the beauty of the Lord,
+and to inquire in his temple.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 27:4 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <t>28 May 2026
+Thursday
+Ordinary Time · Week One</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are at the start of Ordinary Time — the season that follows Pentecost, when the life the Spirit brought is carried back into the full ordinary length of a day.
+Today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Paul VI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — the pope who received the renewal of the Second Vatican Council and spent his papacy asking what it meant, in practice, to carry the Gospel into a changed world.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>PROCLAIM [pruh-KLAYM]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Greek word is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kēryssō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (κηρύσσω) — to herald, to announce publicly, to declare what is already true. It is not the word for persuasion, or for making a case. It is the word for someone standing in the town square with news that does not belong to them.
+In the ancient world, the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kēryx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — the herald — did not compose the message. They carried it. Their authority came entirely from the one who sent them, and their job was simply not to lose the content on the way. What they proclaimed had already happened. They were not creating the event; they were making it known.
+That is the word the New Testament uses for what the apostles do with the resurrection. Not argue for it. Not perform it. Proclaim it — as people who were there, or who received it from those who were.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"But how are they to call on one in whom they have not believed? 
+And how are they to believe in one of whom they have never heard? 
+And how are they to hear without someone to proclaim him? 
+And how are they to proclaim him unless they are sent?"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Romans 10:14–15a (NRSV)</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You sent your word into the world and it did not return empty.
+You gave your heralds not their own message but yours — and asked only that they carry it faithfully.
+Where the Gospel has grown familiar in us, make it new.
+Where we have kept it too private to be of use to anyone, give us the courage of those who could not stay quiet.
+Where we have been ashamed of the chain that brought it to us, teach us to honour it — and to extend it.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The herald's job is not to compose the message. It is to carry it without losing it. But before you can carry something, you have to know what it actually is — not in the abstract, but in your own life: the specific moment the Gospel arrived and something shifted.
+Today, before any other conversation, write one sentence — just one — finishing this: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Gospel became real to me when… </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Don't edit it. Don't make it sound impressive. Let it be as plain and particular as it actually was.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>That sentence is your proclamation. Everything else follows from it.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Paul VI (1897–1978)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Pope from 1963 to 1978. He received the Second Vatican Council from his predecessor and spent his papacy working out what renewal meant in practice — in the liturgy, in the Church's relationship to the modern world, and in Christian mission. His 1975 apostolic exhortation</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Evangelii Nuntiandi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>(on the proclamation of the Gospel in the contemporary world) remains one of the most searching documents on what it means to carry the Gospel without losing it on the way.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+St Paul (1st century AD)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Apostle, missionary and author of letters central to the New Testament. He is featured today because Romans 10 gives the day's word its most precise structural account: proclamation is not an optional feature of Christian life but the load-bearing link in a chain that runs from God's sending to the hearer's faith.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Notice what the herald does not do. They do not compose the message. They do not adjust it for the audience. They do not decide whether the news is good enough to be worth announcing today.
+They simply do not lose it on the way.
+Most of the difficulty in Christian proclamation is not a failure of courage. It is a much quieter problem: the message has become too familiar to feel like news. The resurrection (if you have been hearing it since childhood) can settle into background noise, and background noise is not something anyone feels compelled to announce.
+But </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Paul's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> chain in the letter to the Romans assumes the message is still news. Still capable of being the thing someone hasn't heard yet and needed to. The herald's job is to keep treating it that way — to carry it as though it were still urgent, because it is.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>When did you last feel the Gospel as news — something that arrived, changed the room, and couldn't be unfelt? And what has been quietly domesticating it since then?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">RECEIVE [ri-SEEV]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>dechomai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (δέχομαι) means to take hold of what is offered — not passively, but with open hands and deliberate willingness. It is the word for someone who sees something coming toward them and makes the conscious choice not to step aside.
+This matters because receiving is harder than it sounds. Most of us are better at doing, giving, managing and producing than we are at simply taking in what we are being offered. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Dechomai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> names the movement that makes all of those possible: the prior act of opening your hands before anything else can be placed in them.
+In the New Testament, it is the word used for receiving the kingdom of God, receiving the Word, receiving a person. In every case, the same logic applies: what is being offered is real and full, and the only question is whether the one it is offered to is willing to receive it.</t>
+    </r>
+  </si>
+  <si>
+    <t>Here am I, Lord.
+You know how much easier it is for us to give than to receive — to stay busy and useful and needed, rather than to open our hands and let something come in.
+Where we have kept you at a working distance, draw us close.
+Where we have been offered more than we have allowed ourselves to take — your peace, your forgiveness, your presence in the ordinary hours — teach us to receive it.
+Make us more like the one who said: let it be with me according to your word.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are at the end of the first week of Ordinary Time — the Saturday after Pentecost, the day before the Church keeps the Solemnity of the Most Holy Trinity.
+On Saturdays throughout Ordinary Time, the Church holds a quiet, optional memory of </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>. Not a feast. Just a pause — a moment to remember the woman who, more than anyone else in the story, knew what it meant to receive something she had not asked for, and to let it change everything.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mary's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> response to the angel is one of the most compressed sentences in all of scripture. She does not pretend to understand what she has been told. She asks one question — how can this be? — and then, before the answer is complete, she opens her hands.
+That is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>dechomai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">. Not blind compliance. Not immediate comprehension. A willingness to let something come in before she knows what it will ask of her.
+Most of us receive well when we can see what we are receiving — when the shape of the gift is legible and the cost seems manageable. The harder work is receiving something whose full weight won't be clear until much later. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> received the Annunciation without knowing the cross was at the end of it.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>What is being offered to you at the moment that you have not yet let yourself fully receive — not because it is bad, but because you cannot yet see where it leads?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Today, when someone offers you something—help you didn't ask for, a kindness you feel you should decline, a compliment that makes you want to deflect—stop before you redirect it. 
+Notice the reflex to say </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>I'm fine, you didn't have to, it's nothing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">. Then receive it: say thank you and mean it. 
+And let that small act of receiving be, quietly, a prayer.: a practice of the same open-handedness you are asking God for.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Receiving is a form of trust. Every time you let something good in without immediately deflecting it, you are practising the posture </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mary</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> held before God.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">In the sixth month the angel </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Gabriel</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> was sent by God to a town in Galilee called Nazareth, to a virgin engaged to a man whose name was </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Joseph</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, of the house of David. The virgin's name was </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mary</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 
+And he came to her and said, "Greetings, favoured one! The Lord is with you." But she was much perplexed by his saying and pondered what sort of greeting this might be. 
+The angel said to her, "Do not be afraid, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mary</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, for you have found favour with God. And now, you will conceive in your womb and bear a son, and you will name him Jesus."
+Then </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mary</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> said, "Here am I, the servant of the Lord; let it be with me according to your word." 
+Then the angel departed from her.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Luke</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 1:26–31, 38 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mary (1st century BC – 1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">The mother of Jesus. She appears at the most significant moments of his life and story: the Annunciation, the birth, the beginning of Jesus' public ministry, the crucifixion, and in the Upper Room before Pentecost. The Church remembers her on Saturdays in Ordinary Time as a recurring act of quiet devotion.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Joseph (1st century BC – 1st century AD). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Carpenter of Nazareth, betrothed to Mary at the time of the Annunciation, and the man the Gospels name as the earthly father of Jesus. He is named here to establish Jesus' descent from the royal house of David.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Gabriel (dates unknown). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">One of the named angelic messengers of God: a figure whose appearances mark moments of divine announcement. His name means </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>God is my strength</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> in Hebrew.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+St Luke (1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally identified as a physician and companion of St Paul, and as the author of both the third Gospel and the Acts of the Apostles. He is featured today because it is Luke's Gospel that gives us the Annunciation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">30 May 2026
+Saturday
+Ordinary Time · Week One
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Blesssed Virgin Mary</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Ordinary Time, on its first Sunday — and before the long green season settles into its rhythm, the Church pauses to keep the Solemnity of the Most Holy Trinity.
+Everything Eastertide revealed—the Son sent by the Father, the Spirit sent by the Son—points here: to the kind of God in whom giving and receiving are not separate acts, but a single, shared life.</t>
+  </si>
+  <si>
+    <t>Lord,
+You are not a God who exists alone and occasionally shares yourself. You are a life that is communion — Father, Son and Spirit, giving and receiving without end.
+We have felt the edge of this. We have known moments of closeness that stayed with us, that showed us something about what we were made for.
+We bring you the longing that has not yet found its home. Not as a complaint, but as a prayer: draw us in.
+Teach us to receive what you are already giving, and to give what we have been keeping.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Think of one person in your life with whom something has been kept back — a word unsaid, a warmth withheld, a distance maintained that neither of you has named. 
+You do not need to resolve it today. But you can, quietly, name it before God: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>this is where my giving has stopped short.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Then do one small thing that closes the distance slightly — a message, a question, a moment of genuine attention — not because you have resolved whatever made you pull back, but because today's word suggests that God gives himself entirely, and that we are made for something like that.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Communion begins not when everything is resolved, but when we stop pretending the distance isn't there.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"When the Spirit of truth comes, he will guide you into all the truth; for he will not speak on his own, but will speak whatever he hears, and he will declare to you the things that are to come. 
+He will glorify me, because he will take what is mine and declare it to you. 
+All that the Father has is mine. For this reason I said that he will take what is mine and declare it to you."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>John</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 16:13–15 (NRSV)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Trinity is not three beings who happen to get along well. It is a single divine life constituted entirely by the act of giving oneself to the other. The Father gives himself to the Son; the Son gives himself to the Father; the Spirit is (in </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Augustine's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> words) the love between them. Nothing is held in reserve.
+The closest we come to this in ordinary life is where we stop calculating. We stop asking whether we are getting as much as we are giving or whether our trust is being matched.  When that calculation goes quiet, that is what communion begins to look like.
+The question worth sitting with is whether your relationship with God has that quality. Not whether you feel close to him on the good days, but whether you are still keeping score on the bad ones, still waiting to find out if your trust was worth it.
+Because God is not waiting to see how you turn out before he gives himself. The giving is already happening. What would change in how you pray today if you actually believed that?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Paul [c. 5–c. 67 AD]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Apostle, missionary and author of letters central to the New Testament. He is featured today because his second letter to the Corinthians closes with a benediction that has shaped Christian worship ever since — naming Father, Son and Spirit in a single sentence as the one source of grace, love and koinōnia given to the Church.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+St John [1st century AD]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally identified as one of the Twelve Apostles and as the author of the fourth Gospel, three letters and the book of Revelation. He is featured today because John 16 gives the interior life of the Trinity its most intimate scriptural expression — Jesus describing, from inside the relationship, the continuous movement of giving between Father, Son and Spirit.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+St Augustine [354–430 AD]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bishop of Hippo in North Africa, Doctor of the Church and one of the most influential thinkers in the history of Western Christianity. He is featured today because his work </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>De Trinitate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (On the Trinity) gives us the image of the Spirit as the love shared between Father and Son: communion made personal within God himself.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">COMMUNION [kəm-YOON-yən]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Most of us reach for this word in two places: the Lord's Table, and the feeling of being"in communion with" or truly known by another person.
+The Greek word is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>koinōnia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (κοινωνία), meaning a fellowship that holds in common something that no party could hold alone. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> closes his second letter to the Corinthians with it in a phrase that has been spoken at Christian gatherings ever since: "the grace of the Lord Jesus Christ, the love of God, and the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>koinōnia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> of the Holy Spirit." Three names. One benediction.
+Today the Church keeps the Solemnity of the Most Holy Trinity. Classical Christian theology has one answer to what kind of God this is: not a solitary being who sometimes communicates, but a God who is communion in himself. The Father, the Son and the Holy Spirit share themselves, completely and without loss.
+Which means the human longing not to be alone is not a deficiency in need of correction: it is the image of God in which we are made.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Think of the last time you lost track of time—perhaps when you were absorbed in a problem or a conversation, in a piece of music or in something you were making or reading—and then you emerged from it feeling (without quite being able to say why) that it mattered.
+That quality of absorption is worth paying attention to. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Justin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> believed the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Logos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> seeds human minds precisely through the things that pull us in without our permission.
+Before the day ends, name that thing to God. Not with a theological conclusion attached but with just this: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>This is what drew me in. I don't know why it matters. But I think you might.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+--
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Word has been at work in you longer than you have known where to look.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lord,
+You are the Reason through whom all things were made — and you have not confined yourself to the places we set aside for you.
+Where we have divided our lives into the sacred and the rest, forgive us.
+Where we have been looking for you only in the expected places, open our eyes to the ones we have not thought to look.
+Let the honesty we bring to the rest of our lives become the honesty we bring to you — and let what we find there lead us, as it led </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Justin</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, closer to the Word that was there from the beginning.
+In Christ's name, Amen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">There is a habit that is easy to fall into of dividing experience into the sacred and the ordinary: the moments that count spiritually ... and the rest of life which doesn't. A church service on one side; a conversation about physics or politics or art on the other.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Justin's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>logos spermatikos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> quietly dismantles that division. 
+If seeds of the divine Reason are scattered through all human thinking, then the boundary between sacred and secular is less solid than it looks. 
+The mathematician who follows a proof to its conclusion, the philosopher who will not let a bad argument stand, the person who looks at suffering and refuses to call it meaningless — all of them may be closer to the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Logos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> than they know.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The question is not whether God is present in the parts of your life you have set aside for him. It is whether you have been looking for him in the parts you haven't.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>He is the image of the invisible God, the firstborn of all creation; for in him all things in heaven and on earth were created, things visible and invisible, whether thrones or dominions or rulers or powers — all things have been created through him and for him. 
+He himself is before all things, and in him all things hold together.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Colossians 1:15–17 (NRSV)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">REASON [REE-zən]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+"In the beginning," opens </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>John's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Gospel, "was the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Logos," </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">the Greek word meaning reason, word and ordering principle all at once.  It was an explanation that the intelligence through which all things came into being was there before anything else was.
+That claim had been sitting in Christian thought for decades when a philosopher named </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Justin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, writing in Rome in the second century, drew out its most radical implication. If the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Logos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — the divine Reason — is the source of all things, then wherever human beings reason truthfully, wherever they arrive at something real and good, they are brushing up against the same Word.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Justin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> called these scattered touches the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>logos spermatikos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> or "seeds of the Logos", present in every human mind before anyone had heard the name of Christ. 
+Which means that reason, at its most honest, is not a rival to faith. It is one of the places where the Word has always been at work.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are at the start of Ordinary Time — the season in which the life of the Spirit is carried into the full ordinary length of a day.
+Today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Justin Martyr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, a second-century philosopher who gave his life for what he believed — and who spent that life arguing that faith and reason are not enemies, but that one, followed honestly enough, leads to the other.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Justin Martyr (c. 100–165 AD)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Philosopher and martyr, one of the earliest Christian apologists. The Church remembers him today; his life gives the day's word its sharpest instance — a man who followed reason honestly enough that it led him to Christ, and then to a trial in Rome where he was beheaded for refusing to renounce what he had found.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">St Paul (1st century AD)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apostle, missionary and author of letters central to the New Testament. He is featured today because the letter to the Colossians — written in his name, though some scholars consider it the work of a close associate — gives the day's word its most concentrated scriptural expression: the Logos through whom all things were made is the one in whom all things hold together.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St John (1st century AD)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Traditionally identified as one of the Twelve Apostles and as the author of the fourth Gospel, three letters and the book of Revelation. He is featured today because the opening of John's Gospel gives the day's word its deepest ground: in the beginning was the Logos — the divine Reason through whom all things were made, present before anything else existed.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You do not ask us to understand what endurance is making in us, only to remain inside it.
+Where we have been managing our way around the hard thing rather than staying present to it, forgive us.
+Make us faithful in the middle of the process, when nothing yet is visible and the temptation to leave is strongest.
+And give us eyes for those around us who are quietly carrying a weight that has been there a long time, that we might stay near them as you stay near us.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The middle of a long endurance is the place where nothing feels like it is happening. That is not a sign that it has stalled. It is simply what the inside of formation looks like.
+At some point today, find one person who is in the middle of something — not at the crisis point, just quietly carrying a weight that has been there a while — and tell them simply: I have not forgotten you are in this. No advice. No resolution. No attempt to move them on from it.
+That act of witness — staying present to someone else's endurance without trying to end it — is itself a form of endurance.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>To remain alongside someone who is remaining is one of the most concrete acts of faith there is.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Consider it nothing but joy, my brothers and sisters, when you face trials of any kind, for you know that the testing of your faith produces endurance; and let endurance have its full effect, so that you may be mature and complete, lacking in nothing.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>James</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 1:2–4 (NRSV)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are at the start of Ordinary Time — the second week of the green season, when the Church carries the life of Easter into the ordinary length of a day.
+Today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Sts Marcellinus and Peter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, two early Christians who were put to death for their faith in Rome, and whose names have been spoken at the heart of the Church's prayer ever since. Ordinary Time begins, quietly, with people who did not give up.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Sts Marcellinus and Peter (d. 304 AD)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Early Christian martyrs executed in Rome during the persecution under the Emperor Diocletian — Marcellinus a priest, Peter an exorcist. Their names have been included in the Canon of the Mass since at least the sixth century, making them among the most consistently commemorated martyrs in Christian liturgical history.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">St James (d. c. 62 AD)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally identified as the brother of Jesus and leader of the early Christian community in Jerusalem. He is featured today because his letter — addressed to believers facing hardship — gives the day's word its most precise theological definition: endurance not as resignation, but as what the testing of faith actively produces.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>James</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> says: let endurance have its full effect. That word let is worth sitting with.
+Endurance, by its very nature, is not instantaneous. It has an effect, and that effect takes time. Which means the reader may be somewhere in the middle — the trial has arrived, the choice to remain has been made, but the effect is not yet visible. Just in the middle. Still there. Not sure it is working.
+The temptation at that point is always the same: to assume nothing is happening because nothing visible is changing. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>James's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> logic runs the other way. The invisibility of the process is not evidence of failure. It is simply what formation looks like from the inside.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The relationship that has not healed. The prayer that has not been answered. The grief that has not lifted. If any of these has been with you long enough to feel permanent — what would change today if you stopped treating the invisibility as a problem to solve, and trusted instead that the work is already happening?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>ENDURE [en-DYOOR]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Here is what the word does not mean. It does not mean gritting your teeth until something passes.  That is endurance as we usually reach for it — putting up with difficulty until it stops.
+The Greek word is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hypomonē</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ὑπομονή), and it works differently. Built from </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hypo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (under) and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>menō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (to remain), it describes someone who remains under a weight long enough for faith to be stress-tested — and to hold.  Not resignation.  Not stoic indifference.  The person who endures has not found a way around the difficulty.  They have found a reason to stay inside it.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St James</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> writes to people facing real hardship and tells them something striking: endurance is not what faith costs you.  It is what faith produces in you.  It grows precisely where the pressure is greatest and cannot be manufactured any other way.
+Endurance is not the absence of struggle. It is what the struggle is quietly making.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Today someone will ask you an ordinary question whose honest answer brushes against your faith — how your weekend was, why you do a thing you do, what you make of something difficult. 
+You will feel the familiar pull to give the edited version, the one that leaves God out to keep things smooth. 
+When it comes, give the unedited answer instead. Not a sermon, just the true sentence you would otherwise have trimmed.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>A faith never said aloud can thin, over time, into something you only think you hold — so the small true word is worth saying.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You promise to acknowledge before the Father everyone who acknowledges you — and you ask of us nothing we have not already been given.
+Where we have edited you out of the day to keep ourselves safe, forgive us.
+Where our faith has gone quiet — not from doubt, but from caution — give us back our voice.
+Teach us to let our words match what we believe, in the small places before the large ones.
+And keep us mindful of those, like the martyrs we remember today, for whom confessing your name still costs everything.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Everyone therefore who acknowledges me before others, I also will acknowledge before my Father in heaven; but whoever denies me before others, I also will deny before my Father in heaven.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Matthew 10:32–33 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">CONFESS [kən-FESS]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The word has both a courtroom and a church in it. We confess to a crime; we confess our faith. Both senses are in the original Greek.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>homologeō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ὁμολογέω) is built from </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>homos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (same) and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>legō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (to say): to say the same thing — to agree out loud, to let your word match what is already true. To confess is not to reveal a secret. It is to stop keeping one.
+In the early Church, the distinction between a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>confessor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>martyr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> was narrow. The confessor was the one who acknowledged Christ under questioning and lived. The martyr was the one who acknowledged him and did not. The same act, the same word — only the cost differed.
+Which is why English keeps the older sense in its other translation. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>homologeō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is often rendered not "confess" but "acknowledge": simply to say, before others, to whom you belong.
+To confess, then, is not chiefly about admitting fault. It is about admitting allegiance: owning in the open the thing you already hold in private.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in Ordinary Time, on the Wednesday of its second week — the long green season in which the life given at Easter and Pentecost is worked into the ordinary length of a day.
+Today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Charles Lwanga and his companions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>: young men and boys in a royal court in what is now Uganda, many of them new to the faith, who would not deny it when denial was the price of their lives. Vigil turns today to what their deaths were made of — the act of saying openly, and at cost, whose you are.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Most of us do not deny Christ. We edit him. The sentence that would have mentioned him gets shortened; the belief that would have surfaced stays just below the waterline; the conversation moves on and nothing untrue has been said. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Charles Lwanga and his companions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> were handed the cleaner version of the choice — say it or die — and they said it. 
+The version most of us are given is quieter, and in some ways harder to notice: a hundred small economies of truth that never feel like denial, because each one is so small.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where has your faith become something you hold without quite acknowledging — true in private, edited in public? 
+And what might change between you and God if, in one of those small places, you simply let your word match what you already believe?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Saint Charles Lwanga (c. 1860–1886) and his Companions, martyrs.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Converts to Christianity at the royal court of the kingdom of Buganda, in what is now Uganda. Lwanga had charge of the king's pages and protected the younger boys among them; he and his companions — several baptised only shortly before — were put to death, many by burning at Namugongo, for refusing to renounce their faith. The Church remembers them today as among the first modern martyrs of sub-Saharan Africa. Catholic and Anglican converts died together in the same persecution, and both Churches honour them.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Saint Matthew (1st century AD).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally identified as one of the Twelve Apostles — a tax collector called by Jesus — and as the author of the first Gospel. He is featured today because his Gospel records Jesus' words to his closest followers about acknowledging him before others: the promise, and the warning, on which the day's word turns.</t>
+    </r>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">03 June 2026
+Wednesday
+Ninth Week • Ordinary Time
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Charles Lwanga and his companions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, martyrs</t>
+    </r>
+  </si>
+  <si>
+    <t>04 June 2026
+Thursday
+Ninth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">05 June 2026
+Friday
+Ninth Week • Ordinary Time
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Boniface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, bishop and martyr</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">06 June 2026
+Saturday
+Ninth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Norbert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, bishop
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Blessed Virgin Mary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> on Saturday</t>
+    </r>
+  </si>
+  <si>
+    <t>07 June 2026
+Sunday
+Tenth Week • Ordinary Time
+Solemnity: Corpus Christi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">02 June 2026
+Tuesday
+Ninth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Marcellinus and St Peter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, martyrs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">01 June 2026
+Monday
+Ninth Week • Ordinary Time
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Justin Martyr</t>
+    </r>
+  </si>
+  <si>
+    <t>08 June 2026
+Monday
+Tenth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>10 June 2026
+Wednesday
+Tenth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>12 June 2026
+Friday
+Tenth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>15 June 2026
+Monday
+Eleventh Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>17 June 2026
+Wednesday
+Eleventh Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>21 June 2026
+Sunday
+Twelfth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>26 June 2026
+Friday
+Twelfth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>29 June 2026
+Monday
+Thirteenth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>25 June 2026
+Thursday
+Twelfth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>18 June 2026
+Thursday
+Eleventh Week • Ordinary Time</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">09 June 2026
+Tuesday
+Tenth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Columba</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, abbot
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ephrem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, deacon and Doctor of the Church</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">11 June 2026
+Thursday
+Tenth Week • Ordinary Time
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Barnabas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, apostle</t>
+    </r>
+  </si>
+  <si>
+    <t>13 June 2026
+Saturday
+Tenth Week • Ordinary Time
+Solemnity: The Most Sacred Heart of Jesus</t>
+  </si>
+  <si>
+    <t>14 June 2026
+Sunday
+Eleventh Week • Ordinary Time
+Memorial: The Immaculate Heart of the Blessed Virgin Mary</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">16 June 2026
+Tuesday
+Eleventh Week • Ordinary Time
+Optional Memoral: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Richard of Chichester</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, bishop</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">19 June 2026
+Friday
+Eleventh Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Romuald</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, abbot</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">20 June 2026
+Saturday
+Eleventh Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Alban</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, martyr</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">22 June 2026
+Monday
+Twelfth Week • Ordinary Time
+Feast: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Sts John Fisher and Thomas More</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, martyrs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">23 June 2026
+Tuesday
+Twelfth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St. Etheldreda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, abbess</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">24 June 2026
+Wednesday
+Twelfth Week • Ordinary Time
+Solemnity: The Nativity of </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St John the Baptist</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">27 June 2026
+Saturday
+Twelfth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Cyril of Alexandria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, bishop and Doctor of the Church</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">28 June 2026
+Sunday
+Thirteenth Week • Ordinary Time
+Solemnity: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Sts Peter and Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, apostles</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">30 June 2026
+Tuesday
+Thirteenth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The First Martyrs of the Church of Rome</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>SPIRIT [SPIR-it]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+In the original languages of scripture, the word for spirit carries more than one meaning at once — and that is not an accident.
+The Hebrew </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>ruach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (רוּחַ) means wind, breath and spirit. The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>pneuma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (πνεῦμα) carries the same range. In both cases, what the word holds together is the movement of an invisible force that is known not by being seen but by what it does: the breath that animates a body, the wind that bends the trees, the spirit that moves through and beyond what is merely physical.
+This is why, when the Spirit arrives at Pentecost, it arrives as wind and fire — not as metaphors added afterward to explain something, but as the thing itself in its most recognisable forms. The word was never only spiritual in the modern, ethereal sense. It was always also breath. Always also force.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"When the day of Pentecost had come, they were all together in one place. 
+And suddenly from heaven there came a sound like the rush of a violent wind, and it filled the entire house where they were sitting. 
+Divided tongues, as of fire, appeared among them, and a tongue rested on each of them. 
+All of them were filled with the Holy Spirit and began to speak in other languages, as the Spirit gave them ability."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Acts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2:1–4 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">What arrived at Pentecost did not arrive quietly. It arrived as wind and fire — disruptive, unmistakable, impossible to ignore. The disciples in that room had been waiting, praying and keeping still. They had done everything that could be done from the human side.
+And then something happened that they could not have produced by their own waiting.
+That is the character of the Spirit throughout scripture: it is not generated, it is received. It comes from outside the system. It does not reward effort in the way that effort normally expects to be rewarded. It comes when and how it will — which is not an argument against preparation, but an argument against the assumption that preparation is what causes the arrival.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where in your life have you been trying to generate what can only be received — working to produce a quality of faith, peace or love that is, in the end, a gift? 
+And what would it mean to stop producing and simply become the kind of person through whom the Spirit can move?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Choose one thing today that you have been trying to do in your own strength — a conversation you have been dreading, a habit you have been fighting, a relationship you have been managing — and before you face it, pause and ask the Spirit to go with you into it.
+Not a long prayer. A single breath, and the simplest of requests:
+Come, Holy Spirit.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Veni, Sancte Spiritus.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Spirit does not need elaborate invitation. It needs only the door to be open.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Author · Acts of the Apostles (1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally identified as Luke, a physician and companion of St Paul, and as the author of both the synonymous Gospel and the Acts of the Apostles. He is featured today because the opening of Acts 2 is his account of the Spirit's arrival at Pentecost — the event that closes Eastertide and opens the life of the Church.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7252,39 +10194,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FFF0E0D0"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FFF0E0D0"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFF0E0D0"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FFF0E0D0"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFF0E0D0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7324,18 +10239,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFDF5"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC04040"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC04040"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -7525,7 +10428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -7638,25 +10541,7 @@
     <xf numFmtId="15" fontId="2" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7668,14 +10553,14 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7685,10 +10570,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFDF5"/>
+      <color rgb="FF3D4A5C"/>
       <color rgb="FFF0E0D0"/>
       <color rgb="FFC04040"/>
-      <color rgb="FF3D4A5C"/>
-      <color rgb="FFFFFDF5"/>
       <color rgb="FFF2EBE0"/>
       <color rgb="FF8C8680"/>
       <color rgb="FFFFFFFF"/>
@@ -7997,7 +10882,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
-    <col min="2" max="2" width="40.83203125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" style="10" customWidth="1"/>
     <col min="3" max="3" width="40.83203125" style="2" customWidth="1"/>
     <col min="4" max="10" width="50.83203125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="10.83203125" style="1"/>
@@ -8007,8 +10892,8 @@
       <c r="A1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="45" t="s">
-        <v>344</v>
+      <c r="B1" s="39" t="s">
+        <v>330</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>7</v>
@@ -8039,7 +10924,7 @@
       <c r="A2" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="40"/>
       <c r="C2" s="6" t="s">
         <v>98</v>
       </c>
@@ -8069,7 +10954,7 @@
       <c r="A3" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="46"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="6" t="s">
         <v>99</v>
       </c>
@@ -8099,7 +10984,7 @@
       <c r="A4" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="46"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="6" t="s">
         <v>100</v>
       </c>
@@ -8127,7 +11012,7 @@
       <c r="A5" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="47"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="23" t="s">
         <v>101</v>
       </c>
@@ -8157,7 +11042,7 @@
       <c r="A6" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="49"/>
+      <c r="B6" s="42"/>
       <c r="C6" s="12" t="s">
         <v>102</v>
       </c>
@@ -8187,7 +11072,7 @@
       <c r="A7" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="50"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="30" t="s">
         <v>103</v>
       </c>
@@ -8216,7 +11101,7 @@
     <row r="8" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="30" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="28" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -8225,11 +11110,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
-    <col min="2" max="2" width="40.83203125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" style="10" customWidth="1"/>
     <col min="3" max="3" width="40.83203125" style="2" customWidth="1"/>
     <col min="4" max="10" width="50.83203125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="10.83203125" style="1"/>
@@ -8239,8 +11124,8 @@
       <c r="A1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="45" t="s">
-        <v>344</v>
+      <c r="B1" s="39" t="s">
+        <v>330</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>7</v>
@@ -8271,7 +11156,7 @@
       <c r="A2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="40"/>
       <c r="C2" s="6" t="s">
         <v>91</v>
       </c>
@@ -8301,7 +11186,7 @@
       <c r="A3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="46"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="6" t="s">
         <v>92</v>
       </c>
@@ -8331,7 +11216,7 @@
       <c r="A4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="46"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="6" t="s">
         <v>93</v>
       </c>
@@ -8361,7 +11246,7 @@
       <c r="A5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="46"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="6" t="s">
         <v>94</v>
       </c>
@@ -8391,7 +11276,7 @@
       <c r="A6" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="47"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="36" t="s">
         <v>95</v>
       </c>
@@ -8421,7 +11306,7 @@
       <c r="A7" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="47"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="23" t="s">
         <v>96</v>
       </c>
@@ -8451,7 +11336,7 @@
       <c r="A8" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="47"/>
+      <c r="B8" s="41"/>
       <c r="C8" s="23" t="s">
         <v>97</v>
       </c>
@@ -8481,7 +11366,7 @@
       <c r="A9" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="B9" s="47"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="23" t="s">
         <v>132</v>
       </c>
@@ -8511,7 +11396,7 @@
       <c r="A10" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="47"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="23" t="s">
         <v>133</v>
       </c>
@@ -8541,7 +11426,7 @@
       <c r="A11" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="23" t="s">
         <v>144</v>
       </c>
@@ -8571,7 +11456,7 @@
       <c r="A12" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="47"/>
+      <c r="B12" s="41"/>
       <c r="C12" s="37" t="s">
         <v>151</v>
       </c>
@@ -8601,7 +11486,7 @@
       <c r="A13" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="47"/>
+      <c r="B13" s="41"/>
       <c r="C13" s="37" t="s">
         <v>153</v>
       </c>
@@ -8631,7 +11516,7 @@
       <c r="A14" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="41"/>
       <c r="C14" s="37" t="s">
         <v>203</v>
       </c>
@@ -8661,7 +11546,7 @@
       <c r="A15" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="B15" s="47"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="37" t="s">
         <v>180</v>
       </c>
@@ -8691,7 +11576,7 @@
       <c r="A16" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="B16" s="47"/>
+      <c r="B16" s="41"/>
       <c r="C16" s="37" t="s">
         <v>188</v>
       </c>
@@ -8721,7 +11606,7 @@
       <c r="A17" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="B17" s="47"/>
+      <c r="B17" s="41"/>
       <c r="C17" s="37" t="s">
         <v>196</v>
       </c>
@@ -8747,11 +11632,11 @@
         <v>227</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="B18" s="47"/>
+      <c r="B18" s="41"/>
       <c r="C18" s="23" t="s">
         <v>207</v>
       </c>
@@ -8777,11 +11662,11 @@
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="37" t="s">
         <v>214</v>
       </c>
@@ -8811,12 +11696,12 @@
       <c r="A20" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="B20" s="47"/>
+      <c r="B20" s="41"/>
       <c r="C20" s="37" t="s">
         <v>232</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="E20" s="24" t="s">
         <v>229</v>
@@ -8841,7 +11726,7 @@
       <c r="A21" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="B21" s="47"/>
+      <c r="B21" s="41"/>
       <c r="C21" s="37" t="s">
         <v>233</v>
       </c>
@@ -8871,282 +11756,359 @@
       <c r="A22" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="41"/>
       <c r="C22" s="37" t="s">
         <v>252</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="H22" s="27" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="J22" s="28" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="B23" s="47"/>
+      <c r="B23" s="41"/>
       <c r="C23" s="37" t="s">
         <v>253</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="J23" s="28" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="B24" s="47"/>
+      <c r="B24" s="41"/>
       <c r="C24" s="37" t="s">
         <v>254</v>
       </c>
       <c r="D24" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="J24" s="28" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="38" customFormat="1" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="B25" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>422</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>423</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="H25" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="E24" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>314</v>
-      </c>
-      <c r="H24" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>316</v>
-      </c>
-      <c r="J24" s="28" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="44" customFormat="1" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="39" t="s">
-        <v>244</v>
-      </c>
-      <c r="B25" s="48" t="s">
-        <v>340</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>260</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>323</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>324</v>
-      </c>
-      <c r="G25" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="H25" s="42" t="s">
-        <v>321</v>
-      </c>
-      <c r="I25" s="38" t="s">
-        <v>325</v>
-      </c>
-      <c r="J25" s="43" t="s">
-        <v>332</v>
+      <c r="I25" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="B26" s="47" t="s">
-        <v>341</v>
+      <c r="B26" s="41" t="s">
+        <v>328</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="H26" s="27" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="B27" s="47" t="s">
-        <v>341</v>
+      <c r="B27" s="41" t="s">
+        <v>328</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="B28" s="47" t="s">
-        <v>341</v>
+      <c r="B28" s="41" t="s">
+        <v>328</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="28"/>
+        <v>255</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>334</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="H28" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="I28" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="J28" s="28" t="s">
+        <v>338</v>
+      </c>
     </row>
-    <row r="29" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="374" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="41" t="s">
+        <v>329</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="H29" s="27" t="s">
         <v>342</v>
       </c>
-      <c r="C29" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="28"/>
+      <c r="I29" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>341</v>
+      </c>
     </row>
-    <row r="30" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="B30" s="47" t="s">
-        <v>342</v>
+      <c r="B30" s="41" t="s">
+        <v>329</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="28"/>
+        <v>256</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>350</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="H30" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="I30" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="J30" s="28" t="s">
+        <v>353</v>
+      </c>
     </row>
-    <row r="31" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="B31" s="47" t="s">
-        <v>342</v>
+      <c r="B31" s="41" t="s">
+        <v>329</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="28"/>
+        <v>362</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>360</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="H31" s="27" t="s">
+        <v>356</v>
+      </c>
+      <c r="I31" s="24" t="s">
+        <v>359</v>
+      </c>
+      <c r="J31" s="28" t="s">
+        <v>361</v>
+      </c>
     </row>
-    <row r="32" spans="1:10" ht="86" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="409.6" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A32" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="B32" s="47" t="s">
-        <v>341</v>
+      <c r="B32" s="41" t="s">
+        <v>328</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="28"/>
+        <v>257</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="H32" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="I32" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="J32" s="28" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="33" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E33" s="44"/>
+      <c r="G33" s="44"/>
+    </row>
+    <row r="34" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="G34" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="27" fitToHeight="8" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="28" fitToHeight="8" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -9159,7 +12121,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
-    <col min="2" max="2" width="40.83203125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" style="10" customWidth="1"/>
     <col min="3" max="3" width="40.83203125" style="2" customWidth="1"/>
     <col min="4" max="10" width="50.83203125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="10.83203125" style="1"/>
@@ -9169,8 +12131,8 @@
       <c r="A1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="45" t="s">
-        <v>344</v>
+      <c r="B1" s="39" t="s">
+        <v>330</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>7</v>
@@ -9197,69 +12159,111 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="4" customFormat="1" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="5" customFormat="1" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>398</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>397</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="5" customFormat="1" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="14"/>
-    </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="14"/>
-    </row>
-    <row r="4" spans="1:10" s="5" customFormat="1" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>264</v>
-      </c>
       <c r="B4" s="13" t="s">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="14"/>
+        <v>392</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>293</v>
+        <v>393</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -9271,13 +12275,13 @@
     </row>
     <row r="6" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>295</v>
+        <v>394</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="25"/>
@@ -9289,13 +12293,13 @@
     </row>
     <row r="7" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>296</v>
+        <v>395</v>
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="25"/>
@@ -9307,13 +12311,13 @@
     </row>
     <row r="8" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="25"/>
@@ -9323,14 +12327,16 @@
       <c r="I8" s="24"/>
       <c r="J8" s="28"/>
     </row>
-    <row r="9" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C9" s="23"/>
+        <v>329</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>399</v>
+      </c>
       <c r="D9" s="24"/>
       <c r="E9" s="25"/>
       <c r="F9" s="26"/>
@@ -9339,14 +12345,16 @@
       <c r="I9" s="24"/>
       <c r="J9" s="28"/>
     </row>
-    <row r="10" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C10" s="23"/>
+        <v>329</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>409</v>
+      </c>
       <c r="D10" s="24"/>
       <c r="E10" s="25"/>
       <c r="F10" s="26"/>
@@ -9355,14 +12363,16 @@
       <c r="I10" s="24"/>
       <c r="J10" s="28"/>
     </row>
-    <row r="11" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C11" s="23"/>
+        <v>329</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>400</v>
+      </c>
       <c r="D11" s="24"/>
       <c r="E11" s="25"/>
       <c r="F11" s="26"/>
@@ -9371,14 +12381,16 @@
       <c r="I11" s="24"/>
       <c r="J11" s="28"/>
     </row>
-    <row r="12" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="C12" s="37"/>
+        <v>327</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>410</v>
+      </c>
       <c r="D12" s="24"/>
       <c r="E12" s="24"/>
       <c r="F12" s="26"/>
@@ -9387,14 +12399,16 @@
       <c r="I12" s="24"/>
       <c r="J12" s="28"/>
     </row>
-    <row r="13" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C13" s="37"/>
+        <v>329</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>401</v>
+      </c>
       <c r="D13" s="26"/>
       <c r="E13" s="24"/>
       <c r="F13" s="26"/>
@@ -9403,14 +12417,16 @@
       <c r="I13" s="24"/>
       <c r="J13" s="28"/>
     </row>
-    <row r="14" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="C14" s="37"/>
+        <v>328</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>411</v>
+      </c>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
       <c r="F14" s="26"/>
@@ -9419,14 +12435,16 @@
       <c r="I14" s="24"/>
       <c r="J14" s="28"/>
     </row>
-    <row r="15" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C15" s="37"/>
+        <v>328</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>412</v>
+      </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
       <c r="F15" s="26"/>
@@ -9435,14 +12453,16 @@
       <c r="I15" s="24"/>
       <c r="J15" s="28"/>
     </row>
-    <row r="16" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C16" s="37"/>
+        <v>329</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>402</v>
+      </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
       <c r="F16" s="26"/>
@@ -9451,14 +12471,16 @@
       <c r="I16" s="24"/>
       <c r="J16" s="28"/>
     </row>
-    <row r="17" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C17" s="37"/>
+        <v>329</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>413</v>
+      </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -9467,14 +12489,16 @@
       <c r="I17" s="24"/>
       <c r="J17" s="28"/>
     </row>
-    <row r="18" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C18" s="23"/>
+        <v>329</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>403</v>
+      </c>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
@@ -9483,14 +12507,16 @@
       <c r="I18" s="24"/>
       <c r="J18" s="28"/>
     </row>
-    <row r="19" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C19" s="37"/>
+        <v>329</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>408</v>
+      </c>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
@@ -9499,14 +12525,16 @@
       <c r="I19" s="24"/>
       <c r="J19" s="28"/>
     </row>
-    <row r="20" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="C20" s="37"/>
+        <v>329</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>414</v>
+      </c>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
@@ -9515,14 +12543,16 @@
       <c r="I20" s="24"/>
       <c r="J20" s="28"/>
     </row>
-    <row r="21" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="C21" s="37"/>
+        <v>391</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>415</v>
+      </c>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
       <c r="F21" s="26"/>
@@ -9531,14 +12561,16 @@
       <c r="I21" s="24"/>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="C22" s="37"/>
+        <v>329</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>404</v>
+      </c>
       <c r="D22" s="24"/>
       <c r="E22" s="24"/>
       <c r="F22" s="26"/>
@@ -9547,14 +12579,16 @@
       <c r="I22" s="24"/>
       <c r="J22" s="28"/>
     </row>
-    <row r="23" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="C23" s="37"/>
+        <v>327</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>416</v>
+      </c>
       <c r="D23" s="24"/>
       <c r="E23" s="24"/>
       <c r="F23" s="26"/>
@@ -9563,14 +12597,16 @@
       <c r="I23" s="24"/>
       <c r="J23" s="28"/>
     </row>
-    <row r="24" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C24" s="37"/>
+        <v>328</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>417</v>
+      </c>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
       <c r="F24" s="26"/>
@@ -9579,14 +12615,16 @@
       <c r="I24" s="24"/>
       <c r="J24" s="28"/>
     </row>
-    <row r="25" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="C25" s="23"/>
+        <v>328</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>418</v>
+      </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
       <c r="F25" s="26"/>
@@ -9595,14 +12633,16 @@
       <c r="I25" s="24"/>
       <c r="J25" s="28"/>
     </row>
-    <row r="26" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C26" s="37"/>
+        <v>329</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>407</v>
+      </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
       <c r="F26" s="26"/>
@@ -9611,14 +12651,16 @@
       <c r="I26" s="24"/>
       <c r="J26" s="28"/>
     </row>
-    <row r="27" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C27" s="37"/>
+        <v>329</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>405</v>
+      </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
       <c r="F27" s="26"/>
@@ -9627,14 +12669,16 @@
       <c r="I27" s="24"/>
       <c r="J27" s="28"/>
     </row>
-    <row r="28" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="C28" s="37"/>
+        <v>329</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>419</v>
+      </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24"/>
       <c r="F28" s="26"/>
@@ -9643,14 +12687,16 @@
       <c r="I28" s="24"/>
       <c r="J28" s="28"/>
     </row>
-    <row r="29" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="C29" s="37"/>
+        <v>327</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>420</v>
+      </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24"/>
       <c r="F29" s="26"/>
@@ -9659,14 +12705,16 @@
       <c r="I29" s="24"/>
       <c r="J29" s="28"/>
     </row>
-    <row r="30" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="C30" s="37"/>
+        <v>329</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>406</v>
+      </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24"/>
       <c r="F30" s="26"/>
@@ -9675,14 +12723,16 @@
       <c r="I30" s="24"/>
       <c r="J30" s="28"/>
     </row>
-    <row r="31" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="C31" s="37"/>
+        <v>391</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>421</v>
+      </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
       <c r="F31" s="26"/>
@@ -9695,6 +12745,6 @@
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="27" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="28" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Vigil_Content_v2.0.xlsx
+++ b/Vigil_Content_v2.0.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicsmacbook/pCloud Drive/Personal/Vigil/Vigil v2/vigil-build/Vigil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69367205-1F7E-D74C-9187-6B957D8A102D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE57BCF-EFB1-F046-A9C9-D4906950833B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
+    <workbookView xWindow="140" yWindow="660" windowWidth="29160" windowHeight="15060" activeTab="4" xr2:uid="{D95EB6FA-2870-3442-A079-084F9A0CC5D2}"/>
   </bookViews>
   <sheets>
     <sheet name="April" sheetId="3" r:id="rId1"/>
     <sheet name="May" sheetId="2" r:id="rId2"/>
     <sheet name="June" sheetId="4" r:id="rId3"/>
+    <sheet name="July" sheetId="6" r:id="rId4"/>
+    <sheet name="August" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">April!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">August!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">July!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">June!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">May!$1:$1</definedName>
   </definedNames>
@@ -46,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="595">
   <si>
     <t>Hover Links</t>
   </si>
@@ -9479,6 +9483,1161 @@
     </r>
   </si>
   <si>
+    <t>07 June 2026
+Sunday
+Tenth Week • Ordinary Time
+Solemnity: Corpus Christi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">02 June 2026
+Tuesday
+Ninth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Marcellinus and St Peter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, martyrs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">01 June 2026
+Monday
+Ninth Week • Ordinary Time
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Justin Martyr</t>
+    </r>
+  </si>
+  <si>
+    <t>08 June 2026
+Monday
+Tenth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>10 June 2026
+Wednesday
+Tenth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>12 June 2026
+Friday
+Tenth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>15 June 2026
+Monday
+Eleventh Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>17 June 2026
+Wednesday
+Eleventh Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>21 June 2026
+Sunday
+Twelfth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>26 June 2026
+Friday
+Twelfth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>29 June 2026
+Monday
+Thirteenth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>25 June 2026
+Thursday
+Twelfth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>18 June 2026
+Thursday
+Eleventh Week • Ordinary Time</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">09 June 2026
+Tuesday
+Tenth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Columba</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, abbot
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ephrem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, deacon and Doctor of the Church</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">11 June 2026
+Thursday
+Tenth Week • Ordinary Time
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Barnabas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, apostle</t>
+    </r>
+  </si>
+  <si>
+    <t>13 June 2026
+Saturday
+Tenth Week • Ordinary Time
+Solemnity: The Most Sacred Heart of Jesus</t>
+  </si>
+  <si>
+    <t>14 June 2026
+Sunday
+Eleventh Week • Ordinary Time
+Memorial: The Immaculate Heart of the Blessed Virgin Mary</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">16 June 2026
+Tuesday
+Eleventh Week • Ordinary Time
+Optional Memoral: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Richard of Chichester</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, bishop</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">19 June 2026
+Friday
+Eleventh Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Romuald</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, abbot</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">20 June 2026
+Saturday
+Eleventh Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Alban</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, martyr</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">22 June 2026
+Monday
+Twelfth Week • Ordinary Time
+Feast: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Sts John Fisher and Thomas More</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, martyrs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">23 June 2026
+Tuesday
+Twelfth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St. Etheldreda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, abbess</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">24 June 2026
+Wednesday
+Twelfth Week • Ordinary Time
+Solemnity: The Nativity of </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St John the Baptist</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">27 June 2026
+Saturday
+Twelfth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Cyril of Alexandria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, bishop and Doctor of the Church</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">28 June 2026
+Sunday
+Thirteenth Week • Ordinary Time
+Solemnity: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Sts Peter and Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, apostles</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">30 June 2026
+Tuesday
+Thirteenth Week • Ordinary Time
+Optional Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The First Martyrs of the Church of Rome</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>SPIRIT [SPIR-it]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+In the original languages of scripture, the word for spirit carries more than one meaning at once — and that is not an accident.
+The Hebrew </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>ruach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (רוּחַ) means wind, breath and spirit. The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>pneuma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (πνεῦμα) carries the same range. In both cases, what the word holds together is the movement of an invisible force that is known not by being seen but by what it does: the breath that animates a body, the wind that bends the trees, the spirit that moves through and beyond what is merely physical.
+This is why, when the Spirit arrives at Pentecost, it arrives as wind and fire — not as metaphors added afterward to explain something, but as the thing itself in its most recognisable forms. The word was never only spiritual in the modern, ethereal sense. It was always also breath. Always also force.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"When the day of Pentecost had come, they were all together in one place. 
+And suddenly from heaven there came a sound like the rush of a violent wind, and it filled the entire house where they were sitting. 
+Divided tongues, as of fire, appeared among them, and a tongue rested on each of them. 
+All of them were filled with the Holy Spirit and began to speak in other languages, as the Spirit gave them ability."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Acts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2:1–4 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">What arrived at Pentecost did not arrive quietly. It arrived as wind and fire — disruptive, unmistakable, impossible to ignore. The disciples in that room had been waiting, praying and keeping still. They had done everything that could be done from the human side.
+And then something happened that they could not have produced by their own waiting.
+That is the character of the Spirit throughout scripture: it is not generated, it is received. It comes from outside the system. It does not reward effort in the way that effort normally expects to be rewarded. It comes when and how it will — which is not an argument against preparation, but an argument against the assumption that preparation is what causes the arrival.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where in your life have you been trying to generate what can only be received — working to produce a quality of faith, peace or love that is, in the end, a gift? 
+And what would it mean to stop producing and simply become the kind of person through whom the Spirit can move?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Choose one thing today that you have been trying to do in your own strength — a conversation you have been dreading, a habit you have been fighting, a relationship you have been managing — and before you face it, pause and ask the Spirit to go with you into it.
+Not a long prayer. A single breath, and the simplest of requests:
+Come, Holy Spirit.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Veni, Sancte Spiritus.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Spirit does not need elaborate invitation. It needs only the door to be open.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Author · Acts of the Apostles (1st century AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally identified as Luke, a physician and companion of St Paul, and as the author of both the synonymous Gospel and the Acts of the Apostles. He is featured today because the opening of Acts 2 is his account of the Spirit's arrival at Pentecost — the event that closes Eastertide and opens the life of the Church.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Ordinary Time — the long green season in which the life given at Easter and Pentecost is worked into the full, ordinary length of a day.
+This week Vigil has been turning over what faith costs in the open: reason offered honestly, endurance sustained quietly, allegiance declared at price. Today it turns inward. The question is not what you say about God before others, but what you bring to God in full.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">WHOLE [hohl]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Hebrew </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Shema</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — the ancient prayer at the centre of Jewish worship — does not ask for sincerity. It asks for totality. Love God, it says, with your whole heart, your whole soul, your whole strength. In Greek, the word is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>holos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ὅλος): not partly, not in the portions you have set aside for the purpose, but entirely.
+The distinction matters. Sincerity is possible in a divided life. You can mean what you say and still be holding something back — keeping one part of yourself in reserve, one room locked, one loyalty quietly maintained alongside the main one. Holos names what the Shema is actually asking for: not a sincere heart, but an undivided one.
+Wholeness, in this sense, is not a spiritual achievement. It is a direction of travel.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Shema</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> does not ask whether you love God. It asks whether the love has reached the whole of you, your heart, soul, mind, strength. 
+That fourfold list is not decoration. It is the recognition that a person can be genuinely devoted in one part of their life and quietly elsewhere in another: warm in feeling, but cooler in thought; present in prayer, but absent in the decisions that cost something.
+Sincerity, on its own, doesn't close that gap. You can mean what you say and still be holding something back — not in defiance, but simply because that particular part of life has never been brought into the relationship.
+The Shema asks you to notice which part that is. Not to correct it immediately. Just to name it honestly before God.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Is there a capacity — a way you think, or act, or spend yourself — where the love of God has never quite arrived? And what would it mean to bring even that one thing, today, into the open?</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You do not ask us to arrive whole before we come to you.
+You ask us to come.
+Where we have loved you sincerely but partially — present in some capacities, absent in others — receive even that.
+Where there is a part of us we have never quite brought into the open, let the naming of it be enough for now.
+Draw what is still distant in us toward you, not by our effort alone, but by yours.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Shema's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> demand doesn't end with you.  To love God with the whole of yourself is already, in the same breath, to love your neighbour — the two commandments arrive together in the passage, and the scribe who understands them understands them as one movement, not two.
+Today, let the earlier, inward contemplation become something that reaches another person.
+It need not be large: a moment of genuine attention, a kindness that costs a little, a choice that puts someone else's need inside the frame of what you love.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Wholeness is not only what you bring to God. It is what the love of God, received fully, begins to make of how you live toward others.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Jesus answered, "The first is, 'Hear, O Israel: the Lord our God, the Lord is one; you shall love the Lord your God with all your heart, and with all your soul, and with all your mind, and with all your strength.'
+The second is this, 'You shall love your neighbour as yourself.' There is no other commandment greater than these." 
+Then the scribe said to him, "You are right, Teacher; you have truly said that 'he is one, and besides him there is no other'; and 'to love him with all the heart, and with all the understanding, and with all the strength,' and 'to love one's neighbour as oneself,' — this is much more than all whole burnt-offerings and sacrifices." 
+When Jesus saw that he answered wisely, he said to him, "You are not far from the kingdom of God."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mark</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 12:29–34 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Mark, Evangelist (1st century AD)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Traditionally identified as the author of the second Gospel and, in early Christian tradition, as a companion of St Peter. Mark's Gospel is widely regarded as the earliest of the four to have been written. It is notable for its speed and brevity, which makes its rare moments of extended dialogue, including today's exchange between Jesus and the scribe, carry particular weight.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in Ordinary Time — the long season in which what has been given is worked slowly into the grain of a life.
+Today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Boniface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, an English monk who spent fifty years carrying the Christian faith into the forests and kingdoms of what is now Germany, and who died at the edge of a river, preparing to baptise new believers, with his books around him.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FAITHFUL [FAYTH-fəl]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The word has two directions at once, and both matter.
+To be faithful is to trust — to rely on someone or something as steady and true. But it also means to be that steady, true thing for someone else. The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>pistos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (πιστός) holds both senses in a single term: the one who trusts, and the one who can be trusted.
+In the New Testament, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>pistos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is used of God before it is used of human beings. God is pistos — utterly reliable, the one whose word holds — and it is only from that ground that human faithfulness becomes possible at all. We are not generating trustworthiness from inside ourselves. We are reflecting something that already exists.
+This matters because it changes what faithfulness actually looks like. It is not chiefly an achievement or a virtue to be cultivated. It is a response — a long, ordinary, sometimes unnoticed alignment with the one who is faithful first.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">The steadfast love of the Lord never ceases,
+his mercies never come to an end;
+they are new every morning;
+great is your faithfulness.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Lamentations 3:22–23 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You are faithful — not once, at a distance, but new every morning, given again before we have thought to ask.
+Where we have let our commitments become hollow through habit, restore the intention that first made them.
+Where faithfulness has felt too small to matter — too unremarked, too unwitnessed — remind us that you see the long ordinary, and that it is enough.
+Where we are tired of returning to the same ground, give us the grace to return once more.
+We do not ask to be extraordinary. We ask to be faithful — and to trust that in you, those are not so different.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Boniface (c. 675–754 AD).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>English Benedictine monk, bishop and martyr, known as the Apostle of the Germans. The Church remembers him today; he spent the second half of his life reorganising the Church in what is now Germany and the Netherlands, and was killed in Frisia while preparing a group of new converts for baptism — the last act of a half-century of faithfulness to a single commission.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">There is a particular kind of faithfulness that never makes the news. Not the single dramatic moment—the public stand, the costly choice that everyone sees—but the long, unremarkable pattern of showing up: the commitment honoured when no one is watching, the promise kept on a day when keeping it costs something small and unspecifiable.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Boniface's</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> martyrdom is remembered because it was dramatic. But it was the last day of fifty years. The river's edge was not where his faithfulness was formed. It was where a very long pattern reached its end.
+Lamentations says God's faithfulness is new every morning. Not new in the sense of different — new in the sense of given again. Fresh. Renewed. God does not maintain faithfulness by sustaining a single act. He returns to it, daily, as a decision.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where in your life is faithfulness currently asking for the small, unremarkable thing — not the grand gesture, but simply showing up again today? And what would it mean to trust that showing up is enough?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Think of one commitment you made to a person, a practice, a relationship that has become background noise. Not broken, not abandoned, but no longer inhabited with attention.
+Today, return to it once, deliberately. Not by doing something large or visible, but by naming it before God and choosing it again: a single, quiet re-commitment that costs nothing except the decision itself.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Faithfulness is not maintained by the single great act. It is renewed by the daily return.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in Ordinary Time — the long season in which what was given at Easter is worked slowly into the grain of a life.
+Today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Norbert of Xanten</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>: a man whose restless early life was stopped in its tracks by a single moment, and who spent everything that followed learning what it means to be still before God.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">STILL [stil]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Hebrew </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>raphah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (רָפָה) means, literally, to let the hands drop. Stop striving. Release your grip. It is the word behind the line in Psalm 46: "be still, and know that I am God" and it is not a gentle suggestion, but a command addressed to people who are very busy being afraid.
+The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hēsychia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ἡσυχία) carries the same weight: an interior quietness that is not emptiness but attention. 
+Early Christian contemplatives built an entire practice around it — the conviction that stillness before God is not a retreat from life but the most honest way of meeting it.
+To be still, in scripture, is not passivity. It is the decision to stop filling the silence and then to find out what remains when you do.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"God is our refuge and strength,
+a very present help in trouble.
+Therefore we will not fear, though the earth should change,
+though the mountains shake in the heart of the sea;
+though its waters roar and foam,
+though the mountains tremble with its tumult.
+Be still, and know that I am God!"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Psalm 46:1–3, 10a (NRSV)</t>
+    </r>
+  </si>
+  <si>
+    <t>The Psalm does not say: wait until you are less afraid, then be still. It says: be still, and know. The stillness comes first. The knowing follows from it.
+That is a counterintuitive sequence. We tend to assume that certainty — knowing God is present, knowing things will be alright — is the condition for peace. The Psalm reverses it. You do not become still because you know. You come to know because you became still. The knowledge is not the entry point. The stillness is.
+Which means the fear is not disqualifying. The Psalmist is surrounded by roaring water and shaking mountains and writes this anyway. The invitation is not addressed to people who have resolved their fears. It is addressed to people who are inside them.
+Where is the upheaval in your life right now — the thing that is making stillness feel impossible? And what if you tried to be still not after it has resolved, but inside it, in the presence of the God who is already there?</t>
+  </si>
+  <si>
+    <t>Lord,
+You are our refuge and strength — not once the storm has passed, but inside it, where we actually are.
+We confess that we have been waiting for better conditions: for the fear to lift, the noise to stop, the ground to steady beneath us.
+Teach us to be still now, in the middle of what we cannot resolve.
+Let the stillness be not our achievement but our surrender, the moment we stop adding our own noise to what is already loud.
+In the quiet we cannot quite reach, meet us.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">When the noise is at its loudest—not in a quiet moment you have manufactured, but in the middle of whatever is actually happening—stop.
+Pause for thirty seconds. 
+Do not close your eyes or find a better setting. Stay exactly where you are.
+Say the words from the Psalm once, slowly, as an address to yourself from God: "Be still, and know that I am God". 
+Let them land on whatever is causing you disquiet, to race or to be anxious.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Stillness is not a technique for coping. It is how you meet the God who is already present in whatever may be causing you a challenge.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Norbert of Xanten (c. 1080–1134 AD).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>German bishop, founder of the Premonstratensian order, a community of canons committed to contemplative prayer and active ministry. The Church remembers him today; his life turned on a single moment of involuntary stillness — thrown from his horse in a thunderstorm, he lay unable to move and heard, in the silence that followed, a call he could not ignore. Everything he built afterward was grounded in that stillness.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">06 June 2026
 Saturday
@@ -9502,67 +10661,1976 @@
         <rFont val="Georgia"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">, bishop
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>The Blessed Virgin Mary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> on Saturday</t>
-    </r>
-  </si>
-  <si>
-    <t>07 June 2026
+      <t>, bishop</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Today is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Corpus Christi—</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>the Solemnity of the Body and Blood of Christ—the feast on which the Church turns its full attention to the bread and wine at the heart of Christian worship, and asks what they actually are.
+Ordinary Time is barely a week old. This is its first Sunday, and already the season pauses because some things are too important to carry past without stopping.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">For I received from the Lord what I also handed on to you, that the Lord Jesus on the night when he was betrayed took a loaf of bread, and when he had given thanks, he broke it and said, "This is my body that is for you. Do this in remembrance of me." 
+In the same way he took the cup also, after supper, saying, "This cup is the new covenant in my blood. Do this, as often as you drink it, in remembrance of me." 
+For as often as you eat this bread and drink the cup, you proclaim the Lord's death until he comes.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+1 Corinthians 11:23–26 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, the author of 1 Corinthians, does not begin with theology. He begins with transmission: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"I received... I handed on"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">. The account of the Last Supper reaches him not as a text but as something carried person to person from the night it happened.
+That chain has not broken. The words spoken in an upper room in Jerusalem have arrived here, to you, this morning — carried across twenty centuries by people who kept doing what they were asked.
+Anamnēsis is not a technique for making the past feel vivid. It is the claim that what Christ did at that table is not finished. Every time the bread is broken in his name, the distance between that night and this morning closes. Not as metaphor. As the thing itself.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Which part of your life has become commemoration rather than encounter — kept faithfully, observed correctly, but no longer quite inhabited? And what would it mean to bring even that, today, to the table?</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You do not ask us to arrive with our attention restored and our devotion intact. You ask us to come.
+We confess that what was once alive in us has sometimes grown habitual — the prayer said, the bread broken, the faith held, but not always inhabited.
+Today, on this feast of your body and blood, we bring what has drifted. Not polished, not resolved — just here.
+Receive us as we are. And in the receiving, make the distance close.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Paul (c. 5–c. 64 AD)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Apostle, missionary and author of letters central to the New Testament. His first letter to the Corinthians was written around 53–54 AD to a young, fractious Christian community in the port city of Corinth in Greece. His account of the Last Supper is the earliest written record of it that we have, predating the writing of the Gospels by at least a decade.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The chain </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> describes—I received, I handed on—did not end with the first disciples. Every person who has carried the faith to someone else is a link in it. 
+You are in that chain because someone before you kept doing what they were asked.
+Today, name that person to God. Not in a general thanksgiving, but specifically: the one whose faithfulness, spoken or unspoken, reached you. 
+Hold them before God for a moment, and let the gratitude be particular and unique.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>To remember, in the fullest sense, is to know whose hands passed this to you and to hold them, in turn, before the one who began it.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">REMEMBER [rih-MEM-ber]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To remember, in ordinary English, means to call something to mind. To reach back and retrieve what was. But the word at the centre of </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Corpus Christi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is doing something different.
+The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>anamnēsis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (ἀνάμνησις) is the word Jesus uses at the Last Supper when he says "do this in remembrance of me." In Greek usage, anamnēsis is not about mental recall. It described the act of making a past event present and effective again: not a thought, but a re-enactment; not nostalgia, but the past arriving into the present with its full force intact.
+When Christians gather and break bread in Christ's name, they are not commemorating someone who is absent. They are doing what he asked. And in doing it, the distance between then and now collapses.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Ordinary Time — the long green season that follows the great feasts, when what has been given is carried into the full, ordinary length of a day.
+There are no feasts today. No saints to commemorate, no solemnity to mark the date. Just Monday, and the invitation to receive what the season quietly insists on: that the ordinary days are not gaps between the important ones.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Surely goodness and mercy shall follow me
+all the days of my life,
+and I shall dwell in the house of the Lord
+my whole life long."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Psalm 23:6 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Psalm does not say mercy might follow, or mercy could follow. It says surely. That word is doing quiet but serious work. It is not an observation about what tends to happen. It is a declaration. The kind you make when you have decided to trust something before the evidence is complete.
+Psalm 23 moves through a valley of deep darkness before it arrives at the line you have just read. The "surely" is not the confidence of someone who has never been afraid. It is the confidence of someone who has been afraid and yet decided, in the middle of it, what to believe about God anyway.
+That is what mercy looks like when it is received rather than simply hoped for. It is not a feeling, but a decision to stop treating God's commitment as provisional.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Somewhere in your life you have been treating God's mercy as conditional — something to be earned back, re-qualified for, waited on. What would it mean to say surely about it today, before the evidence feels complete?</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You do not offer mercy provisionally. It is not withheld until we have done enough to deserve it, nor withdrawn when we have failed and not yet recovered.
+Yet we confess that we have treated it that way: earning, re-qualifying, waiting for a sign that your commitment to us still holds.
+Meet us here — not ahead of where we are, but in the place we have actually reached.
+And let what you have already given be enough to take the next step.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Most of us approach mercy like a verdict still under appeal: we keep building the case for why we might deserve it before we allow ourselves to receive it.
+Today, before the day goes any further, write one sentence — by hand if possible, on paper or in a notes app if not. Not a prayer, not a reflection. A verdict. 
+Finish this:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>God's mercy toward me is not conditional on...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+...and then name the specific thing you have been using as the condition. The failure. The habit. The gap between who you are and who you think you need to be before God's mercy fully applies.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Write it. Then read it back. What you have written is not a confession awaiting a response. It is the ground mercy has already covered.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">MERCY [MUR-see]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Hebrew word for mercy is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hesed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (חֶסֶד) and English has never quite managed to translate it. 
+"Mercy" gets close and so does "steadfast love," but neither captures the sense of a loyalty that doesn't depend on whether it is deserved.
+In the Hebrew Bible, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hesed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is the faithfulness God brings to his bond with Israel, even when Israel has failed to keep their side of it.
+His </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>hesed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> does not waver; it is not conditional on the behaviour of the one receiving it.
+Which means mercy, in the biblical sense, is not a softening of justice. It is not God looking away. It is God remaining present and committed to a relationship the other party has already broken. Not reluctantly, but as an expression of his deepest character.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in Ordinary Time — the long green season in which what was given at Easter and Pentecost is carried into the full, ordinary length of a life.
+Today the Church remembers two figures who knew that the most honest response to God is not silence: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Columba</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, who crossed the sea to a windswept island and spent his life there in prayer and mission, and </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ephrem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, who decided that theology was too large for prose and wrote it in hymns instead.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lord,
+You are worthy of praise before the circumstances improve, before the fear lifts, before we feel ready to offer it.
+Where we have been waiting for better conditions, forgive us.
+Teach us the sacrifice </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ephrem</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> knew: to open our mouths before the siege lifts, and to find, in the act of declaring what is true about you, that it is enough.
+Let praise become not what escapes us when life is easy, but what we choose when it is not.
+In Christ's name, Amen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Columba (521–597 AD)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Irish monk, abbot and missionary. The Church remembers him today; he left Ireland in 563 and founded a monastery on the island of Iona, off the west coast of Scotland, which became one of the great centres of Celtic Christian scholarship and mission.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ephrem of Syria (c. 306–373 AD)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Syrian deacon, theologian and poet, Doctor of the Church. The Church remembers him today; he wrote almost entirely in verse, on the conviction that hymns and poetry could carry theological truths that prose could not. He is sometimes called the Harp of the Holy Spirit.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Author · Letter to the Hebrews (1st century AD)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>A New Testament letter traditionally attributed to St Paul (though this is disputed among scholars), addressed to early Jewish Christians and concerned with the fulfilment of the old covenant in Christ. It is featured today because Hebrews 13 gives the day's word its most precise definition: praise not as mood or overflow, but as a deliberate sacrifice offered to God through Christ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>PRAISE [prayz]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To praise is not to perform enthusiasm. It is to declare, out loud, that something is worth more than your silence.
+The Hebrew </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>halal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (הָלַל)—the root of hallelujah—means to make a noise about what is real: to break the quiet with the fact of what you have found.
+It is not a mood. It is a decision. 
+The Letter to the </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Hebrews</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> calls it a sacrifice as "the fruit of lips that confess his name" because genuine praise is not what spills out when everything is going well. It is what you choose to offer when it would be equally possible to say nothing.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ephrem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> of Syria understood this better than almost anyone. He was a theologian but he expressed his theology in poetry and song and on the conviction that some truths are too large for argument and can only be carried in the mouth as music.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>"Through him, then, let us continually offer a sacrifice of praise to God, that is, the fruit of lips that confess his name. 
+Do not neglect to do good and to share what you have, for such sacrifices are pleasing to God."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Hebrews</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 13:15–16 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Most of us treat praise as a response to good news. Something lifts, something resolves, something goes the way we hoped and gratitude becomes easy. That is not what the Letter to the </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Hebrews</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is describing.
+The word it uses is sacrifice. In the world the writer inhabited, a sacrifice was not what you gave from your surplus. It was what you brought to the altar at cost. It was an offering that required something of you before it left your hands.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ephrem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> spent thirty years writing theology as poetry and hymns, in a Syrian city at the edges of empire, under repeated military threat. The praise was not a byproduct of easy circumstances. It was his most serious theological act: the decision, made daily, that God was worth declaring before the situation improved.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where has praise gone quiet in you not from doubt, but because nothing has happened yet to justify it? That silence is not failure. Look for the one thing that remains true about God even inside he silence. Start there.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ephrem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> believed that some truths about God are too large for prose. They need to be carried in the body, in breath, in sound. That is why he wrote hymns rather than treatises.
+At some point today, sing something. It does not need to be loud or performed. It can be a single line of a hymn, a song you half-remember, even a phrase from today's prayer given more breath than usual. 
+If now is not the moment, don't skip it. Set a reminder for later on your phone, for a place where you can be alone with it.
+You see, when praise moves from thought to sound, something physical happens: your breath deepens, your chest opens and your body commits to what your mind was only holding. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sound is not decoration added to the meaning. For </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ephrem</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, speaking or singing a truth about God was itself an act of knowing that truth more fully — the body completing what the mind had only begun.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"So if you have been raised with Christ, seek the things that are above, where Christ is, seated at the right hand of God. 
+Set your minds on things that are above, not on things that are on earth, for you have died, and your life is hidden with Christ in God. 
+When Christ who is your life is revealed, then you also will be revealed with him in glory."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Colossians 3:1–4 (NRSV)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">There is likely someone in your life whose faith you have never directly witnessed — someone who believes, or struggles to believe, quietly and without announcement. You may not even be certain they would call themselves a Christian, a believer or a person of faith.
+Today, hold that person before God. Not with a request attached, not asking for anything on their behalf. Simply name them, and let the fact that God sees in them what you cannot see be enough.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>To pray for someone's hiddenness — the part of them held in God that you will never fully know — is one of the most honest prayers there is.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Ordinary Time, the long stretch of the Christian year with no fixed event to mark it, no feast at the centre, just the ordinary length of a day and whatever God might be doing in it.
+Which turns out to be exactly the right kind of day to ask what God sees that nobody else does.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HIDDEN [HID-ən]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+To hide something is to place it out of sight. But the question the New Testament keeps asking is: out of reach of whose sight — and why?
+The Greek </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>kryptō</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (κρύπτω) describes something placed beyond ordinary sight, not because it is shameful but because it belongs to a different kind of attention. 
+Jesus tells his followers to pray behind a closed door and to give without letting the left hand know what the right hand is doing. The point is not secrecy for its own sake. It is that some things are addressed to God alone, and the moment they acquire an audience, they become something else.
+St Paul's letter to the Colossians puts it plainly: "</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>your life is hidden with Christ in God</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>." 
+Not hidden from God but hidden in him. The deepest thing about a person is held inside the life of God rather than on display to the world, and that is not a loss but a kind of safety.</t>
+    </r>
+  </si>
+  <si>
+    <t>The passage makes a strange claim: that the life of faith is simultaneously real and not yet visible. You have died, it says, and your life is hidden. 
+Not lost — hidden. Held somewhere the eye cannot reach, waiting for a disclosure that has not happened yet.
+That puts you in an odd position. The most important thing about you, by this account, is precisely the thing you cannot point to or demonstrate. You cannot produce it as evidence of anything. You can only live from it.
+This is not a comfortable idea for a world that measures worth by what is visible and verifiable. But it is also, in a specific way, a relief. 
+After all, if your life is held in God rather than on display, then its value does not depend on whether anyone has noticed.</t>
+  </si>
+  <si>
+    <t>Lord,
+We confess that we have been working hard to be seen, by others, and sometimes by ourselves, as though the reality of our faith depended on its visibility.
+Teach us to trust what we cannot demonstrate: that our lives are held in you, beyond the reach of every verdict except yours.
+Where we have measured our worth by what others have noticed, free us from that self- audit.
+Where we have struggled to believe in what cannot be seen, remind us that you see it, and that is enough.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Paul (c. 5–c. 64 AD)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Apostle, missionary and author of letters central to the New Testament. He is featured today because his letter to the Colossians (which some scholars consider to be the work of a close associate writing in his name) gives the day's word its defining expression: that the life of the baptised is not on display to the world but held, already and securely, within the life of God.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Ordinary Time — the long green season in which the life of faith is carried into the ordinary length of a day.
+Today the Church remembers St Barnabas, an apostle whose very name was given to him by those who knew him best. It was not his birth name. It was a description. And today, Vigil turns to what it describes.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ENCOURAGE [en-KUR-ij]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Most of us know what it feels like to be encouraged by someone — the moment a person said or did something that made it possible to keep going. It probably didn't feel momentous at the time. It rarely does.
+The Greek word beneath it is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>paraklēsis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (παράκλησις): a calling-alongside. It is the same root as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>paraklētos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, the name Jesus gives the Holy Spirit , the Advocate, the one who comes to stand beside you.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Paul</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> writes that God is "the Father of all </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>paraklēsis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">",  the origin from which every genuine act of encouragement flows. Which reframes something you may have taken for granted. The moment someone placed themselves alongside you and made it possible to continue — that was not merely a kindness. It was a reflection of something in the character of God.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Barnabas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> didn't have a theology of encouragement. He just kept doing it, until the people around him named what they saw.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">When he had come to Jerusalem, he attempted to join the disciples; and they were all afraid of him, for they did not believe that he was a disciple. 
+But </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Barnabas</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> took him, brought him to the apostles, and described for them how on the road he had seen the Lord, who had spoken to him, and how in Damascus he had spoken boldly in the name of Jesus.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Acts 9:26–27 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Barnabas stepped in because, as the reader has just seen, the disciples were afraid of Paul. No one else in that room was willing to move first.
+There is almost certainly a moment in your own past where someone did something similar — not dramatic, not costly in any obvious way, but precisely placed. A word said at the right time, a presence that arrived before it was asked for, a decision to move toward someone when the easier thing was to hold back. 
+It may have happened to you directly. You may simply have witnessed it and never forgotten it.
+That kind of act has a particular quality to it. It does not feel like it fully belongs to the person who did it. It feels, in some way that is hard to articulate, given through them rather than by them.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Bring that person, and that moment, before God. Not to analyse it — just to hold it there, and let it say what it already knows.</t>
+    </r>
+  </si>
+  <si>
+    <t>Father of all encouragement,
+We confess that we have often received the gift without seeing the giver — accepted what was offered through another person and called it luck, or kindness, or coincidence.
+Open our eyes to what has already reached us. For the one who moved toward us when it would have been easier not to, for the word that arrived before we knew we needed it — we give you thanks.
+Make us, in our turn, the kind of people who move first. Not from duty, but because we have begun to understand where that impulse comes from.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">There is someone in your life who is in the position Paul was in that room: present, but not yet vouched for. Not necessarily in disgrace — just not yet accompanied.
+Maybe it's someone who has arrived somewhere new and doesn't yet know anyone. Maybe it's a colleague no one has quite drawn in. Or maybe it's a family member whose recent history has made others cautious.
+You already know who it is. The reason you haven't moved is probably reasonable. St Barnabas's reasons for holding back would have been reasonable too.
+Before the day ends, do one small thing in their direction. Not a grand gesture — Barnabas simply told the truth about what he had seen. A message, a introduction, a moment of genuine attention that costs you only the decision to give it.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>The formation here is not in the act itself but in what it requires you to override: the calculation that says it is not your place to move first. Paraklēsis begins precisely there.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Barnabas (d. c. 61 AD)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Apostle and early missionary, born Joseph of Cyprus. The Church remembers him today. He travelled with Paul on the first missionary journey through Asia Minor and Cyprus, later parted from him, and tradition holds that he was martyred in Cyprus. He was not one of the original Twelve, but the early church accorded him the title of apostle in recognition of the range and cost of what he did.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+St Paul (c. 5–c. 64 AD)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Apostle, missionary and author of letters central to the New Testament. He is featured today not as a writer but as the person Barnabas stood up for: a former persecutor of the church whose conversion the Jerusalem disciples had good reason to distrust, and whose entire subsequent ministry depended, at this early moment, on one person being willing to speak for him.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Ordinary Time — the long green season with no solemnity to anchor it, just Friday at the end of a working week.
+Tomorrow the Church keeps the feast of the Sacred Heart of Jesus. Today, on the threshold of that, Vigil turns to the word that makes it possible to stand before such a love at all.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">RESTORE [reh-STOR]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Hebrew word beneath this is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>chadash</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (חָדַשׁ) — to make new, to renew, to bring something back to what it was always meant to be. It is not the language of repair. Repair fixes what broke. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Chadash</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> assumes there was an original condition worth returning to, and that condition is still the destination.
+The Psalms reach for it at moments of greatest need. Not as a self-improvement project and not as something the speaker can produce from inside themselves. The initiative belongs entirely to God. The person praying is not the agent of their own restoration. They are the thing held in hands that know what it was made to be.
+That is a different kind of hope from the one we usually carry. It does not depend on having enough left to work with.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Create in me a clean heart, O God,
+and put a new and right spirit within me.
+Do not cast me away from your presence,
+and do not take your holy spirit from me.
+Restore to me the joy of your salvation,
+and sustain in me a willing spirit."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Psalm 51:10–12 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+We come to you not because the distance feels small but because we have nowhere else to go.
+We have let things diminish quietly, not through great rebellion but through the long drift of ordinary days.
+Do not cast us away from your presence.
+Restore to us what we were made to be: not a better version of what we have become but the thing you had in mind from the beginning.
+We do not ask from strength. We ask because we are still here, still turning toward you and we trust that is enough.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Chadash</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">—to make new—is not the language of addition. It does not ask you to take something on. It asks what was already there to be renewed.
+Think of one practice, habit or commitment that belonged to your life with God and has quietly lapsed. 
+Not something that was abandoned dramatically but rather something that was just set down somewhere and not picked back up. 
+It might be small: a particular time of quiet, a way of beginning the day, a form of prayer that once meant something.
+Do that one thing today. Not as a resolution to continue it. Not with any promise attached. Just once, today, as a single act of returning.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Restoration does not require a plan. It requires a first step taken before the plan exists.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Psalm contains a fear that the request for restoration might be refused:  "do not cast me away from your presence." 
+That line is easy to read past, but it is doing serious work. The Psalmist is not certain the door is still open. They are asking, alongside the request itself, for permission to ask.
+That fear is more common than it is usually admitted. Not dramatic doubt, but a quiet sense that the distance between you and God has become, through accumulation rather than intention, too large to close from your side.
+The Psalmist's answer to that fear is the act of praying it. The one who fears they have been cast away is still addressing God directly. The prayer is itself the evidence that the door has not closed.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Is there a fear underneath your praying? A sense that the distance has grown too wide or that what you are asking has been asked too many times already? Let the fact that you are still praying be the first answer to that fear.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Author · Psalm 51 (c. 6th-5th century BC)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally attributed to King David as being written after the prophet Nathan confronted him over his adultery with Bathsheba. This attribution was most likely added by a later editor rather than being part of the original poem that was most likely composed during—or just after—the Babylonian exile.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Ordinary Time, the long green season in which the life of faith is carried into the full, ordinary length of a day. Today that season pauses.
+The Church keeps the Solemnity of the Most Sacred Heart of Jesus — one of the great feasts of the Christian year, and one of the most personal. It does not celebrate an event in the life of Christ so much as the interior of it: the love that drove everything he did, located in a body that could be touched, and wounded, and opened.
+Today Vigil turns to the word that names what that love looks like when it moves.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>COMPASSION [kəm-PASH-ən]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Greek word is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>splagchnizomai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (σπλαγχνίζομαι) — and yes, it is exactly as difficult to say as it looks! 
+It comes from </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>splanchna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, the inward parts of the body, the organs of the gut. When the Gospels say that Jesus was moved with compassion, they are not reaching for a polite word for sympathy. They are describing something that happens before the will has deliberated: a physical movement, a response that originates deeper than thought.
+This matters because compassion, in the New Testament, is not primarily an attitude. It is the movement of the whole person toward another's suffering, arriving before it is chosen.
+The Sacred Heart points here. What the feast holds up is not an abstraction called divine love. It is a heart: particular, located, capable of being moved and of being pierced. The compassion of Christ is not a policy of benevolence. It is the response of someone who feels the full weight of what he is looking at.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+We confess that we have spent much of our faith preparing what to bring. Arranging our requests. Rehearsing our reasons. Making ourselves presentable before you.
+We had not quite believed that the sight of us, as we are, was already enough.
+Receive what we have not known how to ask for: the grief carried quietly, the need not yet formed into words, the part of us walking behind a coffin with nothing else to offer.
+Meet us there, as you met her. Not because we have asked well, but because you have seen.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Go back to the passage from Luke. Read it again, slowly, as if you do not know how it ends.
+This time, do not read it as theology or as history. Read it as a scene you are standing inside. Notice where you place yourself. Are you in the crowd? Are you the widow? Are you one of the bearers, suddenly told to stop?
+Stay with whichever figure you find yourself beside, and ask one question: what does it feel like to be that person at the moment Jesus arrives?
+Do not force an answer. Do not turn it into a lesson. Simply stay inside the scene long enough for something to surface that you did not expect — a feeling, a recognition, a detail that catches on something in your own life.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>That is the practice. Nothing more is required.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Luke, Evangelist (1st century AD)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Traditionally identified as the author of the third Gospel and the Acts of the Apostles, and as a physician and companion of St Paul. Of the four evangelists, Luke records more instances of Jesus being moved with compassion than any other, and the account of the widow at Nain appears nowhere else in the Gospels. There is something fitting in that: a physician's eye for the suffering body, turned toward the one moment in scripture where divine compassion moves without being asked.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Soon afterwards he went to a town called Nain, and his disciples and a large crowd went with him. 
+As he approached the gate of the town, a man who had died was being carried out. 
+He was his mother's only son, and she was a widow; and with her was a large crowd from the town. 
+When the Lord saw her, he had compassion for her and said to her, "Do not weep." 
+Then he came forward and touched the bier, and the bearers stood still. 
+And he said, "Young man, I say to you, rise!" 
+The dead man sat up and began to speak, and Jesus gave him to his mother.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Luke</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 7:11–15 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The widow at Nain did not ask for anything. She was not praying, not petitioning, not even looking at Jesus. She was walking behind a coffin. What moved him was not her faith or her request. It was simply the sight of her.
+That is worth sitting with. 
+Most of us approach God with something prepared: a request, a confession, a reason for being there. The assumption, usually unexamined, is that God responds to what we bring. This passage quietly runs that the other way. The compassion moves first. Before the widow has done anything except grieve, she has already been seen.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Where in your life have you been grieving without asking — carrying something to God only in the sense that you are carrying it at all? 
+What might it mean to know that the sight of you, exactly as you are, is already enough to move him?</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Ordinary Time — the long season with no fixed event at its centre, just the ordinary length of a day and whatever God is doing in it.
+Today the Church keeps a memorial to the Immaculate Heart of Mary: not an event in her life, but the interior quality she brought to it. A life in which very little was explained in advance, and in which she kept saying yes.
+Today Vigil turns to the word that made that possible.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">TRUST [trust]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+The Hebrew batach (בָּטַח) means to lean your full weight on something — not cautious confidence, but the kind of reliance that commits before the outcome is known. It is the word used when a person has stopped calculating whether the ground will hold and simply stands on it.
+The book of Proverbs places batach in direct contrast with self-reliance: trust in the Lord with all your heart, it says, and do not lean on your own understanding. The contrast matters. Batach is not the absence of intelligence. It is the decision about where, finally, to place your weight — on what you can work out for yourself, or on the one who knows more than you do.
+That decision is rarely made once. It is made again every time the ground feels uncertain.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Blessed are those who trust in the Lord,
+whose trust is the Lord.
+They shall be like a tree planted by water,
+sending out its roots by the stream.
+It shall not fear when heat comes,
+and its leaves shall stay green;
+in the year of drought it is not anxious,
+and it does not cease to bear fruit."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Jeremiah 17:7–8 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">There is a specific texture to distrust that is worth naming. It is not usually dramatic. It does not announce itself as a loss of faith. It looks, most of the time, like competence — the quiet decision to handle things yourself, to keep options open, to wait until you are more certain before committing.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Batach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — placing your full weight — is the opposite of kept options. You cannot lean completely on something while simultaneously maintaining a position from which you could step back. The weight either goes down or it doesn't.
+That is not a call to recklessness. The tree does not uproot itself to find the water. It grows toward it, steadily, in the one place it was planted.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>What if you stop managing your relationship with God from a slight distance, and simply put your weight down?</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord,
+You do not ask us to understand before we trust, but rather that we place our weight on what will hold.
+Where we have kept our options open,
+where we have called our caution wisdom
+and managed what we should have surrendered —
+meet us there.
+Grow in us the kind of trust that was formed before the drought came, 
+so that when the pressure arrives, there is something to draw on.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pick one area of your life where you have been doing the work that trust should be doing — monitoring, re-checking, running the same anxious calculation on a loop. Not because vigilance is wrong, but because at some point the monitoring became a substitute for putting your weight down.
+For the next hour, deliberately stop checking that one thing. Not permanently. Just for an hour, as a single act of practised trust.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Notice what surfaces when the checking stops. That is useful information about where your weight actually is — and where batach is still being asked of you</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jeremiah (c. 7th–6th century BC). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>A prophet active in Jerusalem in the decades before and during the Babylonian conquest of Judah, which ended in the destruction of the Temple and the exile of much of the population in 586 BC. The passage today comes from a section setting two kinds of life in contrast: one rooted in human self-reliance, one rooted in God. He was writing for people whose world was about to collapse. The image of the tree that keeps bearing fruit through drought was not an abstraction.</t>
+    </r>
+  </si>
+  <si>
+    <t>CH-0701</t>
+  </si>
+  <si>
+    <t>CH-0702</t>
+  </si>
+  <si>
+    <t>CH-0703</t>
+  </si>
+  <si>
+    <t>CH-0704</t>
+  </si>
+  <si>
+    <t>CH-0705</t>
+  </si>
+  <si>
+    <t>CH-0706</t>
+  </si>
+  <si>
+    <t>CH-0707</t>
+  </si>
+  <si>
+    <t>CH-0708</t>
+  </si>
+  <si>
+    <t>CH-0709</t>
+  </si>
+  <si>
+    <t>CH-0710</t>
+  </si>
+  <si>
+    <t>CH-0711</t>
+  </si>
+  <si>
+    <t>CH-0712</t>
+  </si>
+  <si>
+    <t>CH-0713</t>
+  </si>
+  <si>
+    <t>CH-0714</t>
+  </si>
+  <si>
+    <t>CH-0715</t>
+  </si>
+  <si>
+    <t>CH-0716</t>
+  </si>
+  <si>
+    <t>CH-0717</t>
+  </si>
+  <si>
+    <t>CH-0718</t>
+  </si>
+  <si>
+    <t>CH-0719</t>
+  </si>
+  <si>
+    <t>CH-0720</t>
+  </si>
+  <si>
+    <t>CH-0721</t>
+  </si>
+  <si>
+    <t>CH-0722</t>
+  </si>
+  <si>
+    <t>CH-0723</t>
+  </si>
+  <si>
+    <t>CH-0724</t>
+  </si>
+  <si>
+    <t>CH-0725</t>
+  </si>
+  <si>
+    <t>CH-0726</t>
+  </si>
+  <si>
+    <t>CH-0727</t>
+  </si>
+  <si>
+    <t>CH-0728</t>
+  </si>
+  <si>
+    <t>CH-0729</t>
+  </si>
+  <si>
+    <t>CH-0730</t>
+  </si>
+  <si>
+    <t>CH-0731</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">31 July 2026
+Friday
+Seventeenth Week • Ordinary Time
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ignatius of Loyola</t>
+    </r>
+  </si>
+  <si>
+    <t>"He came to his hometown and began to teach the people in their synagogue, so that they were astounded and said, 
+“Where did this man get this wisdom and these deeds of power? Is not this the carpenter's son? Is not his mother called Mary? And are not his brothers James and Joseph and Simon and Judas? And are not all his sisters with us? Where then did this man get all this?”
+And they took offense at him. But Jesus said to them, “Prophets are not without honor except in their own country and in their own house.”
+And he did not do many deeds of power there, because of their unbelief.
+Matthew 13:54–58 — NRSV</t>
+  </si>
+  <si>
+    <t>Lord,
+You know each person entirely, and your knowledge of them is never finished.
+We make our judgements quickly, and we hold them for years.
+Where we have set the worth of another too low, give us grace to look again.
+Teach us to receive the people we already think we know, as you receive them.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">St Ignatius of Loyola (c. 1491–1556 AD). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Basque soldier turned priest, founder of the Society of Jesus (the Jesuits) and author of the Spiritual Exercises, a structured method of prayer and discernment now used well beyond his own tradition. The Church remembers him today; the Exercises rest on the conviction that a person's judgement of what things are worth is precisely what needs healing.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in Ordinary Time, on the Friday of its seventeenth week, and today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Ignatius of Loyola</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, a soldier who spent his early life building exactly the sort of reputation that we seek with our wordly life.
+Ordinary Time has no festival to lift it, which makes it a fair stretch of the year in which to ask what things are actually worth.</t>
+    </r>
+  </si>
+  <si>
+    <t>The people who had known Jesus longest were the ones who could not receive him. 
+Their familiarity with him had already done its work: they had settled what he was worth years before and nothing that happened in the synagogue that day was going to shift it. 
+The line that follows is the one to sit with, because the low estimate did not only wound him, it narrowed what could happen in the place at all. 
+Where have you settled the worth of someone you see most days—whether a colleague or a relative or a friend—and stopped expecting anything more from them? Bring that person to God today, and ask to be shown the worth that God sees in them.</t>
+  </si>
+  <si>
+    <t>Write down the names of the 3 people you are physically near during the course of a normal week. 
+Beside each name, write the one sentence you would use to sum that person up if someone asked you today. 
+Read the 3 sentences back and work out roughly when each was written, not on the page but in you.
+Hand the list to God, not as a confession but as three estimates you are willing to have corrected.</t>
+  </si>
+  <si>
+    <t>CH-0801</t>
+  </si>
+  <si>
+    <t>CH-0802</t>
+  </si>
+  <si>
+    <t>CH-0803</t>
+  </si>
+  <si>
+    <t>CH-0804</t>
+  </si>
+  <si>
+    <t>CH-0805</t>
+  </si>
+  <si>
+    <t>CH-0806</t>
+  </si>
+  <si>
+    <t>CH-0808</t>
+  </si>
+  <si>
+    <t>CH-0809</t>
+  </si>
+  <si>
+    <t>CH-0810</t>
+  </si>
+  <si>
+    <t>CH-0811</t>
+  </si>
+  <si>
+    <t>CH-0812</t>
+  </si>
+  <si>
+    <t>CH-0813</t>
+  </si>
+  <si>
+    <t>CH-0814</t>
+  </si>
+  <si>
+    <t>CH-0815</t>
+  </si>
+  <si>
+    <t>CH-0816</t>
+  </si>
+  <si>
+    <t>CH-0817</t>
+  </si>
+  <si>
+    <t>CH-0818</t>
+  </si>
+  <si>
+    <t>CH-0819</t>
+  </si>
+  <si>
+    <t>CH-0820</t>
+  </si>
+  <si>
+    <t>CH-0821</t>
+  </si>
+  <si>
+    <t>CH-0822</t>
+  </si>
+  <si>
+    <t>CH-0823</t>
+  </si>
+  <si>
+    <t>CH-0824</t>
+  </si>
+  <si>
+    <t>CH-0825</t>
+  </si>
+  <si>
+    <t>CH-0826</t>
+  </si>
+  <si>
+    <t>CH-0827</t>
+  </si>
+  <si>
+    <t>CH-0828</t>
+  </si>
+  <si>
+    <t>CH-0829</t>
+  </si>
+  <si>
+    <t>CH-0830</t>
+  </si>
+  <si>
+    <t>CH-0831</t>
+  </si>
+  <si>
+    <t>CH-0807</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1 August 2026
+Saturday
+Seventeenth Week • Ordinary Time
+Memorial: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Alphonsus Liguori</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> bishop and doctor of the Church</t>
+    </r>
+  </si>
+  <si>
+    <t>2 August 2026
 Sunday
-Tenth Week • Ordinary Time
-Solemnity: Corpus Christi</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">02 June 2026
+Eighteenth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <t>3 August 2026
+Monday
+Eighteenth Week • Ordinary Time</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4 August 2026
 Tuesday
-Ninth Week • Ordinary Time
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Marcellinus and St Peter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, martyrs</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">01 June 2026
-Monday
-Ninth Week • Ordinary Time
+Eighteenth Week • Ordinary Time
 Memorial: </t>
     </r>
     <r>
@@ -9573,111 +12641,41 @@
         <rFont val="Georgia"/>
         <family val="1"/>
       </rPr>
-      <t>St Justin Martyr</t>
-    </r>
-  </si>
-  <si>
-    <t>08 June 2026
-Monday
-Tenth Week • Ordinary Time</t>
-  </si>
-  <si>
-    <t>10 June 2026
+      <t>St John Vianney</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, priest</t>
+    </r>
+  </si>
+  <si>
+    <t>5 August 2026
 Wednesday
-Tenth Week • Ordinary Time</t>
-  </si>
-  <si>
-    <t>12 June 2026
+Eighteenth Week • Ordinary Time
+Optional Memorial: The Dedication of the Basilica of St Mary Major in Rome</t>
+  </si>
+  <si>
+    <t>6 August 2026
+Thursday
+Eighteenth Week • Ordinary Time
+Feast: The Transfiguration of the Lord</t>
+  </si>
+  <si>
+    <t>7 August 2026
 Friday
-Tenth Week • Ordinary Time</t>
-  </si>
-  <si>
-    <t>15 June 2026
-Monday
-Eleventh Week • Ordinary Time</t>
-  </si>
-  <si>
-    <t>17 June 2026
-Wednesday
-Eleventh Week • Ordinary Time</t>
-  </si>
-  <si>
-    <t>21 June 2026
-Sunday
-Twelfth Week • Ordinary Time</t>
-  </si>
-  <si>
-    <t>26 June 2026
-Friday
-Twelfth Week • Ordinary Time</t>
-  </si>
-  <si>
-    <t>29 June 2026
-Monday
-Thirteenth Week • Ordinary Time</t>
-  </si>
-  <si>
-    <t>25 June 2026
-Thursday
-Twelfth Week • Ordinary Time</t>
-  </si>
-  <si>
-    <t>18 June 2026
-Thursday
-Eleventh Week • Ordinary Time</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">09 June 2026
-Tuesday
-Tenth Week • Ordinary Time
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Columba</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">, abbot
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Ephrem</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, deacon and Doctor of the Church</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">11 June 2026
-Thursday
-Tenth Week • Ordinary Time
+Eighteenth Week • Ordinary Time
+Optional Memorial: St Sixtus II, pope, and companions, martyrs</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">8 August 2026
+Saturday
+Eighteenth Week • Ordinary Time
 Memorial: </t>
     </r>
     <r>
@@ -9688,253 +12686,104 @@
         <rFont val="Georgia"/>
         <family val="1"/>
       </rPr>
-      <t>St Barnabas</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, apostle</t>
-    </r>
-  </si>
-  <si>
-    <t>13 June 2026
-Saturday
-Tenth Week • Ordinary Time
-Solemnity: The Most Sacred Heart of Jesus</t>
-  </si>
-  <si>
-    <t>14 June 2026
-Sunday
-Eleventh Week • Ordinary Time
-Memorial: The Immaculate Heart of the Blessed Virgin Mary</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">16 June 2026
-Tuesday
-Eleventh Week • Ordinary Time
-Optional Memoral: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Richard of Chichester</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, bishop</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">19 June 2026
-Friday
-Eleventh Week • Ordinary Time
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Romuald</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, abbot</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">20 June 2026
-Saturday
-Eleventh Week • Ordinary Time
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Alban</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, martyr</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">22 June 2026
-Monday
-Twelfth Week • Ordinary Time
-Feast: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Sts John Fisher and Thomas More</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, martyrs</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">23 June 2026
-Tuesday
-Twelfth Week • Ordinary Time
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St. Etheldreda</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, abbess</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">24 June 2026
-Wednesday
-Twelfth Week • Ordinary Time
-Solemnity: The Nativity of </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St John the Baptist</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">27 June 2026
-Saturday
-Twelfth Week • Ordinary Time
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>St Cyril of Alexandria</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, bishop and Doctor of the Church</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">28 June 2026
-Sunday
-Thirteenth Week • Ordinary Time
-Solemnity: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Sts Peter and Paul</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>, apostles</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">30 June 2026
-Tuesday
-Thirteenth Week • Ordinary Time
-Optional Memorial: </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>The First Martyrs of the Church of Rome</t>
+      <t>St Dominic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, priest</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are in Ordinary Time, on the Saturday of its seventeenth week, and today the Church remembers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Alphonsus Liguori</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>, a working lawyer who became a priest and who then spent the rest of his life on the question of what ordinary people could actually be asked to do.</t>
+    </r>
+  </si>
+  <si>
+    <t>Lord, 
+You have not waited for us to be made right before wanting us near.
+You call us to amend what we have neglected, and in the same breath you ask to dwell with us as we are.
+We confess the things we have quietly stopped tending, not because they were too broken for you, but because we had not yet decided they were worth mending.
+Come near to them anyway. Give us the will to amend what we have neglected, and the patience to let you do it with us rather than waiting until it is done.
+Amen.</t>
+  </si>
+  <si>
+    <t>Go back to the lamp from a moment ago. 
+Nobody trims a lamp they've already decided to throw out. So if God is telling you to amend your life, that instruction only makes sense if God has already decided you're worth keeping as you are, faults and all, before you've fixed a single thing.
+Now think of something in your own life you quietly stopped looking after. Maybe a friendship you let go thin, fewer messages, shorter visits, until distance became the normal state of it rather than something either of you chose. Or a part of yourself you quietly filed as not worth the bother and stopped checking on.
+What would it look like to let God amend it with you, not once you've tidied it up yourself, but exactly as it stands now?</t>
+  </si>
+  <si>
+    <t>Light a candle or a flame at some point today.
+Before you do anything else with the flickering light, spend thirty seconds simply keeping it burning: shielding it from the draught, watching it, tending it. 
+As you do, hold the friendship, or the part of yourself, that this morning's contemplation named, and let God see it with you exactly as it stands.
+You have just let God begin to amend it with you, before it was fixed. That is today's practice.</t>
+  </si>
+  <si>
+    <r>
+      <t>Thus says the Lord of hosts, the God of Israel:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Amend your ways and your doings, and let me dwell with you in this place.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Jeremiah</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 7:3 (NRSV)</t>
     </r>
   </si>
   <si>
@@ -9946,7 +12795,7 @@
         <rFont val="Georgia"/>
         <family val="1"/>
       </rPr>
-      <t>SPIRIT [SPIR-it]</t>
+      <t>HONOUR [ON-er]</t>
     </r>
     <r>
       <rPr>
@@ -9956,62 +12805,57 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">
-In the original languages of scripture, the word for spirit carries more than one meaning at once — and that is not an accident.
-The Hebrew </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>ruach</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (רוּחַ) means wind, breath and spirit. The Greek </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>pneuma</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (πνεῦμα) carries the same range. In both cases, what the word holds together is the movement of an invisible force that is known not by being seen but by what it does: the breath that animates a body, the wind that bends the trees, the spirit that moves through and beyond what is merely physical.
-This is why, when the Spirit arrives at Pentecost, it arrives as wind and fire — not as metaphors added afterward to explain something, but as the thing itself in its most recognisable forms. The word was never only spiritual in the modern, ethereal sense. It was always also breath. Always also force.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>"When the day of Pentecost had come, they were all together in one place. 
-And suddenly from heaven there came a sound like the rush of a violent wind, and it filled the entire house where they were sitting. 
-Divided tongues, as of fire, appeared among them, and a tongue rested on each of them. 
-All of them were filled with the Holy Spirit and began to speak in other languages, as the Spirit gave them ability."</t>
+Honour sounds like a formal word. It belongs to medals and speeches and the kind of courtesy you extend to people who have clearly earned it. 
+The Greek word behind it in the New Testament, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>timē</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (τιμή), is far more ordinary than that: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>timē</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> is simply what something is worth. 
+It covers the value of a field as much as the regard owed to a person, because both are answers to the same question: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>what is this is worth to you?</t>
     </r>
     <r>
       <rPr>
@@ -10021,63 +12865,20 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Acts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 2:1–4 — NRSV</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">What arrived at Pentecost did not arrive quietly. It arrived as wind and fire — disruptive, unmistakable, impossible to ignore. The disciples in that room had been waiting, praying and keeping still. They had done everything that could be done from the human side.
-And then something happened that they could not have produced by their own waiting.
-That is the character of the Spirit throughout scripture: it is not generated, it is received. It comes from outside the system. It does not reward effort in the way that effort normally expects to be rewarded. It comes when and how it will — which is not an argument against preparation, but an argument against the assumption that preparation is what causes the arrival.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Where in your life have you been trying to generate what can only be received — working to produce a quality of faith, peace or love that is, in the end, a gift? 
-And what would it mean to stop producing and simply become the kind of person through whom the Spirit can move?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Choose one thing today that you have been trying to do in your own strength — a conversation you have been dreading, a habit you have been fighting, a relationship you have been managing — and before you face it, pause and ask the Spirit to go with you into it.
-Not a long prayer. A single breath, and the simplest of requests:
-Come, Holy Spirit.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Veni, Sancte Spiritus.</t>
+So honour turns out to be a reckoning rather than a courtesy. To honour someone is to have arrived at an estimate of what they are worth and to treat them accordingly, whether or not you could say out loud what that estimate really is. 
+Because honour is not really something you give or withhold now and again.  You are doing it all the time—to everyone you know—and mostly without noticing it.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>AMEND [uh-MEND]</t>
     </r>
     <r>
       <rPr>
@@ -10087,33 +12888,280 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>The Spirit does not need elaborate invitation. It needs only the door to be open.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Author · Acts of the Apostles (1st century AD). 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF3D4A5C"/>
-        <rFont val="Georgia"/>
-        <family val="1"/>
-      </rPr>
-      <t>Traditionally identified as Luke, a physician and companion of St Paul, and as the author of both the synonymous Gospel and the Acts of the Apostles. He is featured today because the opening of Acts 2 is his account of the Spirit's arrival at Pentecost — the event that closes Eastertide and opens the life of the Church.</t>
-    </r>
+Amend sounds like a word for fixing what has gone wrong. That is certainly what the English carries: it arrives from the Latin </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>emendare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, to take the fault out, and when the front of the word wore away over the centuries what was left behind was </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>mend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+The Hebrew verb that sits behind it runs the other way. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Yatab</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (יָטַב) does not mean remove the flaw. It means make it good. It is the verb used for tending the lamps in the sanctuary, trimming them every morning so they burn properly. Nothing there is broken and nothing is being repaired. Something that already works is being made to work well.
+So amending a life is less about damage repair than about preemptive care: the sort of care you would give to anything you wanted to keep working well. It also assumes the life is worth keeping. 
+You do not trim a lamp you have decided to throw away.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>St Alphonsus Liguori (1696–1787)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Italian bishop, moral theologian and Doctor of the Church. The Church remembers him today. Before entering the priesthood he had already practised law for eight years; afterwards he founded the Redemptorists to bring preaching and confession to rural communities that the Church of his day had largely stopped reaching.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Jeremiah (active c. 627–580 BC) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Hebrew prophet in Judah in the decades before and during the Babylonian conquest of Jerusalem. He is featured today because the words quoted in our scripture are the ones that put him on trial for his life: priests and prophets demanded his execution for speaking them, and he was spared only when the city's elders intervened.</t>
+    </r>
+  </si>
+  <si>
+    <t>We are in Ordinary Time, on the Sunday of its eighteenth week. 
+The name is not a comment on the quality of the weeks. It comes from the ordinal numbers used to count them, first, second, third, and it covers the long stretch of the year during which the Church is neither preparing for a festival nor recovering from one. 
+That leaves the weeks to be lived rather than observed, which is a fair description of most of the year and of most of a life.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>SATISFY [SAT-iss-fye]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Satisfy is, underneath, an accounting word. It arrives from the Latin </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>satis facere</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, to do enough, and English kept it in that ledger sense for centuries. You satisfy a debt, or a claim, or a court. Something is owed, the amount is met, and the matter closes.
+The Hebrew word behind it, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>sabaʿ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (שָׂבַע), keeps none of that. It is the ordinary word for having eaten your fill, and it belongs at the end of a meal rather than at the end of a transaction.
+So satisfaction in Hebrew is not the closing of an account. It is the condition of having enough. And the Old Testament treats that condition as the more precarious of the two, because being full makes it easy to stop noticing where the food came from.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>. 
+A collection of 150 Hebrew poems, written over several centuries and used in Jewish and Christian worship ever since. They are songs rather than arguments, and they run the full range from praise to complaint. 
+Psalm 145 is a poem of praise built as an acrostic, each verse beginning with the next letter of the Hebrew alphabet in turn, which is one way of saying that the praise is meant to be exhaustive.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">The eyes of all look to you,
+and you give them their food in due season.
+You open your hand,
+satisfying the desire of every living thing.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Psalm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 145:15–16 — NRSV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The psalm does not say that God satisfies the needs of every living thing. It says the desires, which is a larger and considerably less respectable word. 
+Needs can be itemised and defended, and there is a version of prayer that consists almost entirely of them. 
+Desire is the thing wanted without a case attached, and most of it is never said aloud anywhere, least of all in prayer, on the assumption that it would not qualify. 
+The psalm makes no such distinction. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF3D4A5C"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+      </rPr>
+      <t>Name to yourself one thing you want that you have never considered suitable to want in front of God. Tell God what it is, without explaining why you should be allowed to want it.</t>
+    </r>
+  </si>
+  <si>
+    <t>O God,
+Who opens your hand to every living thing, and satisfies the desire of all that you have made:
+We come to you with the wants we are willing to say, and the wants we have kept back because we did not think they would qualify.
+Teach us to ask without first proving that we deserve an answer.
+Satisfy us not as a debt discharged but as a table set, and where what we want is not good for us, want better for us than we know how to want for ourselves.
+In Christ's name, Amen.</t>
+  </si>
+  <si>
+    <t>At one meal today, stop when you have had enough rather than when the plate is empty. Not less than enough and not more than enough. Just enough.
+The point is to catch the moment itself, because it passes almost unnoticed most days. There is a specific point at which the body registers that it has been satisfied, and it usually arrives before we stop eating. 
+When you notice it, say to God, silently, that you have enough. Then decide whether to keep eating or to stop. Either is fine.
+Whatever you decide about the rest of the meal, sit with the fact that the moment came at all. Something in you registered that it had been satisfied, and you did not arrange for that to happen. 
+Ask God today what else in your life has been satisfied without your arranging it.</t>
   </si>
 </sst>
 </file>
@@ -11632,7 +14680,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>204</v>
       </c>
@@ -11662,7 +14710,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>205</v>
       </c>
@@ -11856,22 +14904,22 @@
         <v>312</v>
       </c>
       <c r="E25" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="F25" s="26" t="s">
         <v>422</v>
       </c>
-      <c r="F25" s="26" t="s">
+      <c r="G25" s="24" t="s">
         <v>423</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>424</v>
       </c>
       <c r="H25" s="27" t="s">
         <v>313</v>
       </c>
       <c r="I25" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="J25" s="28" t="s">
         <v>425</v>
-      </c>
-      <c r="J25" s="28" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -12167,7 +15215,7 @@
         <v>327</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>375</v>
@@ -12191,7 +15239,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>261</v>
       </c>
@@ -12199,7 +15247,7 @@
         <v>391</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>380</v>
@@ -12255,7 +15303,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>263</v>
       </c>
@@ -12265,15 +15313,29 @@
       <c r="C5" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="14"/>
+      <c r="D5" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>432</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>264</v>
       </c>
@@ -12283,15 +15345,29 @@
       <c r="C6" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="28"/>
+      <c r="D6" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>435</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>438</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>436</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>437</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>265</v>
       </c>
@@ -12299,17 +15375,31 @@
         <v>329</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="28"/>
+        <v>447</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>440</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>441</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>442</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>445</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>446</v>
+      </c>
     </row>
-    <row r="8" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="358" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>266</v>
       </c>
@@ -12317,17 +15407,31 @@
         <v>328</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>396</v>
-      </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="28"/>
+        <v>395</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>454</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>449</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>453</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>452</v>
+      </c>
     </row>
-    <row r="9" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>267</v>
       </c>
@@ -12335,17 +15439,29 @@
         <v>329</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="24"/>
+        <v>398</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>460</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>457</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>458</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>459</v>
+      </c>
       <c r="J9" s="28"/>
     </row>
-    <row r="10" spans="1:10" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>268</v>
       </c>
@@ -12353,17 +15469,31 @@
         <v>329</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="28"/>
+        <v>408</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>466</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>462</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>467</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>463</v>
+      </c>
     </row>
-    <row r="11" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>269</v>
       </c>
@@ -12371,35 +15501,63 @@
         <v>329</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>400</v>
-      </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="28"/>
+        <v>399</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>470</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>471</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>468</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>472</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>473</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>474</v>
+      </c>
     </row>
-    <row r="12" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>270</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>327</v>
+        <v>391</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>410</v>
-      </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="28"/>
+        <v>409</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>475</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>476</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>477</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>478</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>480</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>481</v>
+      </c>
     </row>
-    <row r="13" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="409.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>271</v>
       </c>
@@ -12407,17 +15565,31 @@
         <v>329</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="28"/>
+        <v>400</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>482</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>483</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>488</v>
+      </c>
     </row>
-    <row r="14" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>272</v>
       </c>
@@ -12425,17 +15597,31 @@
         <v>328</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>411</v>
-      </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="28"/>
+        <v>410</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>495</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>491</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>492</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>493</v>
+      </c>
     </row>
-    <row r="15" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>273</v>
       </c>
@@ -12443,15 +15629,29 @@
         <v>328</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>412</v>
-      </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="28"/>
+        <v>411</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>497</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>498</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>499</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
@@ -12461,7 +15661,7 @@
         <v>329</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
@@ -12479,7 +15679,7 @@
         <v>329</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
@@ -12497,7 +15697,7 @@
         <v>329</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
@@ -12515,7 +15715,7 @@
         <v>329</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
@@ -12533,7 +15733,7 @@
         <v>329</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
@@ -12551,7 +15751,7 @@
         <v>391</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
@@ -12569,7 +15769,7 @@
         <v>329</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D22" s="24"/>
       <c r="E22" s="24"/>
@@ -12587,7 +15787,7 @@
         <v>327</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="24"/>
@@ -12605,7 +15805,7 @@
         <v>328</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
@@ -12623,7 +15823,7 @@
         <v>328</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
@@ -12641,7 +15841,7 @@
         <v>329</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
@@ -12659,7 +15859,7 @@
         <v>329</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
@@ -12677,7 +15877,7 @@
         <v>329</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24"/>
@@ -12695,7 +15895,7 @@
         <v>327</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="24"/>
@@ -12713,7 +15913,7 @@
         <v>329</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="24"/>
@@ -12731,7 +15931,7 @@
         <v>391</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
@@ -12745,6 +15945,1107 @@
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="28" fitToHeight="8" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAC4FA0-3553-1F41-AED0-87093F58DA19}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="10"/>
+    <col min="2" max="2" width="20.83203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" style="2" customWidth="1"/>
+    <col min="4" max="10" width="50.83203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="5" customFormat="1" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="14"/>
+    </row>
+    <row r="4" spans="1:10" s="5" customFormat="1" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="14"/>
+    </row>
+    <row r="5" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="28"/>
+    </row>
+    <row r="7" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="28"/>
+    </row>
+    <row r="8" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="28"/>
+    </row>
+    <row r="9" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="28"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="28"/>
+    </row>
+    <row r="11" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="28"/>
+    </row>
+    <row r="12" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="28"/>
+    </row>
+    <row r="13" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="28"/>
+    </row>
+    <row r="14" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="28"/>
+    </row>
+    <row r="15" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="28"/>
+    </row>
+    <row r="16" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="28"/>
+    </row>
+    <row r="17" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="28"/>
+    </row>
+    <row r="18" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="28"/>
+    </row>
+    <row r="19" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="28"/>
+    </row>
+    <row r="20" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="28"/>
+    </row>
+    <row r="21" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="28"/>
+    </row>
+    <row r="22" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="28"/>
+    </row>
+    <row r="23" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="28"/>
+    </row>
+    <row r="24" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="28"/>
+    </row>
+    <row r="25" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="28"/>
+    </row>
+    <row r="26" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="28"/>
+    </row>
+    <row r="27" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>528</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="28"/>
+    </row>
+    <row r="28" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>529</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="28"/>
+    </row>
+    <row r="29" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>531</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="28"/>
+    </row>
+    <row r="31" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="28"/>
+    </row>
+    <row r="32" spans="1:10" ht="406" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>538</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>585</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>535</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="H32" s="27" t="s">
+        <v>536</v>
+      </c>
+      <c r="I32" s="24" t="s">
+        <v>540</v>
+      </c>
+      <c r="J32" s="28" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="33" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="28" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944EFDAB-E760-0C4C-9D75-EF25B87A98FA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="10"/>
+    <col min="2" max="2" width="20.83203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" style="2" customWidth="1"/>
+    <col min="4" max="10" width="50.83203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="5" customFormat="1" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>572</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>573</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="5" customFormat="1" ht="70" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>574</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="14"/>
+    </row>
+    <row r="5" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>575</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>576</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="28"/>
+    </row>
+    <row r="7" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>577</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="28"/>
+    </row>
+    <row r="8" spans="1:10" ht="104" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>578</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="28"/>
+    </row>
+    <row r="9" spans="1:10" ht="87" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>579</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="28"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="28"/>
+    </row>
+    <row r="11" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="28"/>
+    </row>
+    <row r="12" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>550</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C12" s="37"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="28"/>
+    </row>
+    <row r="13" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="28"/>
+    </row>
+    <row r="14" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="C14" s="37"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="28"/>
+    </row>
+    <row r="15" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="28"/>
+    </row>
+    <row r="16" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="28"/>
+    </row>
+    <row r="17" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="28"/>
+    </row>
+    <row r="18" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="28"/>
+    </row>
+    <row r="19" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>557</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C19" s="37"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="28"/>
+    </row>
+    <row r="20" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="28"/>
+    </row>
+    <row r="21" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="28"/>
+    </row>
+    <row r="22" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="28"/>
+    </row>
+    <row r="23" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="28"/>
+    </row>
+    <row r="24" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>562</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="28"/>
+    </row>
+    <row r="25" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="28"/>
+    </row>
+    <row r="26" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C26" s="37"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="28"/>
+    </row>
+    <row r="27" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>565</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C27" s="23"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="28"/>
+    </row>
+    <row r="28" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>566</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C28" s="37"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="28"/>
+    </row>
+    <row r="29" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>567</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C29" s="23"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="28"/>
+    </row>
+    <row r="31" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="28"/>
+    </row>
+    <row r="32" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="28"/>
+    </row>
+    <row r="33" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="28" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>